--- a/03.game/FPS_chars.xlsx
+++ b/03.game/FPS_chars.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EFDF42F-9093-44B1-95D1-BF45D03A5933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FA8D6D-6128-48B0-8434-1535AB650DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="シート1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="93">
   <si>
     <t>名前</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>Tartaglia</t>
+  </si>
+  <si>
+    <t>Nanasaki</t>
+  </si>
+  <si>
+    <t>Less</t>
+  </si>
+  <si>
+    <t>WoohyuN</t>
+  </si>
+  <si>
+    <t>Asuna</t>
+  </si>
+  <si>
+    <t>Cryocells</t>
+  </si>
+  <si>
+    <t>vo0kashu</t>
   </si>
 </sst>
 </file>
@@ -362,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -374,6 +392,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -592,7 +611,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T1000"/>
+  <dimension ref="A1:AA1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -601,9 +620,11 @@
     <col min="9" max="10" width="16.5703125" customWidth="1"/>
     <col min="17" max="17" width="14.85546875" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" customWidth="1"/>
+    <col min="26" max="26" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,35 +658,46 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R1" t="s">
+      <c r="W1" t="s">
         <v>6</v>
       </c>
-      <c r="S1" t="s">
+      <c r="X1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T1" t="s">
+      <c r="Z1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" customHeight="1">
+      <c r="AA1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -673,13 +705,13 @@
         <v>0.35</v>
       </c>
       <c r="C2" s="2">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="D2" s="2">
         <v>105</v>
       </c>
       <c r="E2" s="2">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="F2" s="4">
         <v>135</v>
@@ -692,45 +724,51 @@
       </c>
       <c r="I2" s="4">
         <f>B2*130+(C2)*170+(D2/2)+(E2-0.2)*130+(F2/2.2)</f>
-        <v>258.36363636363637</v>
+        <v>273.86363636363637</v>
       </c>
       <c r="J2" s="10">
         <f>B2*130+(C2)*170+(E2-0.2)*130+(F2/2.2)</f>
-        <v>205.86363636363637</v>
+        <v>221.36363636363637</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" t="str" cm="1">
-        <f t="array" ref="L2:T97">_xlfn._xlws.SORT(A2:I97, {9}, {-1})</f>
-        <v>Tortlilyan</v>
-      </c>
-      <c r="M2">
-        <v>0.23</v>
-      </c>
-      <c r="N2">
-        <v>0.34</v>
-      </c>
-      <c r="O2">
-        <v>123</v>
-      </c>
-      <c r="P2">
-        <v>0.81</v>
-      </c>
-      <c r="Q2">
-        <v>155</v>
-      </c>
-      <c r="R2" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S2" s="10">
+      <c r="Q2" t="str" cm="1">
+        <f t="array" ref="Q2:AA97">_xlfn._xlws.SORT(A2:K97, {10}, {-1})</f>
+        <v>まーやまくん</v>
+      </c>
+      <c r="R2" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="S2" s="11">
+        <v>0.21</v>
+      </c>
+      <c r="T2" s="10">
+        <v>90</v>
+      </c>
+      <c r="U2" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="V2" s="10">
+        <v>140</v>
+      </c>
+      <c r="W2" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X2">
         <v>50</v>
       </c>
-      <c r="T2" s="10">
-        <v>298.95454545454544</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y2" s="10">
+        <v>296.43636363636364</v>
+      </c>
+      <c r="Z2" s="10">
+        <v>251.43636363636361</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -744,7 +782,7 @@
         <v>80</v>
       </c>
       <c r="E3" s="2">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="F3" s="4">
         <v>145</v>
@@ -757,44 +795,50 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I66" si="0">B3*130+(C3)*170+(D3/2)+(E3-0.2)*130+(F3/2.2)</f>
-        <v>278.80909090909086</v>
+        <v>277.5090909090909</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" ref="J3:J66" si="1">B3*130+(C3)*170+(E3-0.2)*130+(F3/2.2)</f>
-        <v>238.80909090909088</v>
+        <v>237.50909090909087</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" t="str">
-        <v>まーやまくん</v>
-      </c>
-      <c r="M3">
-        <v>0.7</v>
-      </c>
-      <c r="N3">
-        <v>0.21</v>
-      </c>
-      <c r="O3">
-        <v>90</v>
-      </c>
-      <c r="P3">
-        <v>0.67</v>
-      </c>
-      <c r="Q3">
-        <v>140</v>
-      </c>
-      <c r="R3" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S3" s="10">
-        <v>50</v>
+      <c r="Q3" t="str">
+        <v>something</v>
+      </c>
+      <c r="R3" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S3" s="11">
+        <v>0.24</v>
       </c>
       <c r="T3" s="10">
-        <v>296.43636363636364</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" customHeight="1">
+        <v>70</v>
+      </c>
+      <c r="U3" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="V3" s="10">
+        <v>165</v>
+      </c>
+      <c r="W3" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X3">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>284.7</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>249.7</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -830,35 +874,41 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" t="str">
-        <v>Leo</v>
-      </c>
-      <c r="M4">
-        <v>0.27</v>
-      </c>
-      <c r="N4">
-        <v>0.22</v>
-      </c>
-      <c r="O4">
-        <v>150</v>
-      </c>
-      <c r="P4">
-        <v>0.83</v>
-      </c>
-      <c r="Q4">
-        <v>135</v>
-      </c>
-      <c r="R4" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S4" s="10">
-        <v>65</v>
+      <c r="Q4" t="str">
+        <v>Alfajer</v>
+      </c>
+      <c r="R4" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="S4" s="11">
+        <v>0.13</v>
       </c>
       <c r="T4" s="10">
-        <v>290.76363636363635</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1">
+        <v>60</v>
+      </c>
+      <c r="U4" s="11">
+        <v>0.91</v>
+      </c>
+      <c r="V4" s="10">
+        <v>145</v>
+      </c>
+      <c r="W4" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X4">
+        <v>60</v>
+      </c>
+      <c r="Y4" s="10">
+        <v>268.80909090909086</v>
+      </c>
+      <c r="Z4" s="10">
+        <v>238.80909090909088</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -894,35 +944,41 @@
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5" t="str">
-        <v>something</v>
-      </c>
-      <c r="M5">
-        <v>0.35</v>
-      </c>
-      <c r="N5">
-        <v>0.24</v>
-      </c>
-      <c r="O5">
-        <v>70</v>
-      </c>
-      <c r="P5">
-        <v>0.88</v>
-      </c>
-      <c r="Q5">
-        <v>165</v>
-      </c>
-      <c r="R5" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S5" s="10">
-        <v>60</v>
+      <c r="Q5" t="str">
+        <v>Demon1</v>
+      </c>
+      <c r="R5" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="S5" s="11">
+        <v>0.13</v>
       </c>
       <c r="T5" s="10">
-        <v>284.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15.75" customHeight="1">
+        <v>80</v>
+      </c>
+      <c r="U5" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="V5" s="10">
+        <v>145</v>
+      </c>
+      <c r="W5" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X5">
+        <v>150</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>277.5090909090909</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>237.50909090909087</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -958,35 +1014,41 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" t="str">
-        <v>Aspas</v>
-      </c>
-      <c r="M6">
-        <v>0.4</v>
-      </c>
-      <c r="N6">
-        <v>0.24</v>
-      </c>
-      <c r="O6">
-        <v>90</v>
-      </c>
-      <c r="P6">
-        <v>0.87</v>
-      </c>
-      <c r="Q6">
-        <v>120</v>
-      </c>
-      <c r="R6" s="10" t="str">
+      <c r="Q6" t="str">
+        <v>Tortlilyan</v>
+      </c>
+      <c r="R6" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="S6" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="T6" s="10">
+        <v>123</v>
+      </c>
+      <c r="U6" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="V6" s="10">
+        <v>155</v>
+      </c>
+      <c r="W6" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S6" s="10">
-        <v>130</v>
-      </c>
-      <c r="T6" s="10">
-        <v>279.44545454545454</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X6">
+        <v>50</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>298.95454545454544</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>237.45454545454544</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1022,35 +1084,41 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" t="str">
-        <v>Demon1</v>
-      </c>
-      <c r="M7">
+      <c r="Q7" t="str">
+        <v>Zest</v>
+      </c>
+      <c r="R7" s="11">
         <v>0.5</v>
       </c>
-      <c r="N7">
-        <v>0.13</v>
-      </c>
-      <c r="O7">
-        <v>80</v>
-      </c>
-      <c r="P7">
-        <v>0.86</v>
-      </c>
-      <c r="Q7">
-        <v>145</v>
-      </c>
-      <c r="R7" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S7" s="10">
-        <v>150</v>
+      <c r="S7" s="11">
+        <v>0.25</v>
       </c>
       <c r="T7" s="10">
-        <v>278.80909090909086</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="15.75" customHeight="1">
+        <v>75</v>
+      </c>
+      <c r="U7" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="V7" s="10">
+        <v>121</v>
+      </c>
+      <c r="W7" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>272.8</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>235.3</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1086,35 +1154,41 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="L8" t="str">
-        <v>Zest</v>
-      </c>
-      <c r="M8">
-        <v>0.5</v>
-      </c>
-      <c r="N8">
-        <v>0.25</v>
-      </c>
-      <c r="O8">
-        <v>75</v>
-      </c>
-      <c r="P8">
-        <v>0.76</v>
-      </c>
-      <c r="Q8">
-        <v>121</v>
-      </c>
-      <c r="R8" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S8" s="10">
+      <c r="Q8" t="str">
+        <v>Lohen</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="T8" s="10">
+        <v>70</v>
+      </c>
+      <c r="U8" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V8" s="10">
+        <v>130</v>
+      </c>
+      <c r="W8" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X8">
         <v>100</v>
       </c>
-      <c r="T8" s="10">
-        <v>272.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y8" s="10">
+        <v>270.29090909090905</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>235.29090909090908</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -1150,40 +1224,46 @@
       <c r="K9">
         <v>1</v>
       </c>
-      <c r="L9" t="str">
-        <v>Lohen</v>
-      </c>
-      <c r="M9">
+      <c r="Q9" t="str">
+        <v>Aspas</v>
+      </c>
+      <c r="R9" s="11">
         <v>0.4</v>
       </c>
-      <c r="N9">
-        <v>0.31</v>
-      </c>
-      <c r="O9">
-        <v>70</v>
-      </c>
-      <c r="P9">
-        <v>0.75</v>
-      </c>
-      <c r="Q9">
+      <c r="S9" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="T9" s="10">
+        <v>90</v>
+      </c>
+      <c r="U9" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="V9" s="10">
+        <v>120</v>
+      </c>
+      <c r="W9" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X9">
         <v>130</v>
       </c>
-      <c r="R9" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S9" s="10">
-        <v>100</v>
-      </c>
-      <c r="T9" s="10">
-        <v>270.29090909090905</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y9" s="10">
+        <v>279.44545454545454</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>234.44545454545451</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="6">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="C10" s="2">
         <v>0.14000000000000001</v>
@@ -1205,44 +1285,50 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>226.9818181818182</v>
+        <v>228.28181818181818</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v>164.48181818181817</v>
+        <v>165.78181818181818</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="L10" t="str">
+      <c r="Q10" t="str">
         <v>Tartaglia</v>
       </c>
-      <c r="M10">
+      <c r="R10" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N10">
+      <c r="S10" s="11">
         <v>0.15</v>
       </c>
-      <c r="O10">
+      <c r="T10" s="10">
         <v>75</v>
       </c>
-      <c r="P10">
+      <c r="U10" s="11">
         <v>0.72</v>
       </c>
-      <c r="Q10">
+      <c r="V10" s="10">
         <v>150</v>
       </c>
-      <c r="R10" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S10" s="10">
-        <v>150</v>
-      </c>
-      <c r="T10" s="10">
+      <c r="W10" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X10">
+        <v>80</v>
+      </c>
+      <c r="Y10" s="10">
         <v>270.28181818181821</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Z10" s="10">
+        <v>232.78181818181821</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1278,35 +1364,41 @@
       <c r="K11">
         <v>1</v>
       </c>
-      <c r="L11" t="str">
-        <v>Jean</v>
-      </c>
-      <c r="M11">
-        <v>0.35</v>
-      </c>
-      <c r="N11">
-        <v>0.2</v>
-      </c>
-      <c r="O11">
-        <v>115</v>
-      </c>
-      <c r="P11">
+      <c r="Q11" t="str">
+        <v>Nanasaki</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="S11" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="T11" s="10">
+        <v>100</v>
+      </c>
+      <c r="U11" s="11">
         <v>0.75</v>
       </c>
-      <c r="Q11">
-        <v>135</v>
-      </c>
-      <c r="R11" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S11" s="10">
-        <v>50</v>
-      </c>
-      <c r="T11" s="10">
-        <v>269.86363636363637</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="15.75" customHeight="1">
+      <c r="V11" s="10">
+        <v>80</v>
+      </c>
+      <c r="W11" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X11">
+        <v>75</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>277.86363636363637</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>227.86363636363637</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1342,35 +1434,41 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" t="str">
-        <v>Arlecchino</v>
-      </c>
-      <c r="M12">
+      <c r="Q12" t="str">
+        <v>Primmie</v>
+      </c>
+      <c r="R12" s="11">
         <v>0.47</v>
       </c>
-      <c r="N12">
-        <v>0.19</v>
-      </c>
-      <c r="O12">
-        <v>135</v>
-      </c>
-      <c r="P12">
-        <v>0.6</v>
-      </c>
-      <c r="Q12">
-        <v>125</v>
-      </c>
-      <c r="R12" s="10" t="str">
+      <c r="S12" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="T12" s="10">
+        <v>59</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="V12" s="10">
+        <v>98</v>
+      </c>
+      <c r="W12" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S12" s="10">
-        <v>100</v>
-      </c>
-      <c r="T12" s="10">
-        <v>269.71818181818179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X12">
+        <v>90</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>252.64545454545453</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>223.14545454545456</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1406,35 +1504,41 @@
       <c r="K13">
         <v>1</v>
       </c>
-      <c r="L13" t="str">
-        <v>Lisa</v>
-      </c>
-      <c r="M13">
-        <v>0.36</v>
-      </c>
-      <c r="N13">
-        <v>0.25</v>
-      </c>
-      <c r="O13">
-        <v>120</v>
-      </c>
-      <c r="P13">
+      <c r="Q13" t="str">
+        <v>Chronicle</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="T13" s="10">
+        <v>105</v>
+      </c>
+      <c r="U13" s="11">
         <v>0.78</v>
       </c>
-      <c r="Q13">
-        <v>99</v>
-      </c>
-      <c r="R13" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S13" s="10">
+      <c r="V13" s="10">
+        <v>135</v>
+      </c>
+      <c r="W13" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X13">
         <v>80</v>
       </c>
-      <c r="T13" s="10">
-        <v>269.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y13" s="10">
+        <v>273.86363636363637</v>
+      </c>
+      <c r="Z13" s="10">
+        <v>221.36363636363637</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1470,35 +1574,41 @@
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="L14" t="str">
-        <v>Alfajer</v>
-      </c>
-      <c r="M14">
-        <v>0.45</v>
-      </c>
-      <c r="N14">
-        <v>0.13</v>
-      </c>
-      <c r="O14">
-        <v>60</v>
-      </c>
-      <c r="P14">
-        <v>0.91</v>
-      </c>
-      <c r="Q14">
-        <v>145</v>
-      </c>
-      <c r="R14" s="10" t="str">
+      <c r="Q14" t="str">
+        <v>Canezera</v>
+      </c>
+      <c r="R14" s="11">
+        <v>0.41</v>
+      </c>
+      <c r="S14" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T14" s="10">
+        <v>90</v>
+      </c>
+      <c r="U14" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="V14" s="10">
+        <v>135</v>
+      </c>
+      <c r="W14" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S14" s="10">
-        <v>60</v>
-      </c>
-      <c r="T14" s="10">
-        <v>268.80909090909086</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X14">
+        <v>80</v>
+      </c>
+      <c r="Y14" s="10">
+        <v>265.26363636363641</v>
+      </c>
+      <c r="Z14" s="10">
+        <v>220.26363636363641</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1534,35 +1644,41 @@
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="L15" t="str">
-        <v>TenZ</v>
-      </c>
-      <c r="M15">
+      <c r="Q15" t="str">
+        <v>Flashback</v>
+      </c>
+      <c r="R15" s="11">
         <v>0.38</v>
       </c>
-      <c r="N15">
-        <v>0.23</v>
-      </c>
-      <c r="O15">
-        <v>105</v>
-      </c>
-      <c r="P15">
-        <v>0.76</v>
-      </c>
-      <c r="Q15">
-        <v>120</v>
-      </c>
-      <c r="R15" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S15" s="10">
-        <v>170</v>
+      <c r="S15" s="11">
+        <v>0.22</v>
       </c>
       <c r="T15" s="10">
-        <v>268.34545454545457</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="15.75" customHeight="1">
+        <v>79</v>
+      </c>
+      <c r="U15" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="V15" s="10">
+        <v>130</v>
+      </c>
+      <c r="W15" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X15">
+        <v>70</v>
+      </c>
+      <c r="Y15" s="10">
+        <v>259.4909090909091</v>
+      </c>
+      <c r="Z15" s="10">
+        <v>219.9909090909091</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,35 +1714,41 @@
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="L16" t="str">
-        <v>s0m</v>
-      </c>
-      <c r="M16">
-        <v>0.3</v>
-      </c>
-      <c r="N16">
-        <v>0.23</v>
-      </c>
-      <c r="O16">
-        <v>145</v>
-      </c>
-      <c r="P16">
-        <v>0.7</v>
-      </c>
-      <c r="Q16">
-        <v>116</v>
-      </c>
-      <c r="R16" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S16" s="10">
+      <c r="Q16" t="str">
+        <v>WoohyuN</v>
+      </c>
+      <c r="R16" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S16" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="T16" s="10">
+        <v>85</v>
+      </c>
+      <c r="U16" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V16" s="10">
+        <v>150</v>
+      </c>
+      <c r="W16" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X16">
         <v>55</v>
       </c>
-      <c r="T16" s="10">
-        <v>268.32727272727266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y16" s="10">
+        <v>261.68181818181819</v>
+      </c>
+      <c r="Z16" s="10">
+        <v>219.18181818181819</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1662,35 +1784,41 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="L17" t="str">
-        <v>Furina</v>
-      </c>
-      <c r="M17">
+      <c r="Q17" t="str">
+        <v>Meteor</v>
+      </c>
+      <c r="R17" s="11">
+        <v>0.37</v>
+      </c>
+      <c r="S17" s="11">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N17">
-        <v>0.19</v>
-      </c>
-      <c r="O17">
-        <v>149</v>
-      </c>
-      <c r="P17">
-        <v>0.69</v>
-      </c>
-      <c r="Q17">
-        <v>129</v>
-      </c>
-      <c r="R17" s="10" t="str">
+      <c r="T17" s="10">
+        <v>73</v>
+      </c>
+      <c r="U17" s="11">
+        <v>0.78</v>
+      </c>
+      <c r="V17" s="10">
+        <v>95</v>
+      </c>
+      <c r="W17" t="str">
         <v>フラッシュ</v>
       </c>
-      <c r="S17" s="10">
-        <v>30</v>
-      </c>
-      <c r="T17" s="10">
-        <v>266.83636363636361</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X17">
+        <v>75</v>
+      </c>
+      <c r="Y17" s="10">
+        <v>252.4818181818182</v>
+      </c>
+      <c r="Z17" s="10">
+        <v>215.9818181818182</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -1726,35 +1854,41 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" t="str">
-        <v>Canezera</v>
-      </c>
-      <c r="M18">
-        <v>0.41</v>
-      </c>
-      <c r="N18">
-        <v>0.17</v>
-      </c>
-      <c r="O18">
-        <v>95</v>
-      </c>
-      <c r="P18">
-        <v>0.77</v>
-      </c>
-      <c r="Q18">
-        <v>135</v>
-      </c>
-      <c r="R18" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S18" s="10">
-        <v>80</v>
+      <c r="Q18" t="str">
+        <v>TenZ</v>
+      </c>
+      <c r="R18" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="S18" s="11">
+        <v>0.23</v>
       </c>
       <c r="T18" s="10">
-        <v>265.16363636363639</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15.75" customHeight="1">
+        <v>105</v>
+      </c>
+      <c r="U18" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="V18" s="10">
+        <v>120</v>
+      </c>
+      <c r="W18" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X18">
+        <v>170</v>
+      </c>
+      <c r="Y18" s="10">
+        <v>268.34545454545457</v>
+      </c>
+      <c r="Z18" s="10">
+        <v>215.84545454545454</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1790,35 +1924,41 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19" t="str">
-        <v>Ethan</v>
-      </c>
-      <c r="M19">
-        <v>0.3</v>
-      </c>
-      <c r="N19">
-        <v>0.18</v>
-      </c>
-      <c r="O19">
+      <c r="Q19" t="str">
+        <v>Leo</v>
+      </c>
+      <c r="R19" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="S19" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="T19" s="10">
         <v>150</v>
       </c>
-      <c r="P19">
-        <v>0.8</v>
-      </c>
-      <c r="Q19">
-        <v>90</v>
-      </c>
-      <c r="R19" s="10" t="str">
+      <c r="U19" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="V19" s="10">
+        <v>135</v>
+      </c>
+      <c r="W19" t="str">
         <v>シーカー</v>
       </c>
-      <c r="S19" s="10">
-        <v>55</v>
-      </c>
-      <c r="T19" s="10">
-        <v>263.5090909090909</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X19">
+        <v>65</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>290.76363636363635</v>
+      </c>
+      <c r="Z19" s="10">
+        <v>215.76363636363635</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>33</v>
       </c>
@@ -1854,35 +1994,41 @@
       <c r="K20">
         <v>1</v>
       </c>
-      <c r="L20" t="str">
+      <c r="Q20" t="str">
         <v>t3xture</v>
       </c>
-      <c r="M20">
+      <c r="R20" s="11">
         <v>0.33</v>
       </c>
-      <c r="N20">
+      <c r="S20" s="11">
         <v>0.19</v>
       </c>
-      <c r="O20">
+      <c r="T20" s="10">
         <v>93</v>
       </c>
-      <c r="P20">
+      <c r="U20" s="11">
         <v>0.75</v>
       </c>
-      <c r="Q20">
+      <c r="V20" s="10">
         <v>150</v>
       </c>
-      <c r="R20" s="10" t="str">
+      <c r="W20" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S20" s="10">
+      <c r="X20">
         <v>75</v>
       </c>
-      <c r="T20" s="10">
+      <c r="Y20" s="10">
         <v>261.38181818181818</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Z20" s="10">
+        <v>214.88181818181818</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -1918,35 +2064,41 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21" t="str">
-        <v>Flashback</v>
-      </c>
-      <c r="M21">
-        <v>0.38</v>
-      </c>
-      <c r="N21">
-        <v>0.22</v>
-      </c>
-      <c r="O21">
-        <v>79</v>
-      </c>
-      <c r="P21">
-        <v>0.77</v>
-      </c>
-      <c r="Q21">
-        <v>130</v>
-      </c>
-      <c r="R21" s="10" t="str">
+      <c r="Q21" t="str">
+        <v>おもこ</v>
+      </c>
+      <c r="R21" s="11">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="S21" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="T21" s="10">
+        <v>67</v>
+      </c>
+      <c r="U21" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="V21" s="10">
+        <v>67</v>
+      </c>
+      <c r="W21" t="str">
         <v>フラッシュ</v>
       </c>
-      <c r="S21" s="10">
-        <v>70</v>
-      </c>
-      <c r="T21" s="10">
-        <v>259.4909090909091</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X21">
+        <v>50</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>247.66454545454548</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>214.16454545454548</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -1982,35 +2134,41 @@
       <c r="K22">
         <v>1</v>
       </c>
-      <c r="L22" t="str">
-        <v>WsLeo</v>
-      </c>
-      <c r="M22">
-        <v>0.36</v>
-      </c>
-      <c r="N22">
-        <v>0.21</v>
-      </c>
-      <c r="O22">
-        <v>130</v>
-      </c>
-      <c r="P22">
-        <v>0.78</v>
-      </c>
-      <c r="Q22">
-        <v>80</v>
-      </c>
-      <c r="R22" s="10" t="str">
+      <c r="Q22" t="str">
+        <v>Jean</v>
+      </c>
+      <c r="R22" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S22" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="T22" s="10">
+        <v>115</v>
+      </c>
+      <c r="U22" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V22" s="10">
+        <v>135</v>
+      </c>
+      <c r="W22" t="str">
         <v>シーカー</v>
       </c>
-      <c r="S22" s="10">
-        <v>50</v>
-      </c>
-      <c r="T22" s="10">
-        <v>259.26363636363635</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X22">
+        <v>40</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>269.86363636363637</v>
+      </c>
+      <c r="Z22" s="10">
+        <v>212.36363636363637</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
@@ -2046,35 +2204,41 @@
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="L23" t="str">
-        <v>Chronicle</v>
-      </c>
-      <c r="M23">
-        <v>0.35</v>
-      </c>
-      <c r="N23">
-        <v>0.2</v>
-      </c>
-      <c r="O23">
-        <v>105</v>
-      </c>
-      <c r="P23">
-        <v>0.7</v>
-      </c>
-      <c r="Q23">
+      <c r="Q23" t="str">
+        <v>jawgemo</v>
+      </c>
+      <c r="R23" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S23" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="T23" s="10">
+        <v>93</v>
+      </c>
+      <c r="U23" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="V23" s="10">
         <v>135</v>
       </c>
-      <c r="R23" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S23" s="10">
-        <v>80</v>
-      </c>
-      <c r="T23" s="10">
-        <v>258.36363636363637</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="15.75" customHeight="1">
+      <c r="W23" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X23">
+        <v>75</v>
+      </c>
+      <c r="Y23" s="10">
+        <v>258.06363636363636</v>
+      </c>
+      <c r="Z23" s="10">
+        <v>211.56363636363636</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
@@ -2088,7 +2252,7 @@
         <v>59</v>
       </c>
       <c r="E24" s="1">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="F24" s="4">
         <v>98</v>
@@ -2101,44 +2265,50 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" si="0"/>
-        <v>247.44545454545451</v>
+        <v>252.64545454545453</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v>217.94545454545451</v>
+        <v>223.14545454545456</v>
       </c>
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="L24" t="str">
-        <v>jawgemo</v>
-      </c>
-      <c r="M24">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N24">
-        <v>0.31</v>
-      </c>
-      <c r="O24">
-        <v>93</v>
-      </c>
-      <c r="P24">
-        <v>0.67</v>
-      </c>
-      <c r="Q24">
-        <v>135</v>
-      </c>
-      <c r="R24" s="10" t="str">
+      <c r="Q24" t="str">
+        <v>Kachina</v>
+      </c>
+      <c r="R24" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="S24" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="T24" s="10">
+        <v>60</v>
+      </c>
+      <c r="U24" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="V24" s="10">
+        <v>90</v>
+      </c>
+      <c r="W24" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S24" s="10">
-        <v>75</v>
-      </c>
-      <c r="T24" s="10">
-        <v>258.06363636363636</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X24">
+        <v>40</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>241.40909090909091</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>211.40909090909091</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
@@ -2172,37 +2342,43 @@
         <v>237.45454545454544</v>
       </c>
       <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="str">
         <v>Derke</v>
       </c>
-      <c r="M25">
+      <c r="R25" s="11">
         <v>0.35</v>
       </c>
-      <c r="N25">
+      <c r="S25" s="11">
         <v>0.24</v>
       </c>
-      <c r="O25">
+      <c r="T25" s="10">
         <v>90</v>
       </c>
-      <c r="P25">
+      <c r="U25" s="11">
         <v>0.75</v>
       </c>
-      <c r="Q25">
+      <c r="V25" s="10">
         <v>115</v>
       </c>
-      <c r="R25" s="10" t="str">
+      <c r="W25" t="str">
         <v>フラッシュ</v>
       </c>
-      <c r="S25" s="10">
+      <c r="X25">
         <v>100</v>
       </c>
-      <c r="T25" s="10">
+      <c r="Y25" s="10">
         <v>255.07272727272726</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Z25" s="10">
+        <v>210.07272727272726</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
@@ -2236,37 +2412,43 @@
         <v>251.43636363636361</v>
       </c>
       <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26" t="str">
-        <v>mada</v>
-      </c>
-      <c r="M26">
-        <v>0.34</v>
-      </c>
-      <c r="N26">
-        <v>0.23</v>
-      </c>
-      <c r="O26">
-        <v>105</v>
-      </c>
-      <c r="P26">
-        <v>0.74</v>
-      </c>
-      <c r="Q26">
-        <v>105</v>
-      </c>
-      <c r="R26" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S26" s="10">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Lisa</v>
+      </c>
+      <c r="R26" s="11">
+        <v>0.36</v>
+      </c>
+      <c r="S26" s="11">
+        <v>0.25</v>
       </c>
       <c r="T26" s="10">
-        <v>253.72727272727272</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="15.75" customHeight="1">
+        <v>120</v>
+      </c>
+      <c r="U26" s="11">
+        <v>0.78</v>
+      </c>
+      <c r="V26" s="10">
+        <v>99</v>
+      </c>
+      <c r="W26" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X26">
+        <v>40</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>269.7</v>
+      </c>
+      <c r="Z26" s="10">
+        <v>209.7</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -2300,51 +2482,57 @@
         <v>214.16454545454548</v>
       </c>
       <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27" t="str">
-        <v>おもこ</v>
-      </c>
-      <c r="M27">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="N27">
-        <v>0.67</v>
-      </c>
-      <c r="O27">
-        <v>67</v>
-      </c>
-      <c r="P27">
-        <v>0.67</v>
-      </c>
-      <c r="Q27">
-        <v>67</v>
-      </c>
-      <c r="R27" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S27" s="10">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>vo0kashu</v>
+      </c>
+      <c r="R27" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S27" s="11">
+        <v>0.23</v>
       </c>
       <c r="T27" s="10">
-        <v>247.66454545454548</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1">
+        <v>78</v>
+      </c>
+      <c r="U27" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="V27" s="10">
+        <v>115</v>
+      </c>
+      <c r="W27" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X27">
+        <v>75</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>248.67272727272729</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>209.67272727272729</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="8">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="C28" s="3">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D28" s="3">
         <v>73</v>
       </c>
       <c r="E28" s="3">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F28" s="4">
         <v>95</v>
@@ -2357,44 +2545,50 @@
       </c>
       <c r="I28" s="4">
         <f t="shared" si="0"/>
-        <v>246.8818181818182</v>
+        <v>252.4818181818182</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v>210.3818181818182</v>
+        <v>215.9818181818182</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="L28" t="str">
-        <v>Primmie</v>
-      </c>
-      <c r="M28">
-        <v>0.47</v>
-      </c>
-      <c r="N28">
+      <c r="Q28" t="str">
+        <v>HYUNMIN</v>
+      </c>
+      <c r="R28" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S28" s="11">
         <v>0.24</v>
       </c>
-      <c r="O28">
-        <v>59</v>
-      </c>
-      <c r="P28">
+      <c r="T28" s="10">
+        <v>76</v>
+      </c>
+      <c r="U28" s="11">
         <v>0.75</v>
       </c>
-      <c r="Q28">
-        <v>98</v>
-      </c>
-      <c r="R28" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S28" s="10">
-        <v>90</v>
-      </c>
-      <c r="T28" s="10">
-        <v>247.44545454545451</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1">
+      <c r="V28" s="10">
+        <v>110</v>
+      </c>
+      <c r="W28" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X28">
+        <v>70</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>245.8</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>207.8</v>
+      </c>
+      <c r="AA28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>42</v>
       </c>
@@ -2430,35 +2624,41 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="L29" t="str">
-        <v>Meteor</v>
-      </c>
-      <c r="M29">
-        <v>0.36</v>
-      </c>
-      <c r="N29">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="O29">
-        <v>73</v>
-      </c>
-      <c r="P29">
-        <v>0.76</v>
-      </c>
-      <c r="Q29">
-        <v>95</v>
-      </c>
-      <c r="R29" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S29" s="10">
+      <c r="Q29" t="str">
+        <v>Wo0t</v>
+      </c>
+      <c r="R29" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="S29" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="T29" s="10">
+        <v>78</v>
+      </c>
+      <c r="U29" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V29" s="10">
+        <v>120</v>
+      </c>
+      <c r="W29" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X29">
         <v>75</v>
       </c>
-      <c r="T29" s="10">
-        <v>246.8818181818182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y29" s="10">
+        <v>244.24545454545452</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>205.24545454545452</v>
+      </c>
+      <c r="AA29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>43</v>
       </c>
@@ -2494,35 +2694,41 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="L30" t="str">
-        <v>HYUNMIN</v>
-      </c>
-      <c r="M30">
-        <v>0.35</v>
-      </c>
-      <c r="N30">
-        <v>0.24</v>
-      </c>
-      <c r="O30">
-        <v>76</v>
-      </c>
-      <c r="P30">
-        <v>0.75</v>
-      </c>
-      <c r="Q30">
-        <v>110</v>
-      </c>
-      <c r="R30" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S30" s="10">
-        <v>70</v>
+      <c r="Q30" t="str">
+        <v>Smoggy</v>
+      </c>
+      <c r="R30" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="S30" s="11">
+        <v>0.19</v>
       </c>
       <c r="T30" s="10">
-        <v>245.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1">
+        <v>75</v>
+      </c>
+      <c r="U30" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="V30" s="10">
+        <v>120</v>
+      </c>
+      <c r="W30" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X30">
+        <v>50</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>242.64545454545453</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>205.14545454545453</v>
+      </c>
+      <c r="AA30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>44</v>
       </c>
@@ -2558,35 +2764,41 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="L31" t="str">
-        <v>kaajak</v>
-      </c>
-      <c r="M31">
+      <c r="Q31" t="str">
+        <v>Rarga</v>
+      </c>
+      <c r="R31" s="11">
         <v>0.35</v>
       </c>
-      <c r="N31">
-        <v>0.2</v>
-      </c>
-      <c r="O31">
-        <v>95</v>
-      </c>
-      <c r="P31">
-        <v>0.76</v>
-      </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S31" s="10">
-        <v>70</v>
+      <c r="S31" s="11">
+        <v>0.19</v>
       </c>
       <c r="T31" s="10">
-        <v>245.25454545454545</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1">
+        <v>75</v>
+      </c>
+      <c r="U31" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V31" s="10">
+        <v>120</v>
+      </c>
+      <c r="W31" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X31">
+        <v>50</v>
+      </c>
+      <c r="Y31" s="10">
+        <v>241.34545454545454</v>
+      </c>
+      <c r="Z31" s="10">
+        <v>203.84545454545454</v>
+      </c>
+      <c r="AA31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>45</v>
       </c>
@@ -2622,35 +2834,41 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="L32" t="str">
-        <v>Wo0t</v>
-      </c>
-      <c r="M32">
-        <v>0.4</v>
-      </c>
-      <c r="N32">
-        <v>0.16</v>
-      </c>
-      <c r="O32">
-        <v>78</v>
-      </c>
-      <c r="P32">
-        <v>0.75</v>
-      </c>
-      <c r="Q32">
-        <v>120</v>
-      </c>
-      <c r="R32" s="10" t="str">
+      <c r="Q32" t="str">
+        <v>ZMJKK</v>
+      </c>
+      <c r="R32" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="S32" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T32" s="10">
+        <v>65</v>
+      </c>
+      <c r="U32" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V32" s="10">
+        <v>150</v>
+      </c>
+      <c r="W32" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S32" s="10">
-        <v>75</v>
-      </c>
-      <c r="T32" s="10">
-        <v>244.24545454545452</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X32">
+        <v>90</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>234.88181818181818</v>
+      </c>
+      <c r="Z32" s="10">
+        <v>202.38181818181818</v>
+      </c>
+      <c r="AA32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>46</v>
       </c>
@@ -2686,35 +2904,41 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="L33" t="str">
-        <v>Zekken</v>
-      </c>
-      <c r="M33">
-        <v>0.35</v>
-      </c>
-      <c r="N33">
-        <v>0.25</v>
-      </c>
-      <c r="O33">
-        <v>85</v>
-      </c>
-      <c r="P33">
-        <v>0.7</v>
-      </c>
-      <c r="Q33">
-        <v>105</v>
-      </c>
-      <c r="R33" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S33" s="10">
+      <c r="Q33" t="str">
+        <v>Arlecchino</v>
+      </c>
+      <c r="R33" s="11">
+        <v>0.47</v>
+      </c>
+      <c r="S33" s="11">
+        <v>0.19</v>
+      </c>
+      <c r="T33" s="10">
+        <v>135</v>
+      </c>
+      <c r="U33" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="V33" s="10">
+        <v>125</v>
+      </c>
+      <c r="W33" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X33">
         <v>100</v>
       </c>
-      <c r="T33" s="10">
-        <v>243.22727272727272</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y33" s="10">
+        <v>269.71818181818179</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>202.21818181818179</v>
+      </c>
+      <c r="AA33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="15.75" customHeight="1">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2750,35 +2974,41 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34" t="str">
-        <v>Smoggy</v>
-      </c>
-      <c r="M34">
-        <v>0.38</v>
-      </c>
-      <c r="N34">
-        <v>0.19</v>
-      </c>
-      <c r="O34">
-        <v>75</v>
-      </c>
-      <c r="P34">
+      <c r="Q34" t="str">
+        <v>Meiy</v>
+      </c>
+      <c r="R34" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S34" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="T34" s="10">
+        <v>70</v>
+      </c>
+      <c r="U34" s="11">
         <v>0.73</v>
       </c>
-      <c r="Q34">
-        <v>120</v>
-      </c>
-      <c r="R34" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S34" s="10">
-        <v>50</v>
-      </c>
-      <c r="T34" s="10">
-        <v>242.64545454545453</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="15.75" customHeight="1">
+      <c r="V34" s="10">
+        <v>110</v>
+      </c>
+      <c r="W34" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X34">
+        <v>90</v>
+      </c>
+      <c r="Y34" s="10">
+        <v>236.8</v>
+      </c>
+      <c r="Z34" s="10">
+        <v>201.8</v>
+      </c>
+      <c r="AA34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="15.75" customHeight="1">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2814,35 +3044,41 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="L35" t="str">
-        <v>IbarakiNinja</v>
-      </c>
-      <c r="M35">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N35">
-        <v>0.16</v>
-      </c>
-      <c r="O35">
-        <v>110</v>
-      </c>
-      <c r="P35">
-        <v>0.75</v>
-      </c>
-      <c r="Q35">
-        <v>115</v>
-      </c>
-      <c r="R35" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S35" s="10">
-        <v>50</v>
+      <c r="Q35" t="str">
+        <v>mada</v>
+      </c>
+      <c r="R35" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="S35" s="11">
+        <v>0.23</v>
       </c>
       <c r="T35" s="10">
-        <v>242.37272727272727</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="15.75" customHeight="1">
+        <v>105</v>
+      </c>
+      <c r="U35" s="11">
+        <v>0.74</v>
+      </c>
+      <c r="V35" s="10">
+        <v>105</v>
+      </c>
+      <c r="W35" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X35">
+        <v>55</v>
+      </c>
+      <c r="Y35" s="10">
+        <v>253.72727272727272</v>
+      </c>
+      <c r="Z35" s="10">
+        <v>201.22727272727272</v>
+      </c>
+      <c r="AA35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="15.75" customHeight="1">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2878,35 +3114,41 @@
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="L36" t="str">
-        <v>Lar0k</v>
-      </c>
-      <c r="M36">
-        <v>0.34</v>
-      </c>
-      <c r="N36">
-        <v>0.18</v>
-      </c>
-      <c r="O36">
-        <v>85</v>
-      </c>
-      <c r="P36">
+      <c r="Q36" t="str">
+        <v>Sato</v>
+      </c>
+      <c r="R36" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="S36" s="11">
+        <v>0.19</v>
+      </c>
+      <c r="T36" s="10">
+        <v>67</v>
+      </c>
+      <c r="U36" s="11">
         <v>0.73</v>
       </c>
-      <c r="Q36">
-        <v>123</v>
-      </c>
-      <c r="R36" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S36" s="10">
-        <v>50</v>
-      </c>
-      <c r="T36" s="10">
-        <v>242.1090909090909</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15.75" customHeight="1">
+      <c r="V36" s="10">
+        <v>105</v>
+      </c>
+      <c r="W36" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X36">
+        <v>60</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>234.42727272727271</v>
+      </c>
+      <c r="Z36" s="10">
+        <v>200.92727272727271</v>
+      </c>
+      <c r="AA36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="15.75" customHeight="1">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2942,35 +3184,41 @@
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="L37" t="str">
-        <v>Kachina</v>
-      </c>
-      <c r="M37">
-        <v>0.45</v>
-      </c>
-      <c r="N37">
-        <v>0.2</v>
-      </c>
-      <c r="O37">
-        <v>60</v>
-      </c>
-      <c r="P37">
-        <v>0.8</v>
-      </c>
-      <c r="Q37">
-        <v>90</v>
-      </c>
-      <c r="R37" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S37" s="10">
-        <v>40</v>
+      <c r="Q37" t="str">
+        <v>Zekken</v>
+      </c>
+      <c r="R37" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S37" s="11">
+        <v>0.25</v>
       </c>
       <c r="T37" s="10">
-        <v>241.40909090909091</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="15.75" customHeight="1">
+        <v>85</v>
+      </c>
+      <c r="U37" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V37" s="10">
+        <v>105</v>
+      </c>
+      <c r="W37" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X37">
+        <v>100</v>
+      </c>
+      <c r="Y37" s="10">
+        <v>243.22727272727272</v>
+      </c>
+      <c r="Z37" s="10">
+        <v>200.72727272727272</v>
+      </c>
+      <c r="AA37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="15.75" customHeight="1">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3006,35 +3254,41 @@
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="L38" t="str">
-        <v>Rarga</v>
-      </c>
-      <c r="M38">
+      <c r="Q38" t="str">
+        <v>Less</v>
+      </c>
+      <c r="R38" s="11">
         <v>0.35</v>
       </c>
-      <c r="N38">
-        <v>0.19</v>
-      </c>
-      <c r="O38">
-        <v>75</v>
-      </c>
-      <c r="P38">
-        <v>0.75</v>
-      </c>
-      <c r="Q38">
-        <v>120</v>
-      </c>
-      <c r="R38" s="10" t="str">
+      <c r="S38" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="T38" s="10">
+        <v>86</v>
+      </c>
+      <c r="U38" s="11">
+        <v>0.74</v>
+      </c>
+      <c r="V38" s="10">
+        <v>104</v>
+      </c>
+      <c r="W38" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S38" s="10">
-        <v>50</v>
-      </c>
-      <c r="T38" s="10">
-        <v>241.34545454545454</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X38">
+        <v>80</v>
+      </c>
+      <c r="Y38" s="10">
+        <v>243.37272727272727</v>
+      </c>
+      <c r="Z38" s="10">
+        <v>200.37272727272727</v>
+      </c>
+      <c r="AA38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="15.75" customHeight="1">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -3070,35 +3324,41 @@
       <c r="K39">
         <v>1</v>
       </c>
-      <c r="L39" t="str">
-        <v>nAts</v>
-      </c>
-      <c r="M39">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N39">
+      <c r="Q39" t="str">
+        <v>Lar0k</v>
+      </c>
+      <c r="R39" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="S39" s="11">
         <v>0.18</v>
       </c>
-      <c r="O39">
-        <v>125</v>
-      </c>
-      <c r="P39">
-        <v>0.71</v>
-      </c>
-      <c r="Q39">
-        <v>88</v>
-      </c>
-      <c r="R39" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S39" s="10">
+      <c r="T39" s="10">
+        <v>85</v>
+      </c>
+      <c r="U39" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="V39" s="10">
+        <v>123</v>
+      </c>
+      <c r="W39" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X39">
         <v>50</v>
       </c>
-      <c r="T39" s="10">
-        <v>237.10000000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y39" s="10">
+        <v>242.1090909090909</v>
+      </c>
+      <c r="Z39" s="10">
+        <v>199.6090909090909</v>
+      </c>
+      <c r="AA39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="15.75" customHeight="1">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -3134,35 +3394,41 @@
       <c r="K40">
         <v>1</v>
       </c>
-      <c r="L40" t="str">
-        <v>Meiy</v>
-      </c>
-      <c r="M40">
+      <c r="Q40" t="str">
+        <v>kaajak</v>
+      </c>
+      <c r="R40" s="11">
         <v>0.35</v>
       </c>
-      <c r="N40">
-        <v>0.22</v>
-      </c>
-      <c r="O40">
+      <c r="S40" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="T40" s="10">
+        <v>95</v>
+      </c>
+      <c r="U40" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="V40" s="10">
+        <v>100</v>
+      </c>
+      <c r="W40" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X40">
         <v>70</v>
       </c>
-      <c r="P40">
-        <v>0.73</v>
-      </c>
-      <c r="Q40">
-        <v>110</v>
-      </c>
-      <c r="R40" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S40" s="10">
-        <v>90</v>
-      </c>
-      <c r="T40" s="10">
-        <v>236.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y40" s="10">
+        <v>245.25454545454545</v>
+      </c>
+      <c r="Z40" s="10">
+        <v>197.75454545454545</v>
+      </c>
+      <c r="AA40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="15.75" customHeight="1">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -3198,35 +3464,41 @@
       <c r="K41">
         <v>1</v>
       </c>
-      <c r="L41" t="str">
-        <v>Lysoar</v>
-      </c>
-      <c r="M41">
-        <v>0.33</v>
-      </c>
-      <c r="N41">
-        <v>0.17</v>
-      </c>
-      <c r="O41">
-        <v>105</v>
-      </c>
-      <c r="P41">
-        <v>0.71</v>
-      </c>
-      <c r="Q41">
-        <v>100</v>
-      </c>
-      <c r="R41" s="10" t="str">
+      <c r="Q41" t="str">
+        <v>s0m</v>
+      </c>
+      <c r="R41" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="S41" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="T41" s="10">
+        <v>145</v>
+      </c>
+      <c r="U41" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V41" s="10">
+        <v>116</v>
+      </c>
+      <c r="W41" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S41" s="10">
-        <v>50</v>
-      </c>
-      <c r="T41" s="10">
-        <v>236.05454545454546</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X41">
+        <v>55</v>
+      </c>
+      <c r="Y41" s="10">
+        <v>268.32727272727266</v>
+      </c>
+      <c r="Z41" s="10">
+        <v>195.82727272727269</v>
+      </c>
+      <c r="AA41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="15.75" customHeight="1">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -3262,35 +3534,41 @@
       <c r="K42">
         <v>1</v>
       </c>
-      <c r="L42" t="str">
-        <v>ZMJKK</v>
-      </c>
-      <c r="M42">
-        <v>0.3</v>
-      </c>
-      <c r="N42">
+      <c r="Q42" t="str">
+        <v>Asuna</v>
+      </c>
+      <c r="R42" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S42" s="11">
         <v>0.17</v>
       </c>
-      <c r="O42">
+      <c r="T42" s="10">
+        <v>85</v>
+      </c>
+      <c r="U42" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V42" s="10">
+        <v>125</v>
+      </c>
+      <c r="W42" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X42">
         <v>65</v>
       </c>
-      <c r="P42">
-        <v>0.71</v>
-      </c>
-      <c r="Q42">
-        <v>150</v>
-      </c>
-      <c r="R42" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S42" s="10">
-        <v>90</v>
-      </c>
-      <c r="T42" s="10">
-        <v>234.88181818181818</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y42" s="10">
+        <v>237.41818181818181</v>
+      </c>
+      <c r="Z42" s="10">
+        <v>194.91818181818181</v>
+      </c>
+      <c r="AA42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" ht="15.75" customHeight="1">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -3326,35 +3604,41 @@
       <c r="K43">
         <v>1</v>
       </c>
-      <c r="L43" t="str">
-        <v>Mazino</v>
-      </c>
-      <c r="M43">
+      <c r="Q43" t="str">
+        <v>Dep</v>
+      </c>
+      <c r="R43" s="11">
         <v>0.33</v>
       </c>
-      <c r="N43">
-        <v>0.18</v>
-      </c>
-      <c r="O43">
+      <c r="S43" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="T43" s="10">
+        <v>75</v>
+      </c>
+      <c r="U43" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="V43" s="10">
         <v>100</v>
       </c>
-      <c r="P43">
-        <v>0.73</v>
-      </c>
-      <c r="Q43">
-        <v>93</v>
-      </c>
-      <c r="R43" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S43" s="10">
-        <v>60</v>
-      </c>
-      <c r="T43" s="10">
-        <v>234.67272727272729</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="15.75" customHeight="1">
+      <c r="W43" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X43">
+        <v>50</v>
+      </c>
+      <c r="Y43" s="10">
+        <v>232.15454545454543</v>
+      </c>
+      <c r="Z43" s="10">
+        <v>194.65454545454543</v>
+      </c>
+      <c r="AA43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="15.75" customHeight="1">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -3390,35 +3674,41 @@
       <c r="K44">
         <v>1</v>
       </c>
-      <c r="L44" t="str">
-        <v>trent</v>
-      </c>
-      <c r="M44">
-        <v>0.3</v>
-      </c>
-      <c r="N44">
-        <v>0.18</v>
-      </c>
-      <c r="O44">
-        <v>120</v>
-      </c>
-      <c r="P44">
-        <v>0.71</v>
-      </c>
-      <c r="Q44">
-        <v>85</v>
-      </c>
-      <c r="R44" s="10" t="str">
+      <c r="Q44" t="str">
+        <v>WsLeo</v>
+      </c>
+      <c r="R44" s="11">
+        <v>0.36</v>
+      </c>
+      <c r="S44" s="11">
+        <v>0.21</v>
+      </c>
+      <c r="T44" s="10">
+        <v>130</v>
+      </c>
+      <c r="U44" s="11">
+        <v>0.78</v>
+      </c>
+      <c r="V44" s="10">
+        <v>80</v>
+      </c>
+      <c r="W44" t="str">
         <v>シーカー</v>
       </c>
-      <c r="S44" s="10">
-        <v>40</v>
-      </c>
-      <c r="T44" s="10">
-        <v>234.5363636363636</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X44">
+        <v>50</v>
+      </c>
+      <c r="Y44" s="10">
+        <v>259.26363636363635</v>
+      </c>
+      <c r="Z44" s="10">
+        <v>194.26363636363635</v>
+      </c>
+      <c r="AA44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" ht="15.75" customHeight="1">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -3454,35 +3744,41 @@
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="L45" t="str">
-        <v>Sato</v>
-      </c>
-      <c r="M45">
+      <c r="Q45" t="str">
+        <v>BABYBAY</v>
+      </c>
+      <c r="R45" s="11">
         <v>0.4</v>
       </c>
-      <c r="N45">
-        <v>0.19</v>
-      </c>
-      <c r="O45">
-        <v>67</v>
-      </c>
-      <c r="P45">
+      <c r="S45" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="T45" s="10">
+        <v>85</v>
+      </c>
+      <c r="U45" s="11">
         <v>0.73</v>
       </c>
-      <c r="Q45">
-        <v>105</v>
-      </c>
-      <c r="R45" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S45" s="10">
-        <v>60</v>
-      </c>
-      <c r="T45" s="10">
-        <v>234.42727272727271</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="15.75" customHeight="1">
+      <c r="V45" s="10">
+        <v>100</v>
+      </c>
+      <c r="W45" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X45">
+        <v>55</v>
+      </c>
+      <c r="Y45" s="10">
+        <v>234.35454545454547</v>
+      </c>
+      <c r="Z45" s="10">
+        <v>191.85454545454547</v>
+      </c>
+      <c r="AA45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" ht="15.75" customHeight="1">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -3518,35 +3814,41 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="L46" t="str">
-        <v>BABYBAY</v>
-      </c>
-      <c r="M46">
-        <v>0.4</v>
-      </c>
-      <c r="N46">
-        <v>0.15</v>
-      </c>
-      <c r="O46">
-        <v>85</v>
-      </c>
-      <c r="P46">
-        <v>0.73</v>
-      </c>
-      <c r="Q46">
+      <c r="Q46" t="str">
+        <v>Buzz</v>
+      </c>
+      <c r="R46" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="S46" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="T46" s="10">
+        <v>80</v>
+      </c>
+      <c r="U46" s="11">
+        <v>0.72</v>
+      </c>
+      <c r="V46" s="10">
         <v>100</v>
       </c>
-      <c r="R46" s="10" t="str">
+      <c r="W46" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S46" s="10">
-        <v>55</v>
-      </c>
-      <c r="T46" s="10">
-        <v>234.35454545454547</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X46">
+        <v>60</v>
+      </c>
+      <c r="Y46" s="10">
+        <v>231.15454545454543</v>
+      </c>
+      <c r="Z46" s="10">
+        <v>191.15454545454543</v>
+      </c>
+      <c r="AA46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" ht="15.75" customHeight="1">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -3582,35 +3884,41 @@
       <c r="K47">
         <v>1</v>
       </c>
-      <c r="L47" t="str">
-        <v>crashies</v>
-      </c>
-      <c r="M47">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N47">
-        <v>0.17</v>
-      </c>
-      <c r="O47">
-        <v>140</v>
-      </c>
-      <c r="P47">
-        <v>0.68</v>
-      </c>
-      <c r="Q47">
-        <v>80</v>
-      </c>
-      <c r="R47" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S47" s="10">
-        <v>45</v>
+      <c r="Q47" t="str">
+        <v>Cryocells</v>
+      </c>
+      <c r="R47" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S47" s="11">
+        <v>0.18</v>
       </c>
       <c r="T47" s="10">
-        <v>234.06363636363636</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="15.75" customHeight="1">
+        <v>85</v>
+      </c>
+      <c r="U47" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="V47" s="10">
+        <v>110</v>
+      </c>
+      <c r="W47" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X47">
+        <v>65</v>
+      </c>
+      <c r="Y47" s="10">
+        <v>233.60000000000002</v>
+      </c>
+      <c r="Z47" s="10">
+        <v>191.10000000000002</v>
+      </c>
+      <c r="AA47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" ht="15.75" customHeight="1">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -3646,35 +3954,41 @@
       <c r="K48">
         <v>1</v>
       </c>
-      <c r="L48" t="str">
-        <v>Dep</v>
-      </c>
-      <c r="M48">
-        <v>0.33</v>
-      </c>
-      <c r="N48">
-        <v>0.22</v>
-      </c>
-      <c r="O48">
-        <v>75</v>
-      </c>
-      <c r="P48">
-        <v>0.73</v>
-      </c>
-      <c r="Q48">
-        <v>100</v>
-      </c>
-      <c r="R48" s="10" t="str">
+      <c r="Q48" t="str">
+        <v>Jinggg</v>
+      </c>
+      <c r="R48" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="S48" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="T48" s="10">
+        <v>68</v>
+      </c>
+      <c r="U48" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V48" s="10">
+        <v>90</v>
+      </c>
+      <c r="W48" t="str">
         <v>タイガー</v>
       </c>
-      <c r="S48" s="10">
+      <c r="X48">
         <v>50</v>
       </c>
-      <c r="T48" s="10">
-        <v>232.15454545454543</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y48" s="10">
+        <v>224.40909090909091</v>
+      </c>
+      <c r="Z48" s="10">
+        <v>190.40909090909091</v>
+      </c>
+      <c r="AA48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" ht="15.75" customHeight="1">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -3710,40 +4024,46 @@
       <c r="K49">
         <v>1</v>
       </c>
-      <c r="L49" t="str">
-        <v>Buzz</v>
-      </c>
-      <c r="M49">
+      <c r="Q49" t="str">
+        <v>Ethan</v>
+      </c>
+      <c r="R49" s="11">
         <v>0.3</v>
       </c>
-      <c r="N49">
-        <v>0.23</v>
-      </c>
-      <c r="O49">
-        <v>80</v>
-      </c>
-      <c r="P49">
-        <v>0.72</v>
-      </c>
-      <c r="Q49">
-        <v>100</v>
-      </c>
-      <c r="R49" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S49" s="10">
-        <v>60</v>
+      <c r="S49" s="11">
+        <v>0.18</v>
       </c>
       <c r="T49" s="10">
-        <v>231.15454545454543</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" ht="15.75" customHeight="1">
+        <v>150</v>
+      </c>
+      <c r="U49" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="V49" s="10">
+        <v>90</v>
+      </c>
+      <c r="W49" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X49">
+        <v>55</v>
+      </c>
+      <c r="Y49" s="10">
+        <v>263.5090909090909</v>
+      </c>
+      <c r="Z49" s="10">
+        <v>188.50909090909093</v>
+      </c>
+      <c r="AA49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B50" s="5">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="C50" s="5">
         <v>0.18</v>
@@ -3765,44 +4085,50 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" si="0"/>
-        <v>224.5545454545454</v>
+        <v>225.85454545454542</v>
       </c>
       <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v>180.0545454545454</v>
+        <v>181.35454545454542</v>
       </c>
       <c r="K50">
         <v>1</v>
       </c>
-      <c r="L50" t="str">
-        <v>C0M</v>
-      </c>
-      <c r="M50">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N50">
-        <v>0.16</v>
-      </c>
-      <c r="O50">
-        <v>120</v>
-      </c>
-      <c r="P50">
-        <v>0.69</v>
-      </c>
-      <c r="Q50">
-        <v>95</v>
-      </c>
-      <c r="R50" s="10" t="str">
+      <c r="Q50" t="str">
+        <v>d4v41</v>
+      </c>
+      <c r="R50" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S50" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T50" s="10">
+        <v>70</v>
+      </c>
+      <c r="U50" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V50" s="10">
+        <v>105</v>
+      </c>
+      <c r="W50" t="str">
         <v>シーカー</v>
       </c>
-      <c r="S50" s="10">
-        <v>60</v>
-      </c>
-      <c r="T50" s="10">
-        <v>230.4818181818182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X50">
+        <v>40</v>
+      </c>
+      <c r="Y50" s="10">
+        <v>223.42727272727271</v>
+      </c>
+      <c r="Z50" s="10">
+        <v>188.42727272727271</v>
+      </c>
+      <c r="AA50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="s">
         <v>64</v>
       </c>
@@ -3838,35 +4164,41 @@
       <c r="K51">
         <v>1</v>
       </c>
-      <c r="L51" t="str">
-        <v>tex</v>
-      </c>
-      <c r="M51">
-        <v>0.34</v>
-      </c>
-      <c r="N51">
+      <c r="Q51" t="str">
+        <v>CHICHOO</v>
+      </c>
+      <c r="R51" s="11">
+        <v>0.32</v>
+      </c>
+      <c r="S51" s="11">
         <v>0.18</v>
       </c>
-      <c r="O51">
-        <v>85</v>
-      </c>
-      <c r="P51">
-        <v>0.73</v>
-      </c>
-      <c r="Q51">
-        <v>95</v>
-      </c>
-      <c r="R51" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S51" s="10">
-        <v>60</v>
-      </c>
       <c r="T51" s="10">
-        <v>229.38181818181818</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" ht="15.75" customHeight="1">
+        <v>80</v>
+      </c>
+      <c r="U51" s="11">
+        <v>0.74</v>
+      </c>
+      <c r="V51" s="10">
+        <v>100</v>
+      </c>
+      <c r="W51" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X51">
+        <v>50</v>
+      </c>
+      <c r="Y51" s="10">
+        <v>227.85454545454547</v>
+      </c>
+      <c r="Z51" s="10">
+        <v>187.85454545454547</v>
+      </c>
+      <c r="AA51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="s">
         <v>65</v>
       </c>
@@ -3902,35 +4234,41 @@
       <c r="K52">
         <v>1</v>
       </c>
-      <c r="L52" t="str">
-        <v>leaf</v>
-      </c>
-      <c r="M52">
-        <v>0.38</v>
-      </c>
-      <c r="N52">
-        <v>0.17</v>
-      </c>
-      <c r="O52">
-        <v>89</v>
-      </c>
-      <c r="P52">
-        <v>0.74</v>
-      </c>
-      <c r="Q52">
-        <v>80</v>
-      </c>
-      <c r="R52" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S52" s="10">
-        <v>40</v>
+      <c r="Q52" t="str">
+        <v>IbarakiNinja</v>
+      </c>
+      <c r="R52" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S52" s="11">
+        <v>0.16</v>
       </c>
       <c r="T52" s="10">
-        <v>229.36363636363637</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" ht="15.75" customHeight="1">
+        <v>110</v>
+      </c>
+      <c r="U52" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V52" s="10">
+        <v>115</v>
+      </c>
+      <c r="W52" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X52">
+        <v>50</v>
+      </c>
+      <c r="Y52" s="10">
+        <v>242.37272727272727</v>
+      </c>
+      <c r="Z52" s="10">
+        <v>187.37272727272727</v>
+      </c>
+      <c r="AA52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
         <v>66</v>
       </c>
@@ -3966,35 +4304,41 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="L53" t="str">
-        <v>Rb</v>
-      </c>
-      <c r="M53">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N53">
-        <v>0.23</v>
-      </c>
-      <c r="O53">
-        <v>110</v>
-      </c>
-      <c r="P53">
-        <v>0.67</v>
-      </c>
-      <c r="Q53">
-        <v>80</v>
-      </c>
-      <c r="R53" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S53" s="10">
-        <v>40</v>
+      <c r="Q53" t="str">
+        <v>tex</v>
+      </c>
+      <c r="R53" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="S53" s="11">
+        <v>0.18</v>
       </c>
       <c r="T53" s="10">
-        <v>229.26363636363635</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="15.75" customHeight="1">
+        <v>85</v>
+      </c>
+      <c r="U53" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="V53" s="10">
+        <v>95</v>
+      </c>
+      <c r="W53" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X53">
+        <v>60</v>
+      </c>
+      <c r="Y53" s="10">
+        <v>229.38181818181818</v>
+      </c>
+      <c r="Z53" s="10">
+        <v>186.88181818181818</v>
+      </c>
+      <c r="AA53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="s">
         <v>67</v>
       </c>
@@ -4030,35 +4374,41 @@
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="L54" t="str">
-        <v>SugarZ3ro</v>
-      </c>
-      <c r="M54">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N54">
-        <v>0.18</v>
-      </c>
-      <c r="O54">
-        <v>120</v>
-      </c>
-      <c r="P54">
-        <v>0.65</v>
-      </c>
-      <c r="Q54">
-        <v>93</v>
-      </c>
-      <c r="R54" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S54" s="10">
-        <v>40</v>
+      <c r="Q54" t="str">
+        <v>Laz</v>
+      </c>
+      <c r="R54" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="S54" s="11">
+        <v>0.14000000000000001</v>
       </c>
       <c r="T54" s="10">
-        <v>229.07272727272726</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" ht="15.75" customHeight="1">
+        <v>70</v>
+      </c>
+      <c r="U54" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V54" s="10">
+        <v>86</v>
+      </c>
+      <c r="W54" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X54">
+        <v>80</v>
+      </c>
+      <c r="Y54" s="10">
+        <v>221.3909090909091</v>
+      </c>
+      <c r="Z54" s="10">
+        <v>186.3909090909091</v>
+      </c>
+      <c r="AA54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="15.75" customHeight="1">
       <c r="A55" s="5" t="s">
         <v>68</v>
       </c>
@@ -4094,40 +4444,46 @@
       <c r="K55">
         <v>1</v>
       </c>
-      <c r="L55" t="str">
-        <v>eggsterr</v>
-      </c>
-      <c r="M55">
-        <v>0.3</v>
-      </c>
-      <c r="N55">
-        <v>0.22</v>
-      </c>
-      <c r="O55">
-        <v>88</v>
-      </c>
-      <c r="P55">
-        <v>0.7</v>
-      </c>
-      <c r="Q55">
-        <v>95</v>
-      </c>
-      <c r="R55" s="10" t="str">
+      <c r="Q55" t="str">
+        <v>leaf</v>
+      </c>
+      <c r="R55" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="S55" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T55" s="10">
+        <v>89</v>
+      </c>
+      <c r="U55" s="11">
+        <v>0.74</v>
+      </c>
+      <c r="V55" s="10">
+        <v>80</v>
+      </c>
+      <c r="W55" t="str">
         <v>フラッシュ</v>
       </c>
-      <c r="S55" s="10">
-        <v>50</v>
-      </c>
-      <c r="T55" s="10">
-        <v>228.58181818181816</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X55">
+        <v>40</v>
+      </c>
+      <c r="Y55" s="10">
+        <v>229.36363636363637</v>
+      </c>
+      <c r="Z55" s="10">
+        <v>184.86363636363637</v>
+      </c>
+      <c r="AA55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B56" s="5">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="C56" s="3">
         <v>0.13</v>
@@ -4149,44 +4505,50 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" si="0"/>
-        <v>214.31818181818181</v>
+        <v>216.91818181818181</v>
       </c>
       <c r="J56" s="10">
         <f t="shared" si="1"/>
-        <v>129.31818181818181</v>
+        <v>131.91818181818181</v>
       </c>
       <c r="K56">
         <v>1</v>
       </c>
-      <c r="L56" t="str">
-        <v>skuba</v>
-      </c>
-      <c r="M56">
-        <v>0.31</v>
-      </c>
-      <c r="N56">
-        <v>0.17</v>
-      </c>
-      <c r="O56">
-        <v>95</v>
-      </c>
-      <c r="P56">
-        <v>0.71</v>
-      </c>
-      <c r="Q56">
+      <c r="Q56" t="str">
+        <v>Mazino</v>
+      </c>
+      <c r="R56" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="S56" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="T56" s="10">
         <v>100</v>
       </c>
-      <c r="R56" s="10" t="str">
+      <c r="U56" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="V56" s="10">
+        <v>93</v>
+      </c>
+      <c r="W56" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S56" s="10">
-        <v>50</v>
-      </c>
-      <c r="T56" s="10">
-        <v>228.45454545454544</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X56">
+        <v>60</v>
+      </c>
+      <c r="Y56" s="10">
+        <v>234.67272727272729</v>
+      </c>
+      <c r="Z56" s="10">
+        <v>184.67272727272729</v>
+      </c>
+      <c r="AA56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" ht="15.75" customHeight="1">
       <c r="A57" s="5" t="s">
         <v>70</v>
       </c>
@@ -4222,35 +4584,41 @@
       <c r="K57">
         <v>1</v>
       </c>
-      <c r="L57" t="str">
-        <v>CHICHOO</v>
-      </c>
-      <c r="M57">
-        <v>0.32</v>
-      </c>
-      <c r="N57">
-        <v>0.18</v>
-      </c>
-      <c r="O57">
-        <v>80</v>
-      </c>
-      <c r="P57">
-        <v>0.74</v>
-      </c>
-      <c r="Q57">
-        <v>100</v>
-      </c>
-      <c r="R57" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S57" s="10">
+      <c r="Q57" t="str">
+        <v>eggsterr</v>
+      </c>
+      <c r="R57" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="S57" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="T57" s="10">
+        <v>88</v>
+      </c>
+      <c r="U57" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V57" s="10">
+        <v>95</v>
+      </c>
+      <c r="W57" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X57">
         <v>50</v>
       </c>
-      <c r="T57" s="10">
-        <v>227.85454545454547</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y57" s="10">
+        <v>228.58181818181816</v>
+      </c>
+      <c r="Z57" s="10">
+        <v>184.58181818181816</v>
+      </c>
+      <c r="AA57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
         <v>71</v>
       </c>
@@ -4286,35 +4654,41 @@
       <c r="K58">
         <v>1</v>
       </c>
-      <c r="L58" t="str">
-        <v>Mako</v>
-      </c>
-      <c r="M58">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N58">
-        <v>0.16</v>
-      </c>
-      <c r="O58">
-        <v>120</v>
-      </c>
-      <c r="P58">
-        <v>0.7</v>
-      </c>
-      <c r="Q58">
-        <v>85</v>
-      </c>
-      <c r="R58" s="10" t="str">
+      <c r="Q58" t="str">
+        <v>Lysoar</v>
+      </c>
+      <c r="R58" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="S58" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T58" s="10">
+        <v>105</v>
+      </c>
+      <c r="U58" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V58" s="10">
+        <v>100</v>
+      </c>
+      <c r="W58" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S58" s="10">
+      <c r="X58">
         <v>50</v>
       </c>
-      <c r="T58" s="10">
-        <v>227.23636363636362</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y58" s="10">
+        <v>236.05454545454546</v>
+      </c>
+      <c r="Z58" s="10">
+        <v>183.55454545454546</v>
+      </c>
+      <c r="AA58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="s">
         <v>72</v>
       </c>
@@ -4350,35 +4724,41 @@
       <c r="K59">
         <v>1</v>
       </c>
-      <c r="L59" t="str">
-        <v>Boaster</v>
-      </c>
-      <c r="M59">
-        <v>0.2</v>
-      </c>
-      <c r="N59">
-        <v>0.12</v>
-      </c>
-      <c r="O59">
-        <v>165</v>
-      </c>
-      <c r="P59">
-        <v>0.62</v>
-      </c>
-      <c r="Q59">
-        <v>96</v>
-      </c>
-      <c r="R59" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S59" s="10">
+      <c r="Q59" t="str">
+        <v>Rossy</v>
+      </c>
+      <c r="R59" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="S59" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="T59" s="10">
+        <v>89</v>
+      </c>
+      <c r="U59" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V59" s="10">
+        <v>100</v>
+      </c>
+      <c r="W59" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X59">
         <v>50</v>
       </c>
-      <c r="T59" s="10">
-        <v>227.13636363636363</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y59" s="10">
+        <v>225.85454545454542</v>
+      </c>
+      <c r="Z59" s="10">
+        <v>181.35454545454542</v>
+      </c>
+      <c r="AA59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="s">
         <v>73</v>
       </c>
@@ -4414,35 +4794,41 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="L60" t="str">
-        <v>F0rsakeN</v>
-      </c>
-      <c r="M60">
-        <v>0.26</v>
-      </c>
-      <c r="N60">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="O60">
-        <v>125</v>
-      </c>
-      <c r="P60">
-        <v>0.69</v>
-      </c>
-      <c r="Q60">
-        <v>95</v>
-      </c>
-      <c r="R60" s="10" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="S60" s="10">
-        <v>50</v>
+      <c r="Q60" t="str">
+        <v>Sayonara</v>
+      </c>
+      <c r="R60" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="S60" s="11">
+        <v>0.19</v>
       </c>
       <c r="T60" s="10">
-        <v>226.9818181818182</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" ht="15.75" customHeight="1">
+        <v>89</v>
+      </c>
+      <c r="U60" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V60" s="10">
+        <v>90</v>
+      </c>
+      <c r="W60" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X60">
+        <v>80</v>
+      </c>
+      <c r="Y60" s="10">
+        <v>225.6090909090909</v>
+      </c>
+      <c r="Z60" s="10">
+        <v>181.1090909090909</v>
+      </c>
+      <c r="AA60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
         <v>74</v>
       </c>
@@ -4478,35 +4864,41 @@
       <c r="K61">
         <v>1</v>
       </c>
-      <c r="L61" t="str">
-        <v>Boostio</v>
-      </c>
-      <c r="M61">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N61">
-        <v>0.15</v>
-      </c>
-      <c r="O61">
-        <v>128</v>
-      </c>
-      <c r="P61">
-        <v>0.68</v>
-      </c>
-      <c r="Q61">
-        <v>85</v>
-      </c>
-      <c r="R61" s="10" t="str">
+      <c r="Q61" t="str">
+        <v>keiko</v>
+      </c>
+      <c r="R61" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="S61" s="11">
+        <v>0.19</v>
+      </c>
+      <c r="T61" s="10">
+        <v>89</v>
+      </c>
+      <c r="U61" s="11">
+        <v>0.72</v>
+      </c>
+      <c r="V61" s="10">
+        <v>90</v>
+      </c>
+      <c r="W61" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S61" s="10">
+      <c r="X61">
         <v>70</v>
       </c>
-      <c r="T61" s="10">
-        <v>226.93636363636364</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y61" s="10">
+        <v>225.6090909090909</v>
+      </c>
+      <c r="Z61" s="10">
+        <v>181.1090909090909</v>
+      </c>
+      <c r="AA61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="s">
         <v>75</v>
       </c>
@@ -4542,35 +4934,41 @@
       <c r="K62">
         <v>1</v>
       </c>
-      <c r="L62" t="str">
-        <v>valyn</v>
-      </c>
-      <c r="M62">
-        <v>0.26</v>
-      </c>
-      <c r="N62">
-        <v>0.13</v>
-      </c>
-      <c r="O62">
-        <v>140</v>
-      </c>
-      <c r="P62">
-        <v>0.64</v>
-      </c>
-      <c r="Q62">
+      <c r="Q62" t="str">
+        <v>skuba</v>
+      </c>
+      <c r="R62" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="S62" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T62" s="10">
         <v>95</v>
       </c>
-      <c r="R62" s="10" t="str">
+      <c r="U62" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V62" s="10">
+        <v>100</v>
+      </c>
+      <c r="W62" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S62" s="10">
-        <v>40</v>
-      </c>
-      <c r="T62" s="10">
-        <v>226.28181818181821</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X62">
+        <v>50</v>
+      </c>
+      <c r="Y62" s="10">
+        <v>228.45454545454544</v>
+      </c>
+      <c r="Z62" s="10">
+        <v>180.95454545454544</v>
+      </c>
+      <c r="AA62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
         <v>76</v>
       </c>
@@ -4606,35 +5004,41 @@
       <c r="K63">
         <v>1</v>
       </c>
-      <c r="L63" t="str">
-        <v>stax</v>
-      </c>
-      <c r="M63">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N63">
-        <v>0.15</v>
-      </c>
-      <c r="O63">
-        <v>130</v>
-      </c>
-      <c r="P63">
-        <v>0.67</v>
-      </c>
-      <c r="Q63">
+      <c r="Q63" t="str">
+        <v>Verno</v>
+      </c>
+      <c r="R63" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="S63" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="T63" s="10">
+        <v>86</v>
+      </c>
+      <c r="U63" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V63" s="10">
+        <v>95</v>
+      </c>
+      <c r="W63" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X63">
         <v>80</v>
       </c>
-      <c r="R63" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S63" s="10">
-        <v>70</v>
-      </c>
-      <c r="T63" s="10">
-        <v>225.66363636363633</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y63" s="10">
+        <v>223.88181818181818</v>
+      </c>
+      <c r="Z63" s="10">
+        <v>180.88181818181818</v>
+      </c>
+      <c r="AA63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="s">
         <v>77</v>
       </c>
@@ -4642,7 +5046,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="C64" s="5">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="D64" s="5">
         <v>149</v>
@@ -4657,48 +5061,54 @@
         <v>12</v>
       </c>
       <c r="H64" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" si="0"/>
-        <v>266.83636363636361</v>
+        <v>249.83636363636361</v>
       </c>
       <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v>192.33636363636361</v>
+        <v>175.33636363636361</v>
       </c>
       <c r="K64">
         <v>1</v>
       </c>
-      <c r="L64" t="str">
-        <v>Sayonara</v>
-      </c>
-      <c r="M64">
-        <v>0.33</v>
-      </c>
-      <c r="N64">
-        <v>0.19</v>
-      </c>
-      <c r="O64">
-        <v>89</v>
-      </c>
-      <c r="P64">
-        <v>0.7</v>
-      </c>
-      <c r="Q64">
-        <v>90</v>
-      </c>
-      <c r="R64" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S64" s="10">
-        <v>80</v>
+      <c r="Q64" t="str">
+        <v>Furina</v>
+      </c>
+      <c r="R64" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S64" s="11">
+        <v>0.09</v>
       </c>
       <c r="T64" s="10">
-        <v>225.6090909090909</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" ht="15.75" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="U64" s="11">
+        <v>0.69</v>
+      </c>
+      <c r="V64" s="10">
+        <v>129</v>
+      </c>
+      <c r="W64" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X64">
+        <v>20</v>
+      </c>
+      <c r="Y64" s="10">
+        <v>249.83636363636361</v>
+      </c>
+      <c r="Z64" s="10">
+        <v>175.33636363636361</v>
+      </c>
+      <c r="AA64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="s">
         <v>78</v>
       </c>
@@ -4721,7 +5131,7 @@
         <v>14</v>
       </c>
       <c r="H65" s="4">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I65" s="4">
         <f t="shared" si="0"/>
@@ -4734,35 +5144,41 @@
       <c r="K65">
         <v>1</v>
       </c>
-      <c r="L65" t="str">
-        <v>keiko</v>
-      </c>
-      <c r="M65">
-        <v>0.31</v>
-      </c>
-      <c r="N65">
-        <v>0.19</v>
-      </c>
-      <c r="O65">
-        <v>89</v>
-      </c>
-      <c r="P65">
-        <v>0.72</v>
-      </c>
-      <c r="Q65">
-        <v>90</v>
-      </c>
-      <c r="R65" s="10" t="str">
+      <c r="Q65" t="str">
+        <v>nAts</v>
+      </c>
+      <c r="R65" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S65" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="T65" s="10">
+        <v>125</v>
+      </c>
+      <c r="U65" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V65" s="10">
+        <v>88</v>
+      </c>
+      <c r="W65" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S65" s="10">
-        <v>70</v>
-      </c>
-      <c r="T65" s="10">
-        <v>225.6090909090909</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X65">
+        <v>50</v>
+      </c>
+      <c r="Y65" s="10">
+        <v>237.10000000000002</v>
+      </c>
+      <c r="Z65" s="10">
+        <v>174.6</v>
+      </c>
+      <c r="AA65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="s">
         <v>79</v>
       </c>
@@ -4785,7 +5201,7 @@
         <v>18</v>
       </c>
       <c r="H66" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I66" s="4">
         <f t="shared" si="0"/>
@@ -4798,35 +5214,41 @@
       <c r="K66">
         <v>1</v>
       </c>
-      <c r="L66" t="str">
-        <v>Rossy</v>
-      </c>
-      <c r="M66">
+      <c r="Q66" t="str">
+        <v>trent</v>
+      </c>
+      <c r="R66" s="11">
         <v>0.3</v>
       </c>
-      <c r="N66">
+      <c r="S66" s="11">
         <v>0.18</v>
       </c>
-      <c r="O66">
-        <v>89</v>
-      </c>
-      <c r="P66">
-        <v>0.7</v>
-      </c>
-      <c r="Q66">
-        <v>100</v>
-      </c>
-      <c r="R66" s="10" t="str">
+      <c r="T66" s="10">
+        <v>120</v>
+      </c>
+      <c r="U66" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V66" s="10">
+        <v>85</v>
+      </c>
+      <c r="W66" t="str">
         <v>シーカー</v>
       </c>
-      <c r="S66" s="10">
-        <v>50</v>
-      </c>
-      <c r="T66" s="10">
-        <v>224.5545454545454</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X66">
+        <v>40</v>
+      </c>
+      <c r="Y66" s="10">
+        <v>234.5363636363636</v>
+      </c>
+      <c r="Z66" s="10">
+        <v>174.5363636363636</v>
+      </c>
+      <c r="AA66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="s">
         <v>80</v>
       </c>
@@ -4852,45 +5274,51 @@
         <v>40</v>
       </c>
       <c r="I67" s="4">
-        <f t="shared" ref="I67:I73" si="2">B67*130+(C67)*170+(D67/2)+(E67-0.2)*130+(F67/2.2)</f>
+        <f t="shared" ref="I67:I79" si="2">B67*130+(C67)*170+(D67/2)+(E67-0.2)*130+(F67/2.2)</f>
         <v>241.40909090909091</v>
       </c>
       <c r="J67" s="10">
-        <f t="shared" ref="J67:J73" si="3">B67*130+(C67)*170+(E67-0.2)*130+(F67/2.2)</f>
+        <f t="shared" ref="J67:J79" si="3">B67*130+(C67)*170+(E67-0.2)*130+(F67/2.2)</f>
         <v>211.40909090909091</v>
       </c>
       <c r="K67">
         <v>1</v>
       </c>
-      <c r="L67" t="str">
-        <v>Jinggg</v>
-      </c>
-      <c r="M67">
-        <v>0.3</v>
-      </c>
-      <c r="N67">
-        <v>0.26</v>
-      </c>
-      <c r="O67">
-        <v>68</v>
-      </c>
-      <c r="P67">
-        <v>0.71</v>
-      </c>
-      <c r="Q67">
-        <v>90</v>
-      </c>
-      <c r="R67" s="10" t="str">
-        <v>タイガー</v>
-      </c>
-      <c r="S67" s="10">
-        <v>50</v>
+      <c r="Q67" t="str">
+        <v>Rb</v>
+      </c>
+      <c r="R67" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S67" s="11">
+        <v>0.23</v>
       </c>
       <c r="T67" s="10">
-        <v>224.40909090909091</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" ht="15.75" customHeight="1">
+        <v>110</v>
+      </c>
+      <c r="U67" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="V67" s="10">
+        <v>80</v>
+      </c>
+      <c r="W67" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X67">
+        <v>40</v>
+      </c>
+      <c r="Y67" s="10">
+        <v>229.26363636363635</v>
+      </c>
+      <c r="Z67" s="10">
+        <v>174.26363636363635</v>
+      </c>
+      <c r="AA67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="s">
         <v>81</v>
       </c>
@@ -4926,35 +5354,41 @@
       <c r="K68">
         <v>1</v>
       </c>
-      <c r="L68" t="str">
-        <v>Jamppi</v>
-      </c>
-      <c r="M68">
-        <v>0.27</v>
-      </c>
-      <c r="N68">
+      <c r="Q68" t="str">
+        <v>Brawk</v>
+      </c>
+      <c r="R68" s="11">
+        <v>0.32</v>
+      </c>
+      <c r="S68" s="11">
         <v>0.15</v>
       </c>
-      <c r="O68">
-        <v>125</v>
-      </c>
-      <c r="P68">
-        <v>0.68</v>
-      </c>
-      <c r="Q68">
-        <v>85</v>
-      </c>
-      <c r="R68" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S68" s="10">
-        <v>55</v>
-      </c>
       <c r="T68" s="10">
-        <v>224.13636363636363</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" ht="15.75" customHeight="1">
+        <v>90</v>
+      </c>
+      <c r="U68" s="11">
+        <v>0.69</v>
+      </c>
+      <c r="V68" s="10">
+        <v>95</v>
+      </c>
+      <c r="W68" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X68">
+        <v>90</v>
+      </c>
+      <c r="Y68" s="10">
+        <v>218.98181818181817</v>
+      </c>
+      <c r="Z68" s="10">
+        <v>173.98181818181817</v>
+      </c>
+      <c r="AA68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
         <v>82</v>
       </c>
@@ -4965,10 +5399,10 @@
         <v>0.17</v>
       </c>
       <c r="D69" s="5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E69" s="5">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="F69" s="4">
         <v>135</v>
@@ -4981,44 +5415,50 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" si="2"/>
-        <v>265.16363636363639</v>
+        <v>265.26363636363641</v>
       </c>
       <c r="J69" s="10">
         <f t="shared" si="3"/>
-        <v>217.66363636363639</v>
+        <v>220.26363636363641</v>
       </c>
       <c r="K69">
         <v>1</v>
       </c>
-      <c r="L69" t="str">
-        <v>Verno</v>
-      </c>
-      <c r="M69">
-        <v>0.35</v>
-      </c>
-      <c r="N69">
+      <c r="Q69" t="str">
+        <v>C0M</v>
+      </c>
+      <c r="R69" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S69" s="11">
         <v>0.16</v>
       </c>
-      <c r="O69">
-        <v>86</v>
-      </c>
-      <c r="P69">
-        <v>0.7</v>
-      </c>
-      <c r="Q69">
+      <c r="T69" s="10">
+        <v>120</v>
+      </c>
+      <c r="U69" s="11">
+        <v>0.69</v>
+      </c>
+      <c r="V69" s="10">
         <v>95</v>
       </c>
-      <c r="R69" s="10" t="str">
+      <c r="W69" t="str">
         <v>シーカー</v>
       </c>
-      <c r="S69" s="10">
-        <v>80</v>
-      </c>
-      <c r="T69" s="10">
-        <v>223.88181818181818</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" ht="15.75" customHeight="1">
+      <c r="X69">
+        <v>60</v>
+      </c>
+      <c r="Y69" s="10">
+        <v>230.4818181818182</v>
+      </c>
+      <c r="Z69" s="10">
+        <v>170.48181818181817</v>
+      </c>
+      <c r="AA69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
         <v>83</v>
       </c>
@@ -5054,35 +5494,41 @@
       <c r="K70">
         <v>1</v>
       </c>
-      <c r="L70" t="str">
-        <v>d4v41</v>
-      </c>
-      <c r="M70">
-        <v>0.35</v>
-      </c>
-      <c r="N70">
-        <v>0.17</v>
-      </c>
-      <c r="O70">
-        <v>70</v>
-      </c>
-      <c r="P70">
-        <v>0.71</v>
-      </c>
-      <c r="Q70">
-        <v>105</v>
-      </c>
-      <c r="R70" s="10" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S70" s="10">
+      <c r="Q70" t="str">
+        <v>SugarZ3ro</v>
+      </c>
+      <c r="R70" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S70" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="T70" s="10">
+        <v>120</v>
+      </c>
+      <c r="U70" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="V70" s="10">
+        <v>93</v>
+      </c>
+      <c r="W70" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X70">
         <v>40</v>
       </c>
-      <c r="T70" s="10">
-        <v>223.42727272727271</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y70" s="10">
+        <v>229.07272727272726</v>
+      </c>
+      <c r="Z70" s="10">
+        <v>169.07272727272726</v>
+      </c>
+      <c r="AA70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" ht="15.75" customHeight="1">
       <c r="A71" s="5" t="s">
         <v>84</v>
       </c>
@@ -5118,35 +5564,41 @@
       <c r="K71">
         <v>1</v>
       </c>
-      <c r="L71" t="str">
-        <v>Laz</v>
-      </c>
-      <c r="M71">
-        <v>0.4</v>
-      </c>
-      <c r="N71">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="O71">
-        <v>70</v>
-      </c>
-      <c r="P71">
-        <v>0.75</v>
-      </c>
-      <c r="Q71">
-        <v>86</v>
-      </c>
-      <c r="R71" s="10" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="S71" s="10">
-        <v>80</v>
+      <c r="Q71" t="str">
+        <v>Mako</v>
+      </c>
+      <c r="R71" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S71" s="11">
+        <v>0.16</v>
       </c>
       <c r="T71" s="10">
-        <v>221.3909090909091</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" ht="15.75" customHeight="1">
+        <v>120</v>
+      </c>
+      <c r="U71" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V71" s="10">
+        <v>85</v>
+      </c>
+      <c r="W71" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X71">
+        <v>50</v>
+      </c>
+      <c r="Y71" s="10">
+        <v>227.23636363636362</v>
+      </c>
+      <c r="Z71" s="10">
+        <v>167.23636363636362</v>
+      </c>
+      <c r="AA71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="s">
         <v>85</v>
       </c>
@@ -5182,35 +5634,42 @@
       <c r="K72">
         <v>1</v>
       </c>
-      <c r="L72" t="str">
-        <v>Brawk</v>
-      </c>
-      <c r="M72">
-        <v>0.32</v>
-      </c>
-      <c r="N72">
-        <v>0.15</v>
-      </c>
-      <c r="O72">
-        <v>90</v>
-      </c>
-      <c r="P72" s="10">
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10" t="str">
+        <v>F0rsakeN</v>
+      </c>
+      <c r="R72" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="S72" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="T72" s="10">
+        <v>125</v>
+      </c>
+      <c r="U72" s="11">
         <v>0.69</v>
       </c>
-      <c r="Q72" s="10">
+      <c r="V72" s="10">
         <v>95</v>
       </c>
-      <c r="R72" t="str">
-        <v>シーカー</v>
-      </c>
-      <c r="S72">
-        <v>90</v>
-      </c>
-      <c r="T72" s="10">
-        <v>218.98181818181817</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" ht="15.75" customHeight="1">
+      <c r="W72" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X72">
+        <v>50</v>
+      </c>
+      <c r="Y72" s="10">
+        <v>228.28181818181818</v>
+      </c>
+      <c r="Z72" s="10">
+        <v>165.78181818181818</v>
+      </c>
+      <c r="AA72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="s">
         <v>86</v>
       </c>
@@ -5230,10 +5689,10 @@
         <v>150</v>
       </c>
       <c r="G73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H73">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="I73" s="4">
         <f t="shared" si="2"/>
@@ -5244,251 +5703,465 @@
         <v>232.78181818181821</v>
       </c>
       <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73" t="str">
+        <v>1</v>
+      </c>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10" t="str">
+        <v>crashies</v>
+      </c>
+      <c r="R73" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S73" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="T73" s="10">
+        <v>140</v>
+      </c>
+      <c r="U73" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="V73" s="10">
+        <v>80</v>
+      </c>
+      <c r="W73" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X73">
+        <v>45</v>
+      </c>
+      <c r="Y73" s="10">
+        <v>234.06363636363636</v>
+      </c>
+      <c r="Z73" s="10">
+        <v>164.06363636363636</v>
+      </c>
+      <c r="AA73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A74" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="C74" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="D74" s="4">
+        <v>100</v>
+      </c>
+      <c r="E74">
+        <v>0.75</v>
+      </c>
+      <c r="F74" s="4">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74">
+        <v>75</v>
+      </c>
+      <c r="I74" s="4">
+        <f t="shared" si="2"/>
+        <v>277.86363636363637</v>
+      </c>
+      <c r="J74" s="10">
+        <f t="shared" si="3"/>
+        <v>227.86363636363637</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10" t="str">
+        <v>Boostio</v>
+      </c>
+      <c r="R74" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S74" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="T74" s="10">
+        <v>128</v>
+      </c>
+      <c r="U74" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="V74" s="10">
+        <v>85</v>
+      </c>
+      <c r="W74" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X74">
+        <v>70</v>
+      </c>
+      <c r="Y74" s="10">
+        <v>226.93636363636364</v>
+      </c>
+      <c r="Z74" s="10">
+        <v>162.93636363636364</v>
+      </c>
+      <c r="AA74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A75" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="C75" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D75" s="5">
+        <v>86</v>
+      </c>
+      <c r="E75" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="F75" s="4">
+        <v>104</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="4">
+        <v>80</v>
+      </c>
+      <c r="I75" s="4">
+        <f t="shared" si="2"/>
+        <v>243.37272727272727</v>
+      </c>
+      <c r="J75" s="10">
+        <f t="shared" si="3"/>
+        <v>200.37272727272727</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>Jamppi</v>
+      </c>
+      <c r="R75" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="S75" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="T75" s="10">
+        <v>125</v>
+      </c>
+      <c r="U75" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="V75" s="10">
+        <v>85</v>
+      </c>
+      <c r="W75" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X75">
+        <v>55</v>
+      </c>
+      <c r="Y75" s="10">
+        <v>224.13636363636363</v>
+      </c>
+      <c r="Z75" s="10">
+        <v>161.63636363636363</v>
+      </c>
+      <c r="AA75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A76" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B76" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="C76" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D76" s="5">
+        <v>85</v>
+      </c>
+      <c r="E76" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F76" s="4">
+        <v>150</v>
+      </c>
+      <c r="G76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="4">
+        <v>55</v>
+      </c>
+      <c r="I76" s="4">
+        <f t="shared" si="2"/>
+        <v>261.68181818181819</v>
+      </c>
+      <c r="J76" s="10">
+        <f t="shared" si="3"/>
+        <v>219.18181818181819</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>stax</v>
+      </c>
+      <c r="R76" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S76" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="T76" s="10">
+        <v>130</v>
+      </c>
+      <c r="U76" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="V76" s="10">
+        <v>80</v>
+      </c>
+      <c r="W76" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X76">
+        <v>70</v>
+      </c>
+      <c r="Y76" s="10">
+        <v>225.66363636363633</v>
+      </c>
+      <c r="Z76" s="10">
+        <v>160.66363636363636</v>
+      </c>
+      <c r="AA76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A77" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B77" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C77" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D77" s="5">
+        <v>85</v>
+      </c>
+      <c r="E77" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F77" s="4">
+        <v>125</v>
+      </c>
+      <c r="G77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" s="4">
+        <v>65</v>
+      </c>
+      <c r="I77" s="4">
+        <f t="shared" si="2"/>
+        <v>237.41818181818181</v>
+      </c>
+      <c r="J77" s="10">
+        <f t="shared" si="3"/>
+        <v>194.91818181818181</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>valyn</v>
+      </c>
+      <c r="R77" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="S77" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="T77" s="10">
+        <v>140</v>
+      </c>
+      <c r="U77" s="11">
+        <v>0.64</v>
+      </c>
+      <c r="V77" s="10">
+        <v>95</v>
+      </c>
+      <c r="W77" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X77">
+        <v>40</v>
+      </c>
+      <c r="Y77" s="10">
+        <v>226.28181818181821</v>
+      </c>
+      <c r="Z77" s="10">
+        <v>156.28181818181818</v>
+      </c>
+      <c r="AA77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A78" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C78" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="D78" s="5">
+        <v>85</v>
+      </c>
+      <c r="E78" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="F78" s="4">
+        <v>110</v>
+      </c>
+      <c r="G78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="4">
+        <v>65</v>
+      </c>
+      <c r="I78" s="4">
+        <f t="shared" si="2"/>
+        <v>233.60000000000002</v>
+      </c>
+      <c r="J78" s="10">
+        <f t="shared" si="3"/>
+        <v>191.10000000000002</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="str">
+        <v>Boaster</v>
+      </c>
+      <c r="R78" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="S78" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="T78" s="10">
+        <v>165</v>
+      </c>
+      <c r="U78" s="11">
+        <v>0.62</v>
+      </c>
+      <c r="V78" s="10">
+        <v>96</v>
+      </c>
+      <c r="W78" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X78">
+        <v>50</v>
+      </c>
+      <c r="Y78" s="10">
+        <v>227.13636363636363</v>
+      </c>
+      <c r="Z78" s="10">
+        <v>144.63636363636363</v>
+      </c>
+      <c r="AA78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A79" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D79" s="5">
+        <v>78</v>
+      </c>
+      <c r="E79" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="F79" s="4">
+        <v>115</v>
+      </c>
+      <c r="G79" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" s="4">
+        <v>75</v>
+      </c>
+      <c r="I79" s="4">
+        <f t="shared" si="2"/>
+        <v>248.67272727272729</v>
+      </c>
+      <c r="J79" s="10">
+        <f t="shared" si="3"/>
+        <v>209.67272727272729</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="str">
         <v>FNS</v>
       </c>
-      <c r="M73">
-        <v>0.15</v>
-      </c>
-      <c r="N73">
+      <c r="R79" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="S79" s="11">
         <v>0.13</v>
       </c>
-      <c r="O73">
+      <c r="T79" s="10">
         <v>170</v>
       </c>
-      <c r="P73" s="10">
+      <c r="U79" s="11">
         <v>0.63</v>
       </c>
-      <c r="Q73" s="10">
+      <c r="V79" s="10">
         <v>70</v>
       </c>
-      <c r="R73" t="str">
+      <c r="W79" t="str">
         <v>スモーカー</v>
       </c>
-      <c r="S73">
+      <c r="X79">
         <v>40</v>
       </c>
-      <c r="T73" s="10">
-        <v>214.31818181818181</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="10">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>0</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75" s="10">
-        <v>0</v>
-      </c>
-      <c r="S75" s="10">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76" s="10">
-        <v>0</v>
-      </c>
-      <c r="S76" s="10">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77" s="10">
-        <v>0</v>
-      </c>
-      <c r="S77" s="10">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>0</v>
-      </c>
-      <c r="R78" s="10">
-        <v>0</v>
-      </c>
-      <c r="S78" s="10">
-        <v>0</v>
-      </c>
-      <c r="T78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79" s="10">
-        <v>0</v>
-      </c>
-      <c r="S79" s="10">
-        <v>0</v>
-      </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" ht="15.75" customHeight="1">
+      <c r="Y79" s="10">
+        <v>216.91818181818181</v>
+      </c>
+      <c r="Z79" s="10">
+        <v>131.91818181818181</v>
+      </c>
+      <c r="AA79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" ht="15.75" customHeight="1">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -5496,21 +6169,6 @@
       <c r="E80" s="3"/>
       <c r="F80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
       <c r="Q80">
         <v>0</v>
       </c>
@@ -5523,8 +6181,29 @@
       <c r="T80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" ht="15.75" customHeight="1">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -5532,21 +6211,6 @@
       <c r="E81" s="3"/>
       <c r="F81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
       <c r="Q81">
         <v>0</v>
       </c>
@@ -5559,8 +6223,29 @@
       <c r="T81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" ht="15.75" customHeight="1">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -5568,21 +6253,6 @@
       <c r="E82" s="5"/>
       <c r="F82" s="4"/>
       <c r="H82" s="4"/>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
       <c r="Q82">
         <v>0</v>
       </c>
@@ -5595,8 +6265,29 @@
       <c r="T82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" ht="15.75" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -5604,21 +6295,6 @@
       <c r="E83" s="5"/>
       <c r="F83" s="4"/>
       <c r="H83" s="4"/>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
       <c r="Q83">
         <v>0</v>
       </c>
@@ -5631,8 +6307,29 @@
       <c r="T83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+      <c r="AA83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" ht="15.75" customHeight="1">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -5640,21 +6337,6 @@
       <c r="E84" s="5"/>
       <c r="F84" s="4"/>
       <c r="H84" s="4"/>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
       <c r="Q84">
         <v>0</v>
       </c>
@@ -5667,8 +6349,29 @@
       <c r="T84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" ht="15.75" customHeight="1">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -5676,21 +6379,6 @@
       <c r="E85" s="5"/>
       <c r="F85" s="4"/>
       <c r="H85" s="4"/>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
       <c r="Q85">
         <v>0</v>
       </c>
@@ -5703,8 +6391,29 @@
       <c r="T85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+      <c r="AA85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" ht="15.75" customHeight="1">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -5712,21 +6421,6 @@
       <c r="E86" s="5"/>
       <c r="F86" s="4"/>
       <c r="H86" s="4"/>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
       <c r="Q86">
         <v>0</v>
       </c>
@@ -5739,8 +6433,29 @@
       <c r="T86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" ht="15.75" customHeight="1">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -5748,21 +6463,6 @@
       <c r="E87" s="5"/>
       <c r="F87" s="4"/>
       <c r="H87" s="4"/>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
       <c r="Q87">
         <v>0</v>
       </c>
@@ -5775,8 +6475,29 @@
       <c r="T87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+      <c r="AA87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" ht="15.75" customHeight="1">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -5784,21 +6505,6 @@
       <c r="E88" s="5"/>
       <c r="F88" s="4"/>
       <c r="H88" s="4"/>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
       <c r="Q88">
         <v>0</v>
       </c>
@@ -5811,8 +6517,29 @@
       <c r="T88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U88">
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
+        <v>0</v>
+      </c>
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+      <c r="AA88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" ht="15.75" customHeight="1">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -5820,21 +6547,6 @@
       <c r="E89" s="5"/>
       <c r="F89" s="4"/>
       <c r="H89" s="4"/>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
       <c r="Q89">
         <v>0</v>
       </c>
@@ -5847,8 +6559,29 @@
       <c r="T89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" ht="15.75" customHeight="1">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -5856,21 +6589,6 @@
       <c r="E90" s="5"/>
       <c r="F90" s="4"/>
       <c r="H90" s="4"/>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
       <c r="Q90">
         <v>0</v>
       </c>
@@ -5883,8 +6601,29 @@
       <c r="T90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" ht="15.75" customHeight="1">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -5892,21 +6631,6 @@
       <c r="E91" s="5"/>
       <c r="F91" s="4"/>
       <c r="H91" s="4"/>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
       <c r="Q91">
         <v>0</v>
       </c>
@@ -5919,8 +6643,29 @@
       <c r="T91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" ht="15.75" customHeight="1">
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+      <c r="AA91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" ht="15.75" customHeight="1">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -5928,21 +6673,6 @@
       <c r="E92" s="5"/>
       <c r="F92" s="4"/>
       <c r="H92" s="4"/>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
       <c r="Q92">
         <v>0</v>
       </c>
@@ -5955,23 +6685,29 @@
       <c r="T92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" ht="15.75" customHeight="1">
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
+      <c r="U92">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+      <c r="AA92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" ht="15.75" customHeight="1">
       <c r="Q93">
         <v>0</v>
       </c>
@@ -5984,23 +6720,29 @@
       <c r="T93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" ht="15.75" customHeight="1">
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
+      <c r="U93">
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+      <c r="AA93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" ht="15.75" customHeight="1">
       <c r="Q94">
         <v>0</v>
       </c>
@@ -6013,23 +6755,29 @@
       <c r="T94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" ht="15.75" customHeight="1">
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
+      <c r="U94">
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
+      <c r="X94">
+        <v>0</v>
+      </c>
+      <c r="Y94">
+        <v>0</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+      <c r="AA94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" ht="15.75" customHeight="1">
       <c r="Q95">
         <v>0</v>
       </c>
@@ -6042,23 +6790,29 @@
       <c r="T95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" ht="15.75" customHeight="1">
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
+      <c r="U95">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0</v>
+      </c>
+      <c r="X95">
+        <v>0</v>
+      </c>
+      <c r="Y95">
+        <v>0</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+      <c r="AA95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" ht="15.75" customHeight="1">
       <c r="Q96">
         <v>0</v>
       </c>
@@ -6071,23 +6825,29 @@
       <c r="T96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="12:20" ht="15.75" customHeight="1">
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
+      <c r="U96">
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0</v>
+      </c>
+      <c r="X96">
+        <v>0</v>
+      </c>
+      <c r="Y96">
+        <v>0</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+      <c r="AA96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="17:27" ht="15.75" customHeight="1">
       <c r="Q97">
         <v>0</v>
       </c>
@@ -6100,22 +6860,43 @@
       <c r="T97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="99" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="100" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="101" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="102" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="103" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="104" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="105" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="106" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="107" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="108" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="109" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="110" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="111" spans="12:20" ht="15.75" customHeight="1"/>
-    <row r="112" spans="12:20" ht="15.75" customHeight="1"/>
+      <c r="U97">
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0</v>
+      </c>
+      <c r="X97">
+        <v>0</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+      <c r="AA97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="99" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="100" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="101" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="102" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="103" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="104" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="105" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="106" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="107" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="108" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="109" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="110" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="111" spans="17:27" ht="15.75" customHeight="1"/>
+    <row r="112" spans="17:27" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
     <row r="115" ht="15.75" customHeight="1"/>

--- a/03.game/FPS_chars.xlsx
+++ b/03.game/FPS_chars.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FA8D6D-6128-48B0-8434-1535AB650DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C7C0B08-5788-4A14-8E3D-000699DD905F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="シート1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
   <si>
     <t>名前</t>
   </si>
@@ -304,7 +304,7 @@
     <t>IbarakiNinja</t>
   </si>
   <si>
-    <t>Canezera</t>
+    <t>Canezerra</t>
   </si>
   <si>
     <t>Arlecchino</t>
@@ -335,6 +335,33 @@
   </si>
   <si>
     <t>vo0kashu</t>
+  </si>
+  <si>
+    <t>Absol</t>
+  </si>
+  <si>
+    <t>marteen</t>
+  </si>
+  <si>
+    <t>Crewn</t>
+  </si>
+  <si>
+    <t>Loita</t>
+  </si>
+  <si>
+    <t>Katarina</t>
+  </si>
+  <si>
+    <t>SereNa</t>
+  </si>
+  <si>
+    <t>cNed</t>
+  </si>
+  <si>
+    <t>soulcas</t>
+  </si>
+  <si>
+    <t>trexx</t>
   </si>
 </sst>
 </file>
@@ -735,34 +762,34 @@
       </c>
       <c r="Q2" t="str" cm="1">
         <f t="array" ref="Q2:AA97">_xlfn._xlws.SORT(A2:K97, {10}, {-1})</f>
-        <v>まーやまくん</v>
+        <v>おもこ</v>
       </c>
       <c r="R2" s="11">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="S2" s="11">
-        <v>0.21</v>
+        <v>0.67</v>
       </c>
       <c r="T2" s="10">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="U2" s="11">
         <v>0.67</v>
       </c>
       <c r="V2" s="10">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="W2" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X2">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="Y2" s="10">
-        <v>296.43636363636364</v>
+        <v>326.05454545454546</v>
       </c>
       <c r="Z2" s="10">
-        <v>251.43636363636361</v>
+        <v>292.55454545454546</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -779,7 +806,7 @@
         <v>0.13</v>
       </c>
       <c r="D3" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2">
         <v>0.85</v>
@@ -795,7 +822,7 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I66" si="0">B3*130+(C3)*170+(D3/2)+(E3-0.2)*130+(F3/2.2)</f>
-        <v>277.5090909090909</v>
+        <v>276.5090909090909</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" ref="J3:J66" si="1">B3*130+(C3)*170+(E3-0.2)*130+(F3/2.2)</f>
@@ -805,37 +832,37 @@
         <v>1</v>
       </c>
       <c r="Q3" t="str">
-        <v>something</v>
+        <v>まーやまくん</v>
       </c>
       <c r="R3" s="11">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="S3" s="11">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="T3" s="10">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="U3" s="11">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="V3" s="10">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="W3" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y3" s="10">
-        <v>284.7</v>
+        <v>319.83636363636361</v>
       </c>
       <c r="Z3" s="10">
-        <v>249.7</v>
+        <v>274.83636363636361</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1">
@@ -849,7 +876,7 @@
         <v>0.24</v>
       </c>
       <c r="D4" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2">
         <v>0.88</v>
@@ -861,11 +888,11 @@
         <v>16</v>
       </c>
       <c r="H4" s="4">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="0"/>
-        <v>284.7</v>
+        <v>282.2</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="1"/>
@@ -875,37 +902,37 @@
         <v>1</v>
       </c>
       <c r="Q4" t="str">
-        <v>Alfajer</v>
+        <v>Tortlilyan</v>
       </c>
       <c r="R4" s="11">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="S4" s="11">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="T4" s="10">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="U4" s="11">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="V4" s="10">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="W4" t="str">
         <v>タイガー</v>
       </c>
       <c r="X4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y4" s="10">
-        <v>268.80909090909086</v>
+        <v>319.60909090909092</v>
       </c>
       <c r="Z4" s="10">
-        <v>238.80909090909088</v>
+        <v>258.10909090909092</v>
       </c>
       <c r="AA4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1">
@@ -945,34 +972,34 @@
         <v>1</v>
       </c>
       <c r="Q5" t="str">
-        <v>Demon1</v>
+        <v>something</v>
       </c>
       <c r="R5" s="11">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="S5" s="11">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="T5" s="10">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="U5" s="11">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="V5" s="10">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="W5" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X5">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="Y5" s="10">
-        <v>277.5090909090909</v>
+        <v>282.2</v>
       </c>
       <c r="Z5" s="10">
-        <v>237.50909090909087</v>
+        <v>249.7</v>
       </c>
       <c r="AA5">
         <v>1</v>
@@ -1015,19 +1042,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="str">
-        <v>Tortlilyan</v>
+        <v>cNed</v>
       </c>
       <c r="R6" s="11">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="S6" s="11">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="T6" s="10">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="U6" s="11">
-        <v>0.81</v>
+        <v>0.95</v>
       </c>
       <c r="V6" s="10">
         <v>155</v>
@@ -1036,16 +1063,16 @@
         <v>タイガー</v>
       </c>
       <c r="X6">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="Y6" s="10">
-        <v>298.95454545454544</v>
+        <v>284.15454545454543</v>
       </c>
       <c r="Z6" s="10">
-        <v>237.45454545454544</v>
+        <v>241.65454545454543</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1">
@@ -1071,7 +1098,7 @@
         <v>12</v>
       </c>
       <c r="H7" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
@@ -1085,37 +1112,37 @@
         <v>1</v>
       </c>
       <c r="Q7" t="str">
-        <v>Zest</v>
+        <v>Katarina</v>
       </c>
       <c r="R7" s="11">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="S7" s="11">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="T7" s="10">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="U7" s="11">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="V7" s="10">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="W7" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Y7" s="10">
-        <v>272.8</v>
+        <v>283.47272727272724</v>
       </c>
       <c r="Z7" s="10">
-        <v>235.3</v>
+        <v>240.47272727272724</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1">
@@ -1129,7 +1156,7 @@
         <v>0.12</v>
       </c>
       <c r="D8" s="2">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E8" s="2">
         <v>0.62</v>
@@ -1145,7 +1172,7 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>227.13636363636363</v>
+        <v>232.13636363636363</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="1"/>
@@ -1155,34 +1182,34 @@
         <v>1</v>
       </c>
       <c r="Q8" t="str">
-        <v>Lohen</v>
+        <v>Alfajer</v>
       </c>
       <c r="R8" s="11">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="S8" s="11">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="T8" s="10">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U8" s="11">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="V8" s="10">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="W8" t="str">
         <v>タイガー</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Y8" s="10">
-        <v>270.29090909090905</v>
+        <v>268.80909090909086</v>
       </c>
       <c r="Z8" s="10">
-        <v>235.29090909090908</v>
+        <v>238.80909090909088</v>
       </c>
       <c r="AA8">
         <v>1</v>
@@ -1225,34 +1252,34 @@
         <v>1</v>
       </c>
       <c r="Q9" t="str">
-        <v>Aspas</v>
+        <v>Demon1</v>
       </c>
       <c r="R9" s="11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="S9" s="11">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="T9" s="10">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="U9" s="11">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="V9" s="10">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="W9" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X9">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="Y9" s="10">
-        <v>279.44545454545454</v>
+        <v>276.5090909090909</v>
       </c>
       <c r="Z9" s="10">
-        <v>234.44545454545451</v>
+        <v>237.50909090909087</v>
       </c>
       <c r="AA9">
         <v>1</v>
@@ -1295,34 +1322,34 @@
         <v>1</v>
       </c>
       <c r="Q10" t="str">
-        <v>Tartaglia</v>
+        <v>Kachina</v>
       </c>
       <c r="R10" s="11">
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="S10" s="11">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="T10" s="10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="U10" s="11">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="V10" s="10">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="W10" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X10">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y10" s="10">
-        <v>270.28181818181821</v>
+        <v>270.45454545454544</v>
       </c>
       <c r="Z10" s="10">
-        <v>232.78181818181821</v>
+        <v>235.45454545454544</v>
       </c>
       <c r="AA10">
         <v>1</v>
@@ -1365,37 +1392,37 @@
         <v>1</v>
       </c>
       <c r="Q11" t="str">
-        <v>Nanasaki</v>
+        <v>Zest</v>
       </c>
       <c r="R11" s="11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="S11" s="11">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="T11" s="10">
+        <v>75</v>
+      </c>
+      <c r="U11" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="V11" s="10">
+        <v>121</v>
+      </c>
+      <c r="W11" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X11">
         <v>100</v>
       </c>
-      <c r="U11" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="V11" s="10">
-        <v>80</v>
-      </c>
-      <c r="W11" t="str">
-        <v>スモーカー</v>
-      </c>
-      <c r="X11">
-        <v>75</v>
-      </c>
       <c r="Y11" s="10">
-        <v>277.86363636363637</v>
+        <v>272.8</v>
       </c>
       <c r="Z11" s="10">
-        <v>227.86363636363637</v>
+        <v>235.3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1">
@@ -1435,34 +1462,34 @@
         <v>1</v>
       </c>
       <c r="Q12" t="str">
-        <v>Primmie</v>
+        <v>Lohen</v>
       </c>
       <c r="R12" s="11">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="S12" s="11">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="T12" s="10">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="U12" s="11">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="V12" s="10">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="W12" t="str">
         <v>タイガー</v>
       </c>
       <c r="X12">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="10">
-        <v>252.64545454545453</v>
+        <v>270.29090909090905</v>
       </c>
       <c r="Z12" s="10">
-        <v>223.14545454545456</v>
+        <v>235.29090909090908</v>
       </c>
       <c r="AA12">
         <v>1</v>
@@ -1505,34 +1532,34 @@
         <v>1</v>
       </c>
       <c r="Q13" t="str">
-        <v>Chronicle</v>
+        <v>Aspas</v>
       </c>
       <c r="R13" s="11">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="S13" s="11">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="T13" s="10">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="U13" s="11">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="V13" s="10">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="W13" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X13">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="Y13" s="10">
-        <v>273.86363636363637</v>
+        <v>279.44545454545454</v>
       </c>
       <c r="Z13" s="10">
-        <v>221.36363636363637</v>
+        <v>234.44545454545451</v>
       </c>
       <c r="AA13">
         <v>1</v>
@@ -1575,34 +1602,34 @@
         <v>1</v>
       </c>
       <c r="Q14" t="str">
-        <v>Canezera</v>
+        <v>Tartaglia</v>
       </c>
       <c r="R14" s="11">
-        <v>0.41</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="S14" s="11">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="T14" s="10">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="U14" s="11">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="V14" s="10">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="W14" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X14">
         <v>80</v>
       </c>
       <c r="Y14" s="10">
-        <v>265.26363636363641</v>
+        <v>270.28181818181821</v>
       </c>
       <c r="Z14" s="10">
-        <v>220.26363636363641</v>
+        <v>232.78181818181821</v>
       </c>
       <c r="AA14">
         <v>1</v>
@@ -1645,34 +1672,34 @@
         <v>1</v>
       </c>
       <c r="Q15" t="str">
-        <v>Flashback</v>
+        <v>Canezerra</v>
       </c>
       <c r="R15" s="11">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="S15" s="11">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="T15" s="10">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="U15" s="11">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="V15" s="10">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="W15" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Y15" s="10">
-        <v>259.4909090909091</v>
+        <v>274.71818181818185</v>
       </c>
       <c r="Z15" s="10">
-        <v>219.9909090909091</v>
+        <v>232.21818181818185</v>
       </c>
       <c r="AA15">
         <v>1</v>
@@ -1718,7 +1745,7 @@
         <v>WoohyuN</v>
       </c>
       <c r="R16" s="11">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="S16" s="11">
         <v>0.2</v>
@@ -1727,7 +1754,7 @@
         <v>85</v>
       </c>
       <c r="U16" s="11">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="V16" s="10">
         <v>150</v>
@@ -1739,13 +1766,13 @@
         <v>55</v>
       </c>
       <c r="Y16" s="10">
-        <v>261.68181818181819</v>
+        <v>270.78181818181821</v>
       </c>
       <c r="Z16" s="10">
-        <v>219.18181818181819</v>
+        <v>228.28181818181821</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1">
@@ -1785,37 +1812,37 @@
         <v>1</v>
       </c>
       <c r="Q17" t="str">
-        <v>Meteor</v>
+        <v>SereNa</v>
       </c>
       <c r="R17" s="11">
-        <v>0.37</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S17" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.19</v>
       </c>
       <c r="T17" s="10">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="U17" s="11">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="V17" s="10">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="W17" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X17">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="Y17" s="10">
-        <v>252.4818181818182</v>
+        <v>283.68181818181819</v>
       </c>
       <c r="Z17" s="10">
-        <v>215.9818181818182</v>
+        <v>224.18181818181819</v>
       </c>
       <c r="AA17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15.75" customHeight="1">
@@ -1829,7 +1856,7 @@
         <v>0.2</v>
       </c>
       <c r="D18" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E18" s="2">
         <v>0.76</v>
@@ -1845,7 +1872,7 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>245.25454545454545</v>
+        <v>255.25454545454545</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="1"/>
@@ -1855,34 +1882,34 @@
         <v>1</v>
       </c>
       <c r="Q18" t="str">
-        <v>TenZ</v>
+        <v>soulcas</v>
       </c>
       <c r="R18" s="11">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="S18" s="11">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="T18" s="10">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="U18" s="11">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="V18" s="10">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="W18" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X18">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="Y18" s="10">
-        <v>268.34545454545457</v>
+        <v>284.15454545454548</v>
       </c>
       <c r="Z18" s="10">
-        <v>215.84545454545454</v>
+        <v>224.15454545454548</v>
       </c>
       <c r="AA18">
         <v>1</v>
@@ -1925,34 +1952,34 @@
         <v>1</v>
       </c>
       <c r="Q19" t="str">
-        <v>Leo</v>
+        <v>Primmie</v>
       </c>
       <c r="R19" s="11">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="S19" s="11">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="T19" s="10">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="U19" s="11">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="V19" s="10">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="W19" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X19">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Y19" s="10">
-        <v>290.76363636363635</v>
+        <v>252.64545454545453</v>
       </c>
       <c r="Z19" s="10">
-        <v>215.76363636363635</v>
+        <v>223.14545454545456</v>
       </c>
       <c r="AA19">
         <v>1</v>
@@ -1995,34 +2022,34 @@
         <v>1</v>
       </c>
       <c r="Q20" t="str">
-        <v>t3xture</v>
+        <v>Chronicle</v>
       </c>
       <c r="R20" s="11">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="S20" s="11">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="T20" s="10">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U20" s="11">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V20" s="10">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="W20" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X20">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Y20" s="10">
-        <v>261.38181818181818</v>
+        <v>273.86363636363637</v>
       </c>
       <c r="Z20" s="10">
-        <v>214.88181818181818</v>
+        <v>221.36363636363637</v>
       </c>
       <c r="AA20">
         <v>1</v>
@@ -2039,7 +2066,7 @@
         <v>0.19</v>
       </c>
       <c r="D21" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2">
         <v>0.7</v>
@@ -2055,7 +2082,7 @@
       </c>
       <c r="I21" s="4">
         <f t="shared" si="0"/>
-        <v>225.6090909090909</v>
+        <v>228.6090909090909</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="1"/>
@@ -2065,37 +2092,37 @@
         <v>1</v>
       </c>
       <c r="Q21" t="str">
-        <v>おもこ</v>
+        <v>Flashback</v>
       </c>
       <c r="R21" s="11">
-        <v>6.7000000000000004E-2</v>
+        <v>0.38</v>
       </c>
       <c r="S21" s="11">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="T21" s="10">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="U21" s="11">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="V21" s="10">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="W21" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X21">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Y21" s="10">
-        <v>247.66454545454548</v>
+        <v>259.4909090909091</v>
       </c>
       <c r="Z21" s="10">
-        <v>214.16454545454548</v>
+        <v>219.9909090909091</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15.75" customHeight="1">
@@ -2135,34 +2162,34 @@
         <v>1</v>
       </c>
       <c r="Q22" t="str">
-        <v>Jean</v>
+        <v>Meteor</v>
       </c>
       <c r="R22" s="11">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="S22" s="11">
-        <v>0.2</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="T22" s="10">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="U22" s="11">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V22" s="10">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="W22" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X22">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Y22" s="10">
-        <v>269.86363636363637</v>
+        <v>252.4818181818182</v>
       </c>
       <c r="Z22" s="10">
-        <v>212.36363636363637</v>
+        <v>215.9818181818182</v>
       </c>
       <c r="AA22">
         <v>1</v>
@@ -2205,34 +2232,34 @@
         <v>1</v>
       </c>
       <c r="Q23" t="str">
-        <v>jawgemo</v>
+        <v>TenZ</v>
       </c>
       <c r="R23" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.38</v>
       </c>
       <c r="S23" s="11">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="T23" s="10">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U23" s="11">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="V23" s="10">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="W23" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X23">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="Y23" s="10">
-        <v>258.06363636363636</v>
+        <v>268.34545454545457</v>
       </c>
       <c r="Z23" s="10">
-        <v>211.56363636363636</v>
+        <v>215.84545454545454</v>
       </c>
       <c r="AA23">
         <v>1</v>
@@ -2275,34 +2302,34 @@
         <v>1</v>
       </c>
       <c r="Q24" t="str">
-        <v>Kachina</v>
+        <v>Leo</v>
       </c>
       <c r="R24" s="11">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
       <c r="S24" s="11">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="T24" s="10">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="U24" s="11">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="V24" s="10">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="W24" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X24">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Y24" s="10">
-        <v>241.40909090909091</v>
+        <v>290.76363636363635</v>
       </c>
       <c r="Z24" s="10">
-        <v>211.40909090909091</v>
+        <v>215.76363636363635</v>
       </c>
       <c r="AA24">
         <v>1</v>
@@ -2316,16 +2343,16 @@
         <v>0.23</v>
       </c>
       <c r="C25" s="3">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="D25" s="3">
         <v>123</v>
       </c>
       <c r="E25" s="3">
-        <v>0.81</v>
+        <v>0.9</v>
       </c>
       <c r="F25" s="4">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
@@ -2335,44 +2362,44 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
-        <v>298.95454545454544</v>
+        <v>319.60909090909092</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v>237.45454545454544</v>
+        <v>258.10909090909092</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="Q25" t="str">
-        <v>Derke</v>
+        <v>t3xture</v>
       </c>
       <c r="R25" s="11">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S25" s="11">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="T25" s="10">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="U25" s="11">
         <v>0.75</v>
       </c>
       <c r="V25" s="10">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="W25" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X25">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Y25" s="10">
-        <v>255.07272727272726</v>
+        <v>261.38181818181818</v>
       </c>
       <c r="Z25" s="10">
-        <v>210.07272727272726</v>
+        <v>214.88181818181818</v>
       </c>
       <c r="AA25">
         <v>1</v>
@@ -2383,7 +2410,7 @@
         <v>39</v>
       </c>
       <c r="B26" s="8">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="C26" s="3">
         <v>0.21</v>
@@ -2392,7 +2419,7 @@
         <v>90</v>
       </c>
       <c r="E26" s="3">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="F26" s="4">
         <v>140</v>
@@ -2405,44 +2432,44 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
-        <v>296.43636363636364</v>
+        <v>319.83636363636361</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v>251.43636363636361</v>
+        <v>274.83636363636361</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="Q26" t="str">
-        <v>Lisa</v>
+        <v>marteen</v>
       </c>
       <c r="R26" s="11">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="S26" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T26" s="10">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="U26" s="11">
         <v>0.78</v>
       </c>
       <c r="V26" s="10">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="W26" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X26">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y26" s="10">
-        <v>269.7</v>
+        <v>254.64545454545456</v>
       </c>
       <c r="Z26" s="10">
-        <v>209.7</v>
+        <v>214.64545454545456</v>
       </c>
       <c r="AA26">
         <v>1</v>
@@ -2453,7 +2480,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="8">
-        <v>6.7000000000000004E-2</v>
+        <v>0.67</v>
       </c>
       <c r="C27" s="3">
         <v>0.67</v>
@@ -2471,51 +2498,51 @@
         <v>12</v>
       </c>
       <c r="H27" s="4">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" si="0"/>
-        <v>247.66454545454548</v>
+        <v>326.05454545454546</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v>214.16454545454548</v>
+        <v>292.55454545454546</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="Q27" t="str">
-        <v>vo0kashu</v>
+        <v>Jean</v>
       </c>
       <c r="R27" s="11">
         <v>0.35</v>
       </c>
       <c r="S27" s="11">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="T27" s="10">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="U27" s="11">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="V27" s="10">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="W27" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X27">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Y27" s="10">
-        <v>248.67272727272729</v>
+        <v>269.86363636363637</v>
       </c>
       <c r="Z27" s="10">
-        <v>209.67272727272729</v>
+        <v>212.36363636363637</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1">
@@ -2555,34 +2582,34 @@
         <v>1</v>
       </c>
       <c r="Q28" t="str">
-        <v>HYUNMIN</v>
+        <v>trexx</v>
       </c>
       <c r="R28" s="11">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="S28" s="11">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="T28" s="10">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="U28" s="11">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="V28" s="10">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="W28" t="str">
-        <v>フラッシュ</v>
+        <v>シーカー</v>
       </c>
       <c r="X28">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="Y28" s="10">
-        <v>245.8</v>
+        <v>262.36363636363637</v>
       </c>
       <c r="Z28" s="10">
-        <v>207.8</v>
+        <v>212.36363636363637</v>
       </c>
       <c r="AA28">
         <v>1</v>
@@ -2625,22 +2652,22 @@
         <v>1</v>
       </c>
       <c r="Q29" t="str">
-        <v>Wo0t</v>
+        <v>jawgemo</v>
       </c>
       <c r="R29" s="11">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S29" s="11">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="T29" s="10">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="U29" s="11">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="V29" s="10">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="W29" t="str">
         <v>タイガー</v>
@@ -2649,10 +2676,10 @@
         <v>75</v>
       </c>
       <c r="Y29" s="10">
-        <v>244.24545454545452</v>
+        <v>258.06363636363636</v>
       </c>
       <c r="Z29" s="10">
-        <v>205.24545454545452</v>
+        <v>211.56363636363636</v>
       </c>
       <c r="AA29">
         <v>1</v>
@@ -2695,34 +2722,34 @@
         <v>1</v>
       </c>
       <c r="Q30" t="str">
-        <v>Smoggy</v>
+        <v>Derke</v>
       </c>
       <c r="R30" s="11">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="S30" s="11">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="T30" s="10">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="U30" s="11">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="V30" s="10">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="W30" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X30">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="Y30" s="10">
-        <v>242.64545454545453</v>
+        <v>255.07272727272726</v>
       </c>
       <c r="Z30" s="10">
-        <v>205.14545454545453</v>
+        <v>210.07272727272726</v>
       </c>
       <c r="AA30">
         <v>1</v>
@@ -2765,34 +2792,34 @@
         <v>1</v>
       </c>
       <c r="Q31" t="str">
-        <v>Rarga</v>
+        <v>Lisa</v>
       </c>
       <c r="R31" s="11">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="S31" s="11">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="T31" s="10">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="U31" s="11">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V31" s="10">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="W31" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X31">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y31" s="10">
-        <v>241.34545454545454</v>
+        <v>269.7</v>
       </c>
       <c r="Z31" s="10">
-        <v>203.84545454545454</v>
+        <v>209.7</v>
       </c>
       <c r="AA31">
         <v>1</v>
@@ -2835,34 +2862,34 @@
         <v>1</v>
       </c>
       <c r="Q32" t="str">
-        <v>ZMJKK</v>
+        <v>vo0kashu</v>
       </c>
       <c r="R32" s="11">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="S32" s="11">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="T32" s="10">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="U32" s="11">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="V32" s="10">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="W32" t="str">
         <v>タイガー</v>
       </c>
       <c r="X32">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Y32" s="10">
-        <v>234.88181818181818</v>
+        <v>249.67272727272729</v>
       </c>
       <c r="Z32" s="10">
-        <v>202.38181818181818</v>
+        <v>209.67272727272729</v>
       </c>
       <c r="AA32">
         <v>1</v>
@@ -2905,34 +2932,34 @@
         <v>1</v>
       </c>
       <c r="Q33" t="str">
-        <v>Arlecchino</v>
+        <v>HYUNMIN</v>
       </c>
       <c r="R33" s="11">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="S33" s="11">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="T33" s="10">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="U33" s="11">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="V33" s="10">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="W33" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X33">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Y33" s="10">
-        <v>269.71818181818179</v>
+        <v>245.8</v>
       </c>
       <c r="Z33" s="10">
-        <v>202.21818181818179</v>
+        <v>207.8</v>
       </c>
       <c r="AA33">
         <v>1</v>
@@ -2975,34 +3002,34 @@
         <v>1</v>
       </c>
       <c r="Q34" t="str">
-        <v>Meiy</v>
+        <v>Absol</v>
       </c>
       <c r="R34" s="11">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="S34" s="11">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="T34" s="10">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="U34" s="11">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="V34" s="10">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="W34" t="str">
         <v>タイガー</v>
       </c>
       <c r="X34">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Y34" s="10">
-        <v>236.8</v>
+        <v>259.66363636363639</v>
       </c>
       <c r="Z34" s="10">
-        <v>201.8</v>
+        <v>207.16363636363639</v>
       </c>
       <c r="AA34">
         <v>1</v>
@@ -3045,34 +3072,34 @@
         <v>1</v>
       </c>
       <c r="Q35" t="str">
-        <v>mada</v>
+        <v>Wo0t</v>
       </c>
       <c r="R35" s="11">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="S35" s="11">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="T35" s="10">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="U35" s="11">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="V35" s="10">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="W35" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X35">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="Y35" s="10">
-        <v>253.72727272727272</v>
+        <v>244.24545454545452</v>
       </c>
       <c r="Z35" s="10">
-        <v>201.22727272727272</v>
+        <v>205.24545454545452</v>
       </c>
       <c r="AA35">
         <v>1</v>
@@ -3115,34 +3142,34 @@
         <v>1</v>
       </c>
       <c r="Q36" t="str">
-        <v>Sato</v>
+        <v>Smoggy</v>
       </c>
       <c r="R36" s="11">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="S36" s="11">
         <v>0.19</v>
       </c>
       <c r="T36" s="10">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="U36" s="11">
         <v>0.73</v>
       </c>
       <c r="V36" s="10">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="W36" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X36">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y36" s="10">
-        <v>234.42727272727271</v>
+        <v>242.64545454545453</v>
       </c>
       <c r="Z36" s="10">
-        <v>200.92727272727271</v>
+        <v>205.14545454545453</v>
       </c>
       <c r="AA36">
         <v>1</v>
@@ -3185,34 +3212,34 @@
         <v>1</v>
       </c>
       <c r="Q37" t="str">
-        <v>Zekken</v>
+        <v>Loita</v>
       </c>
       <c r="R37" s="11">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S37" s="11">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="T37" s="10">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="U37" s="11">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="V37" s="10">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="W37" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X37">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="Y37" s="10">
-        <v>243.22727272727272</v>
+        <v>260.35454545454547</v>
       </c>
       <c r="Z37" s="10">
-        <v>200.72727272727272</v>
+        <v>204.85454545454547</v>
       </c>
       <c r="AA37">
         <v>1</v>
@@ -3255,34 +3282,34 @@
         <v>1</v>
       </c>
       <c r="Q38" t="str">
-        <v>Less</v>
+        <v>Rarga</v>
       </c>
       <c r="R38" s="11">
         <v>0.35</v>
       </c>
       <c r="S38" s="11">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="T38" s="10">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="U38" s="11">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="V38" s="10">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="W38" t="str">
         <v>タイガー</v>
       </c>
       <c r="X38">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Y38" s="10">
-        <v>243.37272727272727</v>
+        <v>241.34545454545454</v>
       </c>
       <c r="Z38" s="10">
-        <v>200.37272727272727</v>
+        <v>203.84545454545454</v>
       </c>
       <c r="AA38">
         <v>1</v>
@@ -3302,7 +3329,7 @@
         <v>110</v>
       </c>
       <c r="E39">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="F39" s="4">
         <v>80</v>
@@ -3315,44 +3342,44 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>229.26363636363635</v>
+        <v>231.86363636363637</v>
       </c>
       <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v>174.26363636363635</v>
+        <v>176.86363636363637</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="Q39" t="str">
-        <v>Lar0k</v>
+        <v>ZMJKK</v>
       </c>
       <c r="R39" s="11">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="S39" s="11">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="T39" s="10">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="U39" s="11">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="V39" s="10">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="W39" t="str">
         <v>タイガー</v>
       </c>
       <c r="X39">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="Y39" s="10">
-        <v>242.1090909090909</v>
+        <v>234.88181818181818</v>
       </c>
       <c r="Z39" s="10">
-        <v>199.6090909090909</v>
+        <v>202.38181818181818</v>
       </c>
       <c r="AA39">
         <v>1</v>
@@ -3372,7 +3399,7 @@
         <v>130</v>
       </c>
       <c r="E40">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="F40" s="4">
         <v>80</v>
@@ -3385,44 +3412,44 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" si="0"/>
-        <v>225.66363636363633</v>
+        <v>228.26363636363635</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v>160.66363636363636</v>
+        <v>163.26363636363635</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="Q40" t="str">
-        <v>kaajak</v>
+        <v>Arlecchino</v>
       </c>
       <c r="R40" s="11">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="S40" s="11">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="T40" s="10">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="U40" s="11">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="V40" s="10">
+        <v>125</v>
+      </c>
+      <c r="W40" t="str">
+        <v>タイガー</v>
+      </c>
+      <c r="X40">
         <v>100</v>
       </c>
-      <c r="W40" t="str">
-        <v>フラッシュ</v>
-      </c>
-      <c r="X40">
-        <v>70</v>
-      </c>
       <c r="Y40" s="10">
-        <v>245.25454545454545</v>
+        <v>269.71818181818179</v>
       </c>
       <c r="Z40" s="10">
-        <v>197.75454545454545</v>
+        <v>202.21818181818179</v>
       </c>
       <c r="AA40">
         <v>1</v>
@@ -3433,16 +3460,16 @@
         <v>54</v>
       </c>
       <c r="B41">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="C41">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="D41">
         <v>85</v>
       </c>
       <c r="E41">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="F41" s="4">
         <v>95</v>
@@ -3455,44 +3482,44 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" si="0"/>
-        <v>229.38181818181818</v>
+        <v>233.68181818181819</v>
       </c>
       <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v>186.88181818181818</v>
+        <v>191.18181818181819</v>
       </c>
       <c r="K41">
         <v>1</v>
       </c>
       <c r="Q41" t="str">
-        <v>s0m</v>
+        <v>Meiy</v>
       </c>
       <c r="R41" s="11">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="S41" s="11">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="T41" s="10">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="U41" s="11">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="V41" s="10">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="W41" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X41">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="Y41" s="10">
-        <v>268.32727272727266</v>
+        <v>236.8</v>
       </c>
       <c r="Z41" s="10">
-        <v>195.82727272727269</v>
+        <v>201.8</v>
       </c>
       <c r="AA41">
         <v>1</v>
@@ -3512,10 +3539,10 @@
         <v>100</v>
       </c>
       <c r="E42">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="F42" s="4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
         <v>14</v>
@@ -3525,44 +3552,44 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>234.67272727272729</v>
+        <v>233.82727272727274</v>
       </c>
       <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v>184.67272727272729</v>
+        <v>183.82727272727274</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="Q42" t="str">
-        <v>Asuna</v>
+        <v>mada</v>
       </c>
       <c r="R42" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.34</v>
       </c>
       <c r="S42" s="11">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="T42" s="10">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="U42" s="11">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="V42" s="10">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="W42" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X42">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Y42" s="10">
-        <v>237.41818181818181</v>
+        <v>253.72727272727272</v>
       </c>
       <c r="Z42" s="10">
-        <v>194.91818181818181</v>
+        <v>201.22727272727272</v>
       </c>
       <c r="AA42">
         <v>1</v>
@@ -3605,34 +3632,34 @@
         <v>1</v>
       </c>
       <c r="Q43" t="str">
-        <v>Dep</v>
+        <v>Sato</v>
       </c>
       <c r="R43" s="11">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="S43" s="11">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="T43" s="10">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="U43" s="11">
         <v>0.73</v>
       </c>
       <c r="V43" s="10">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="W43" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X43">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Y43" s="10">
-        <v>232.15454545454543</v>
+        <v>234.42727272727271</v>
       </c>
       <c r="Z43" s="10">
-        <v>194.65454545454543</v>
+        <v>200.92727272727271</v>
       </c>
       <c r="AA43">
         <v>1</v>
@@ -3675,34 +3702,34 @@
         <v>1</v>
       </c>
       <c r="Q44" t="str">
-        <v>WsLeo</v>
+        <v>Zekken</v>
       </c>
       <c r="R44" s="11">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S44" s="11">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="T44" s="10">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="U44" s="11">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="V44" s="10">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="W44" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X44">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Y44" s="10">
-        <v>259.26363636363635</v>
+        <v>243.22727272727272</v>
       </c>
       <c r="Z44" s="10">
-        <v>194.26363636363635</v>
+        <v>200.72727272727272</v>
       </c>
       <c r="AA44">
         <v>1</v>
@@ -3745,34 +3772,34 @@
         <v>1</v>
       </c>
       <c r="Q45" t="str">
-        <v>BABYBAY</v>
+        <v>Less</v>
       </c>
       <c r="R45" s="11">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="S45" s="11">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="T45" s="10">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U45" s="11">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="V45" s="10">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="W45" t="str">
         <v>タイガー</v>
       </c>
       <c r="X45">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Y45" s="10">
-        <v>234.35454545454547</v>
+        <v>243.37272727272727</v>
       </c>
       <c r="Z45" s="10">
-        <v>191.85454545454547</v>
+        <v>200.37272727272727</v>
       </c>
       <c r="AA45">
         <v>1</v>
@@ -3815,34 +3842,34 @@
         <v>1</v>
       </c>
       <c r="Q46" t="str">
-        <v>Buzz</v>
+        <v>Lar0k</v>
       </c>
       <c r="R46" s="11">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="S46" s="11">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="T46" s="10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U46" s="11">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="V46" s="10">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="W46" t="str">
         <v>タイガー</v>
       </c>
       <c r="X46">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y46" s="10">
-        <v>231.15454545454543</v>
+        <v>242.1090909090909</v>
       </c>
       <c r="Z46" s="10">
-        <v>191.15454545454543</v>
+        <v>199.6090909090909</v>
       </c>
       <c r="AA46">
         <v>1</v>
@@ -3885,34 +3912,34 @@
         <v>1</v>
       </c>
       <c r="Q47" t="str">
-        <v>Cryocells</v>
+        <v>Crewn</v>
       </c>
       <c r="R47" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="S47" s="11">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="T47" s="10">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="U47" s="11">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="V47" s="10">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="W47" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X47">
         <v>65</v>
       </c>
       <c r="Y47" s="10">
-        <v>233.60000000000002</v>
+        <v>266.27272727272725</v>
       </c>
       <c r="Z47" s="10">
-        <v>191.10000000000002</v>
+        <v>198.77272727272725</v>
       </c>
       <c r="AA47">
         <v>1</v>
@@ -3955,34 +3982,34 @@
         <v>1</v>
       </c>
       <c r="Q48" t="str">
-        <v>Jinggg</v>
+        <v>kaajak</v>
       </c>
       <c r="R48" s="11">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="S48" s="11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="T48" s="10">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="U48" s="11">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="V48" s="10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="W48" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X48">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Y48" s="10">
-        <v>224.40909090909091</v>
+        <v>255.25454545454545</v>
       </c>
       <c r="Z48" s="10">
-        <v>190.40909090909091</v>
+        <v>197.75454545454545</v>
       </c>
       <c r="AA48">
         <v>1</v>
@@ -4025,34 +4052,34 @@
         <v>1</v>
       </c>
       <c r="Q49" t="str">
-        <v>Ethan</v>
+        <v>s0m</v>
       </c>
       <c r="R49" s="11">
         <v>0.3</v>
       </c>
       <c r="S49" s="11">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="T49" s="10">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="U49" s="11">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="V49" s="10">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="W49" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X49">
         <v>55</v>
       </c>
       <c r="Y49" s="10">
-        <v>263.5090909090909</v>
+        <v>268.32727272727266</v>
       </c>
       <c r="Z49" s="10">
-        <v>188.50909090909093</v>
+        <v>195.82727272727269</v>
       </c>
       <c r="AA49">
         <v>1</v>
@@ -4095,34 +4122,34 @@
         <v>1</v>
       </c>
       <c r="Q50" t="str">
-        <v>d4v41</v>
+        <v>Asuna</v>
       </c>
       <c r="R50" s="11">
-        <v>0.35</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S50" s="11">
         <v>0.17</v>
       </c>
       <c r="T50" s="10">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="U50" s="11">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="V50" s="10">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="W50" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X50">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Y50" s="10">
-        <v>223.42727272727271</v>
+        <v>237.41818181818181</v>
       </c>
       <c r="Z50" s="10">
-        <v>188.42727272727271</v>
+        <v>194.91818181818181</v>
       </c>
       <c r="AA50">
         <v>1</v>
@@ -4165,34 +4192,34 @@
         <v>1</v>
       </c>
       <c r="Q51" t="str">
-        <v>CHICHOO</v>
+        <v>Dep</v>
       </c>
       <c r="R51" s="11">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="S51" s="11">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="T51" s="10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U51" s="11">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="V51" s="10">
         <v>100</v>
       </c>
       <c r="W51" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X51">
         <v>50</v>
       </c>
       <c r="Y51" s="10">
-        <v>227.85454545454547</v>
+        <v>232.15454545454543</v>
       </c>
       <c r="Z51" s="10">
-        <v>187.85454545454547</v>
+        <v>194.65454545454543</v>
       </c>
       <c r="AA51">
         <v>1</v>
@@ -4235,22 +4262,22 @@
         <v>1</v>
       </c>
       <c r="Q52" t="str">
-        <v>IbarakiNinja</v>
+        <v>WsLeo</v>
       </c>
       <c r="R52" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.36</v>
       </c>
       <c r="S52" s="11">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="T52" s="10">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="U52" s="11">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V52" s="10">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="W52" t="str">
         <v>シーカー</v>
@@ -4259,10 +4286,10 @@
         <v>50</v>
       </c>
       <c r="Y52" s="10">
-        <v>242.37272727272727</v>
+        <v>259.26363636363635</v>
       </c>
       <c r="Z52" s="10">
-        <v>187.37272727272727</v>
+        <v>194.26363636363635</v>
       </c>
       <c r="AA52">
         <v>1</v>
@@ -4305,34 +4332,34 @@
         <v>1</v>
       </c>
       <c r="Q53" t="str">
-        <v>tex</v>
+        <v>Nanasaki</v>
       </c>
       <c r="R53" s="11">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="S53" s="11">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="T53" s="10">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="U53" s="11">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="V53" s="10">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="W53" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X53">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y53" s="10">
-        <v>229.38181818181818</v>
+        <v>253.86363636363637</v>
       </c>
       <c r="Z53" s="10">
-        <v>186.88181818181818</v>
+        <v>193.86363636363637</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -4375,34 +4402,34 @@
         <v>1</v>
       </c>
       <c r="Q54" t="str">
-        <v>Laz</v>
+        <v>BABYBAY</v>
       </c>
       <c r="R54" s="11">
         <v>0.4</v>
       </c>
       <c r="S54" s="11">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="T54" s="10">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="U54" s="11">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="V54" s="10">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="W54" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X54">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Y54" s="10">
-        <v>221.3909090909091</v>
+        <v>234.35454545454547</v>
       </c>
       <c r="Z54" s="10">
-        <v>186.3909090909091</v>
+        <v>191.85454545454547</v>
       </c>
       <c r="AA54">
         <v>1</v>
@@ -4445,34 +4472,34 @@
         <v>1</v>
       </c>
       <c r="Q55" t="str">
-        <v>leaf</v>
+        <v>tex</v>
       </c>
       <c r="R55" s="11">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="S55" s="11">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="T55" s="10">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="U55" s="11">
         <v>0.74</v>
       </c>
       <c r="V55" s="10">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="W55" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X55">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Y55" s="10">
-        <v>229.36363636363637</v>
+        <v>233.68181818181819</v>
       </c>
       <c r="Z55" s="10">
-        <v>184.86363636363637</v>
+        <v>191.18181818181819</v>
       </c>
       <c r="AA55">
         <v>1</v>
@@ -4489,7 +4516,7 @@
         <v>0.13</v>
       </c>
       <c r="D56" s="5">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="E56" s="5">
         <v>0.63</v>
@@ -4501,11 +4528,11 @@
         <v>14</v>
       </c>
       <c r="H56" s="4">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" si="0"/>
-        <v>216.91818181818181</v>
+        <v>226.91818181818181</v>
       </c>
       <c r="J56" s="10">
         <f t="shared" si="1"/>
@@ -4515,34 +4542,34 @@
         <v>1</v>
       </c>
       <c r="Q56" t="str">
-        <v>Mazino</v>
+        <v>Buzz</v>
       </c>
       <c r="R56" s="11">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="S56" s="11">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="T56" s="10">
+        <v>80</v>
+      </c>
+      <c r="U56" s="11">
+        <v>0.72</v>
+      </c>
+      <c r="V56" s="10">
         <v>100</v>
       </c>
-      <c r="U56" s="11">
-        <v>0.73</v>
-      </c>
-      <c r="V56" s="10">
-        <v>93</v>
-      </c>
       <c r="W56" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X56">
         <v>60</v>
       </c>
       <c r="Y56" s="10">
-        <v>234.67272727272729</v>
+        <v>231.15454545454543</v>
       </c>
       <c r="Z56" s="10">
-        <v>184.67272727272729</v>
+        <v>191.15454545454543</v>
       </c>
       <c r="AA56">
         <v>1</v>
@@ -4585,34 +4612,34 @@
         <v>1</v>
       </c>
       <c r="Q57" t="str">
-        <v>eggsterr</v>
+        <v>Cryocells</v>
       </c>
       <c r="R57" s="11">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S57" s="11">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="T57" s="10">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="U57" s="11">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="V57" s="10">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="W57" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X57">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Y57" s="10">
-        <v>228.58181818181816</v>
+        <v>233.60000000000002</v>
       </c>
       <c r="Z57" s="10">
-        <v>184.58181818181816</v>
+        <v>191.10000000000002</v>
       </c>
       <c r="AA57">
         <v>1</v>
@@ -4655,34 +4682,34 @@
         <v>1</v>
       </c>
       <c r="Q58" t="str">
-        <v>Lysoar</v>
+        <v>Jinggg</v>
       </c>
       <c r="R58" s="11">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="S58" s="11">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="T58" s="10">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="U58" s="11">
         <v>0.71</v>
       </c>
       <c r="V58" s="10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W58" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X58">
         <v>50</v>
       </c>
       <c r="Y58" s="10">
-        <v>236.05454545454546</v>
+        <v>224.40909090909091</v>
       </c>
       <c r="Z58" s="10">
-        <v>183.55454545454546</v>
+        <v>190.40909090909091</v>
       </c>
       <c r="AA58">
         <v>1</v>
@@ -4699,7 +4726,7 @@
         <v>0.17</v>
       </c>
       <c r="D59" s="5">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E59" s="5">
         <v>0.71</v>
@@ -4715,7 +4742,7 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" si="0"/>
-        <v>228.45454545454544</v>
+        <v>233.45454545454544</v>
       </c>
       <c r="J59" s="10">
         <f t="shared" si="1"/>
@@ -4725,34 +4752,34 @@
         <v>1</v>
       </c>
       <c r="Q59" t="str">
-        <v>Rossy</v>
+        <v>Ethan</v>
       </c>
       <c r="R59" s="11">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="S59" s="11">
         <v>0.18</v>
       </c>
       <c r="T59" s="10">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="U59" s="11">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="V59" s="10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W59" t="str">
         <v>シーカー</v>
       </c>
       <c r="X59">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y59" s="10">
-        <v>225.85454545454542</v>
+        <v>263.5090909090909</v>
       </c>
       <c r="Z59" s="10">
-        <v>181.35454545454542</v>
+        <v>188.50909090909093</v>
       </c>
       <c r="AA59">
         <v>1</v>
@@ -4795,34 +4822,34 @@
         <v>1</v>
       </c>
       <c r="Q60" t="str">
-        <v>Sayonara</v>
+        <v>d4v41</v>
       </c>
       <c r="R60" s="11">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="S60" s="11">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="T60" s="10">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="U60" s="11">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="V60" s="10">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="W60" t="str">
         <v>シーカー</v>
       </c>
       <c r="X60">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y60" s="10">
-        <v>225.6090909090909</v>
+        <v>223.42727272727271</v>
       </c>
       <c r="Z60" s="10">
-        <v>181.1090909090909</v>
+        <v>188.42727272727271</v>
       </c>
       <c r="AA60">
         <v>1</v>
@@ -4865,34 +4892,34 @@
         <v>1</v>
       </c>
       <c r="Q61" t="str">
-        <v>keiko</v>
+        <v>CHICHOO</v>
       </c>
       <c r="R61" s="11">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="S61" s="11">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="T61" s="10">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="U61" s="11">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="V61" s="10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="W61" t="str">
         <v>スモーカー</v>
       </c>
       <c r="X61">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Y61" s="10">
-        <v>225.6090909090909</v>
+        <v>227.85454545454547</v>
       </c>
       <c r="Z61" s="10">
-        <v>181.1090909090909</v>
+        <v>187.85454545454547</v>
       </c>
       <c r="AA61">
         <v>1</v>
@@ -4935,34 +4962,34 @@
         <v>1</v>
       </c>
       <c r="Q62" t="str">
-        <v>skuba</v>
+        <v>IbarakiNinja</v>
       </c>
       <c r="R62" s="11">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S62" s="11">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="T62" s="10">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="U62" s="11">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="V62" s="10">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="W62" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X62">
         <v>50</v>
       </c>
       <c r="Y62" s="10">
-        <v>228.45454545454544</v>
+        <v>242.37272727272727</v>
       </c>
       <c r="Z62" s="10">
-        <v>180.95454545454544</v>
+        <v>187.37272727272727</v>
       </c>
       <c r="AA62">
         <v>1</v>
@@ -5005,34 +5032,34 @@
         <v>1</v>
       </c>
       <c r="Q63" t="str">
-        <v>Verno</v>
+        <v>Laz</v>
       </c>
       <c r="R63" s="11">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="S63" s="11">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="T63" s="10">
+        <v>70</v>
+      </c>
+      <c r="U63" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V63" s="10">
         <v>86</v>
       </c>
-      <c r="U63" s="11">
-        <v>0.7</v>
-      </c>
-      <c r="V63" s="10">
-        <v>95</v>
-      </c>
       <c r="W63" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X63">
         <v>80</v>
       </c>
       <c r="Y63" s="10">
-        <v>223.88181818181818</v>
+        <v>221.3909090909091</v>
       </c>
       <c r="Z63" s="10">
-        <v>180.88181818181818</v>
+        <v>186.3909090909091</v>
       </c>
       <c r="AA63">
         <v>1</v>
@@ -5075,34 +5102,34 @@
         <v>1</v>
       </c>
       <c r="Q64" t="str">
-        <v>Furina</v>
+        <v>leaf</v>
       </c>
       <c r="R64" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.38</v>
       </c>
       <c r="S64" s="11">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="T64" s="10">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="U64" s="11">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
       <c r="V64" s="10">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="W64" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X64">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Y64" s="10">
-        <v>249.83636363636361</v>
+        <v>229.36363636363637</v>
       </c>
       <c r="Z64" s="10">
-        <v>175.33636363636361</v>
+        <v>184.86363636363637</v>
       </c>
       <c r="AA64">
         <v>1</v>
@@ -5145,34 +5172,34 @@
         <v>1</v>
       </c>
       <c r="Q65" t="str">
-        <v>nAts</v>
+        <v>eggsterr</v>
       </c>
       <c r="R65" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="S65" s="11">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="T65" s="10">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="U65" s="11">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="V65" s="10">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="W65" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X65">
         <v>50</v>
       </c>
       <c r="Y65" s="10">
-        <v>237.10000000000002</v>
+        <v>228.58181818181816</v>
       </c>
       <c r="Z65" s="10">
-        <v>174.6</v>
+        <v>184.58181818181816</v>
       </c>
       <c r="AA65">
         <v>1</v>
@@ -5215,34 +5242,34 @@
         <v>1</v>
       </c>
       <c r="Q66" t="str">
-        <v>trent</v>
+        <v>Mazino</v>
       </c>
       <c r="R66" s="11">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="S66" s="11">
         <v>0.18</v>
       </c>
       <c r="T66" s="10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="U66" s="11">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="V66" s="10">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="W66" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X66">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Y66" s="10">
-        <v>234.5363636363636</v>
+        <v>233.82727272727274</v>
       </c>
       <c r="Z66" s="10">
-        <v>174.5363636363636</v>
+        <v>183.82727272727274</v>
       </c>
       <c r="AA66">
         <v>1</v>
@@ -5253,19 +5280,19 @@
         <v>80</v>
       </c>
       <c r="B67" s="5">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="C67" s="5">
         <v>0.2</v>
       </c>
       <c r="D67" s="5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E67" s="5">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F67" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G67" t="s">
         <v>16</v>
@@ -5274,45 +5301,45 @@
         <v>40</v>
       </c>
       <c r="I67" s="4">
-        <f t="shared" ref="I67:I79" si="2">B67*130+(C67)*170+(D67/2)+(E67-0.2)*130+(F67/2.2)</f>
-        <v>241.40909090909091</v>
+        <f t="shared" ref="I67:I88" si="2">B67*130+(C67)*170+(D67/2)+(E67-0.2)*130+(F67/2.2)</f>
+        <v>270.45454545454544</v>
       </c>
       <c r="J67" s="10">
-        <f t="shared" ref="J67:J79" si="3">B67*130+(C67)*170+(E67-0.2)*130+(F67/2.2)</f>
-        <v>211.40909090909091</v>
+        <f t="shared" ref="J67:J88" si="3">B67*130+(C67)*170+(E67-0.2)*130+(F67/2.2)</f>
+        <v>235.45454545454544</v>
       </c>
       <c r="K67">
         <v>1</v>
       </c>
       <c r="Q67" t="str">
-        <v>Rb</v>
+        <v>Lysoar</v>
       </c>
       <c r="R67" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="S67" s="11">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="T67" s="10">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="U67" s="11">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V67" s="10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W67" t="str">
         <v>スモーカー</v>
       </c>
       <c r="X67">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y67" s="10">
-        <v>229.26363636363635</v>
+        <v>236.05454545454546</v>
       </c>
       <c r="Z67" s="10">
-        <v>174.26363636363635</v>
+        <v>183.55454545454546</v>
       </c>
       <c r="AA67">
         <v>1</v>
@@ -5355,34 +5382,34 @@
         <v>1</v>
       </c>
       <c r="Q68" t="str">
-        <v>Brawk</v>
+        <v>Rossy</v>
       </c>
       <c r="R68" s="11">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="S68" s="11">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="T68" s="10">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U68" s="11">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="V68" s="10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="W68" t="str">
         <v>シーカー</v>
       </c>
       <c r="X68">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Y68" s="10">
-        <v>218.98181818181817</v>
+        <v>225.85454545454542</v>
       </c>
       <c r="Z68" s="10">
-        <v>173.98181818181817</v>
+        <v>181.35454545454542</v>
       </c>
       <c r="AA68">
         <v>1</v>
@@ -5393,19 +5420,19 @@
         <v>82</v>
       </c>
       <c r="B69" s="5">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="C69" s="5">
         <v>0.17</v>
       </c>
       <c r="D69" s="5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E69" s="5">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="F69" s="4">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G69" t="s">
         <v>16</v>
@@ -5415,44 +5442,44 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" si="2"/>
-        <v>265.26363636363641</v>
+        <v>274.71818181818185</v>
       </c>
       <c r="J69" s="10">
         <f t="shared" si="3"/>
-        <v>220.26363636363641</v>
+        <v>232.21818181818185</v>
       </c>
       <c r="K69">
         <v>1</v>
       </c>
       <c r="Q69" t="str">
-        <v>C0M</v>
+        <v>Sayonara</v>
       </c>
       <c r="R69" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="S69" s="11">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="T69" s="10">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="U69" s="11">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="V69" s="10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="W69" t="str">
         <v>シーカー</v>
       </c>
       <c r="X69">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Y69" s="10">
-        <v>230.4818181818182</v>
+        <v>228.6090909090909</v>
       </c>
       <c r="Z69" s="10">
-        <v>170.48181818181817</v>
+        <v>181.1090909090909</v>
       </c>
       <c r="AA69">
         <v>1</v>
@@ -5495,34 +5522,34 @@
         <v>1</v>
       </c>
       <c r="Q70" t="str">
-        <v>SugarZ3ro</v>
+        <v>keiko</v>
       </c>
       <c r="R70" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.31</v>
       </c>
       <c r="S70" s="11">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="T70" s="10">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="U70" s="11">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="V70" s="10">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="W70" t="str">
         <v>スモーカー</v>
       </c>
       <c r="X70">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Y70" s="10">
-        <v>229.07272727272726</v>
+        <v>225.6090909090909</v>
       </c>
       <c r="Z70" s="10">
-        <v>169.07272727272726</v>
+        <v>181.1090909090909</v>
       </c>
       <c r="AA70">
         <v>1</v>
@@ -5565,22 +5592,22 @@
         <v>1</v>
       </c>
       <c r="Q71" t="str">
-        <v>Mako</v>
+        <v>skuba</v>
       </c>
       <c r="R71" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="S71" s="11">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="T71" s="10">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="U71" s="11">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="V71" s="10">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="W71" t="str">
         <v>スモーカー</v>
@@ -5589,10 +5616,10 @@
         <v>50</v>
       </c>
       <c r="Y71" s="10">
-        <v>227.23636363636362</v>
+        <v>233.45454545454544</v>
       </c>
       <c r="Z71" s="10">
-        <v>167.23636363636362</v>
+        <v>180.95454545454544</v>
       </c>
       <c r="AA71">
         <v>1</v>
@@ -5636,34 +5663,34 @@
       </c>
       <c r="P72" s="10"/>
       <c r="Q72" s="10" t="str">
-        <v>F0rsakeN</v>
+        <v>Verno</v>
       </c>
       <c r="R72" s="11">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="S72" s="11">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="T72" s="10">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="U72" s="11">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="V72" s="10">
         <v>95</v>
       </c>
       <c r="W72" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X72">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Y72" s="10">
-        <v>228.28181818181818</v>
+        <v>223.88181818181818</v>
       </c>
       <c r="Z72" s="10">
-        <v>165.78181818181818</v>
+        <v>180.88181818181818</v>
       </c>
       <c r="AA72">
         <v>1</v>
@@ -5707,34 +5734,34 @@
       </c>
       <c r="P73" s="10"/>
       <c r="Q73" s="10" t="str">
-        <v>crashies</v>
+        <v>Rb</v>
       </c>
       <c r="R73" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S73" s="11">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="T73" s="10">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="U73" s="11">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="V73" s="10">
         <v>80</v>
       </c>
       <c r="W73" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X73">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="Y73" s="10">
-        <v>234.06363636363636</v>
+        <v>231.86363636363637</v>
       </c>
       <c r="Z73" s="10">
-        <v>164.06363636363636</v>
+        <v>176.86363636363637</v>
       </c>
       <c r="AA73">
         <v>1</v>
@@ -5745,16 +5772,16 @@
         <v>87</v>
       </c>
       <c r="B74" s="5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C74" s="5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D74" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E74">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="F74" s="4">
         <v>80</v>
@@ -5763,49 +5790,49 @@
         <v>14</v>
       </c>
       <c r="H74">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I74" s="4">
         <f t="shared" si="2"/>
-        <v>277.86363636363637</v>
+        <v>253.86363636363637</v>
       </c>
       <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v>227.86363636363637</v>
+        <v>193.86363636363637</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" s="10"/>
       <c r="Q74" s="10" t="str">
-        <v>Boostio</v>
+        <v>Furina</v>
       </c>
       <c r="R74" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S74" s="11">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="T74" s="10">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="U74" s="11">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="V74" s="10">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="W74" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X74">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="Y74" s="10">
-        <v>226.93636363636364</v>
+        <v>249.83636363636361</v>
       </c>
       <c r="Z74" s="10">
-        <v>162.93636363636364</v>
+        <v>175.33636363636361</v>
       </c>
       <c r="AA74">
         <v>1</v>
@@ -5848,34 +5875,34 @@
         <v>1</v>
       </c>
       <c r="Q75" t="str">
-        <v>Jamppi</v>
+        <v>nAts</v>
       </c>
       <c r="R75" s="11">
-        <v>0.27</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S75" s="11">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="T75" s="10">
         <v>125</v>
       </c>
       <c r="U75" s="11">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="V75" s="10">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="W75" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X75">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y75" s="10">
-        <v>224.13636363636363</v>
+        <v>237.10000000000002</v>
       </c>
       <c r="Z75" s="10">
-        <v>161.63636363636363</v>
+        <v>174.6</v>
       </c>
       <c r="AA75">
         <v>1</v>
@@ -5886,7 +5913,7 @@
         <v>89</v>
       </c>
       <c r="B76" s="5">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="C76" s="5">
         <v>0.2</v>
@@ -5895,7 +5922,7 @@
         <v>85</v>
       </c>
       <c r="E76" s="5">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="F76" s="4">
         <v>150</v>
@@ -5908,44 +5935,44 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" si="2"/>
-        <v>261.68181818181819</v>
+        <v>270.78181818181821</v>
       </c>
       <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v>219.18181818181819</v>
+        <v>228.28181818181821</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="str">
-        <v>stax</v>
+        <v>trent</v>
       </c>
       <c r="R76" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="S76" s="11">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="T76" s="10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="U76" s="11">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V76" s="10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="W76" t="str">
-        <v>フラッシュ</v>
+        <v>シーカー</v>
       </c>
       <c r="X76">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Y76" s="10">
-        <v>225.66363636363633</v>
+        <v>234.5363636363636</v>
       </c>
       <c r="Z76" s="10">
-        <v>160.66363636363636</v>
+        <v>174.5363636363636</v>
       </c>
       <c r="AA76">
         <v>1</v>
@@ -5988,34 +6015,34 @@
         <v>1</v>
       </c>
       <c r="Q77" t="str">
-        <v>valyn</v>
+        <v>Brawk</v>
       </c>
       <c r="R77" s="11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="S77" s="11">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="T77" s="10">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="U77" s="11">
-        <v>0.64</v>
+        <v>0.69</v>
       </c>
       <c r="V77" s="10">
         <v>95</v>
       </c>
       <c r="W77" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X77">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="Y77" s="10">
-        <v>226.28181818181821</v>
+        <v>218.98181818181817</v>
       </c>
       <c r="Z77" s="10">
-        <v>156.28181818181818</v>
+        <v>173.98181818181817</v>
       </c>
       <c r="AA77">
         <v>1</v>
@@ -6058,34 +6085,34 @@
         <v>1</v>
       </c>
       <c r="Q78" t="str">
-        <v>Boaster</v>
+        <v>C0M</v>
       </c>
       <c r="R78" s="11">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S78" s="11">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="T78" s="10">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="U78" s="11">
-        <v>0.62</v>
+        <v>0.69</v>
       </c>
       <c r="V78" s="10">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W78" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X78">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Y78" s="10">
-        <v>227.13636363636363</v>
+        <v>230.4818181818182</v>
       </c>
       <c r="Z78" s="10">
-        <v>144.63636363636363</v>
+        <v>170.48181818181817</v>
       </c>
       <c r="AA78">
         <v>1</v>
@@ -6102,7 +6129,7 @@
         <v>0.23</v>
       </c>
       <c r="D79" s="5">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E79" s="5">
         <v>0.76</v>
@@ -6114,36 +6141,36 @@
         <v>16</v>
       </c>
       <c r="H79" s="4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I79" s="4">
         <f t="shared" si="2"/>
-        <v>248.67272727272729</v>
+        <v>249.67272727272729</v>
       </c>
       <c r="J79" s="10">
         <f t="shared" si="3"/>
         <v>209.67272727272729</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="str">
-        <v>FNS</v>
+        <v>SugarZ3ro</v>
       </c>
       <c r="R79" s="11">
-        <v>0.17</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S79" s="11">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="T79" s="10">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="U79" s="11">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="V79" s="10">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="W79" t="str">
         <v>スモーカー</v>
@@ -6152,391 +6179,643 @@
         <v>40</v>
       </c>
       <c r="Y79" s="10">
-        <v>216.91818181818181</v>
+        <v>229.07272727272726</v>
       </c>
       <c r="Z79" s="10">
+        <v>169.07272727272726</v>
+      </c>
+      <c r="AA79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A80" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="C80" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D80" s="5">
+        <v>105</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="F80" s="4">
+        <v>135</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="4">
+        <v>50</v>
+      </c>
+      <c r="I80" s="4">
+        <f t="shared" si="2"/>
+        <v>259.66363636363639</v>
+      </c>
+      <c r="J80" s="10">
+        <f t="shared" si="3"/>
+        <v>207.16363636363639</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>Mako</v>
+      </c>
+      <c r="R80" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S80" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="T80">
+        <v>120</v>
+      </c>
+      <c r="U80">
+        <v>0.7</v>
+      </c>
+      <c r="V80">
+        <v>85</v>
+      </c>
+      <c r="W80" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X80">
+        <v>50</v>
+      </c>
+      <c r="Y80">
+        <v>227.23636363636362</v>
+      </c>
+      <c r="Z80">
+        <v>167.23636363636362</v>
+      </c>
+      <c r="AA80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A81" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" s="5">
+        <v>0.39</v>
+      </c>
+      <c r="C81" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D81" s="5">
+        <v>80</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="F81" s="4">
+        <v>120</v>
+      </c>
+      <c r="G81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="4">
+        <v>85</v>
+      </c>
+      <c r="I81" s="4">
+        <f t="shared" si="2"/>
+        <v>254.64545454545456</v>
+      </c>
+      <c r="J81" s="10">
+        <f t="shared" si="3"/>
+        <v>214.64545454545456</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>F0rsakeN</v>
+      </c>
+      <c r="R81" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="S81" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="T81">
+        <v>125</v>
+      </c>
+      <c r="U81">
+        <v>0.69</v>
+      </c>
+      <c r="V81">
+        <v>95</v>
+      </c>
+      <c r="W81" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X81">
+        <v>50</v>
+      </c>
+      <c r="Y81">
+        <v>228.28181818181818</v>
+      </c>
+      <c r="Z81">
+        <v>165.78181818181818</v>
+      </c>
+      <c r="AA81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A82" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B82" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C82" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D82" s="5">
+        <v>135</v>
+      </c>
+      <c r="E82" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F82" s="4">
+        <v>115</v>
+      </c>
+      <c r="G82" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="4">
+        <v>65</v>
+      </c>
+      <c r="I82" s="4">
+        <f t="shared" si="2"/>
+        <v>266.27272727272725</v>
+      </c>
+      <c r="J82" s="10">
+        <f t="shared" si="3"/>
+        <v>198.77272727272725</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>crashies</v>
+      </c>
+      <c r="R82" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S82" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="T82">
+        <v>140</v>
+      </c>
+      <c r="U82">
+        <v>0.68</v>
+      </c>
+      <c r="V82">
+        <v>80</v>
+      </c>
+      <c r="W82" t="str">
+        <v>シーカー</v>
+      </c>
+      <c r="X82">
+        <v>45</v>
+      </c>
+      <c r="Y82">
+        <v>234.06363636363636</v>
+      </c>
+      <c r="Z82">
+        <v>164.06363636363636</v>
+      </c>
+      <c r="AA82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A83" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="C83" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D83" s="5">
+        <v>111</v>
+      </c>
+      <c r="E83" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="F83" s="4">
+        <v>111</v>
+      </c>
+      <c r="G83" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" s="4">
+        <v>77</v>
+      </c>
+      <c r="I83" s="4">
+        <f t="shared" si="2"/>
+        <v>260.35454545454547</v>
+      </c>
+      <c r="J83" s="10">
+        <f t="shared" si="3"/>
+        <v>204.85454545454547</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>stax</v>
+      </c>
+      <c r="R83" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S83" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="T83">
+        <v>130</v>
+      </c>
+      <c r="U83">
+        <v>0.69</v>
+      </c>
+      <c r="V83">
+        <v>80</v>
+      </c>
+      <c r="W83" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X83">
+        <v>70</v>
+      </c>
+      <c r="Y83">
+        <v>228.26363636363635</v>
+      </c>
+      <c r="Z83">
+        <v>163.26363636363635</v>
+      </c>
+      <c r="AA83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A84" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="C84" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="D84" s="5">
+        <v>86</v>
+      </c>
+      <c r="E84" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="F84" s="4">
+        <v>170</v>
+      </c>
+      <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="4">
+        <v>110</v>
+      </c>
+      <c r="I84" s="4">
+        <f t="shared" si="2"/>
+        <v>283.47272727272724</v>
+      </c>
+      <c r="J84" s="10">
+        <f t="shared" si="3"/>
+        <v>240.47272727272724</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>Boostio</v>
+      </c>
+      <c r="R84" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S84" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="T84">
+        <v>128</v>
+      </c>
+      <c r="U84">
+        <v>0.68</v>
+      </c>
+      <c r="V84">
+        <v>85</v>
+      </c>
+      <c r="W84" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X84">
+        <v>70</v>
+      </c>
+      <c r="Y84">
+        <v>226.93636363636364</v>
+      </c>
+      <c r="Z84">
+        <v>162.93636363636364</v>
+      </c>
+      <c r="AA84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A85" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C85" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="D85" s="5">
+        <v>119</v>
+      </c>
+      <c r="E85" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="F85" s="4">
+        <v>139</v>
+      </c>
+      <c r="G85" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" s="4">
+        <v>120</v>
+      </c>
+      <c r="I85" s="4">
+        <f t="shared" si="2"/>
+        <v>283.68181818181819</v>
+      </c>
+      <c r="J85" s="10">
+        <f t="shared" si="3"/>
+        <v>224.18181818181819</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="str">
+        <v>Jamppi</v>
+      </c>
+      <c r="R85" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="S85" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="T85">
+        <v>125</v>
+      </c>
+      <c r="U85">
+        <v>0.68</v>
+      </c>
+      <c r="V85">
+        <v>85</v>
+      </c>
+      <c r="W85" t="str">
+        <v>フラッシュ</v>
+      </c>
+      <c r="X85">
+        <v>55</v>
+      </c>
+      <c r="Y85">
+        <v>224.13636363636363</v>
+      </c>
+      <c r="Z85">
+        <v>161.63636363636363</v>
+      </c>
+      <c r="AA85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A86" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="C86" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="D86" s="5">
+        <v>85</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="F86" s="4">
+        <v>155</v>
+      </c>
+      <c r="G86" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" s="4">
+        <v>180</v>
+      </c>
+      <c r="I86" s="4">
+        <f t="shared" si="2"/>
+        <v>284.15454545454543</v>
+      </c>
+      <c r="J86" s="10">
+        <f t="shared" si="3"/>
+        <v>241.65454545454543</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>valyn</v>
+      </c>
+      <c r="R86" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="S86" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="T86">
+        <v>140</v>
+      </c>
+      <c r="U86">
+        <v>0.64</v>
+      </c>
+      <c r="V86">
+        <v>95</v>
+      </c>
+      <c r="W86" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X86">
+        <v>40</v>
+      </c>
+      <c r="Y86">
+        <v>226.28181818181821</v>
+      </c>
+      <c r="Z86">
+        <v>156.28181818181818</v>
+      </c>
+      <c r="AA86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A87" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="C87" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D87" s="5">
+        <v>120</v>
+      </c>
+      <c r="E87" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="F87" s="4">
+        <v>155</v>
+      </c>
+      <c r="G87" t="s">
+        <v>12</v>
+      </c>
+      <c r="H87" s="4">
+        <v>90</v>
+      </c>
+      <c r="I87" s="4">
+        <f t="shared" si="2"/>
+        <v>284.15454545454548</v>
+      </c>
+      <c r="J87" s="10">
+        <f t="shared" si="3"/>
+        <v>224.15454545454548</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>Boaster</v>
+      </c>
+      <c r="R87" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="S87" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="T87">
+        <v>175</v>
+      </c>
+      <c r="U87">
+        <v>0.62</v>
+      </c>
+      <c r="V87">
+        <v>96</v>
+      </c>
+      <c r="W87" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X87">
+        <v>50</v>
+      </c>
+      <c r="Y87">
+        <v>232.13636363636363</v>
+      </c>
+      <c r="Z87">
+        <v>144.63636363636363</v>
+      </c>
+      <c r="AA87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A88" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C88" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D88" s="5">
+        <v>100</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="F88" s="4">
+        <v>135</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" s="4">
+        <v>30</v>
+      </c>
+      <c r="I88" s="4">
+        <f t="shared" si="2"/>
+        <v>262.36363636363637</v>
+      </c>
+      <c r="J88" s="10">
+        <f t="shared" si="3"/>
+        <v>212.36363636363637</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>FNS</v>
+      </c>
+      <c r="R88" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="S88" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="T88">
+        <v>190</v>
+      </c>
+      <c r="U88">
+        <v>0.63</v>
+      </c>
+      <c r="V88">
+        <v>70</v>
+      </c>
+      <c r="W88" t="str">
+        <v>スモーカー</v>
+      </c>
+      <c r="X88">
+        <v>10</v>
+      </c>
+      <c r="Y88">
+        <v>226.91818181818181</v>
+      </c>
+      <c r="Z88">
         <v>131.91818181818181</v>
       </c>
-      <c r="AA79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80" s="10">
-        <v>0</v>
-      </c>
-      <c r="S80" s="10">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="Q81">
-        <v>0</v>
-      </c>
-      <c r="R81" s="10">
-        <v>0</v>
-      </c>
-      <c r="S81" s="10">
-        <v>0</v>
-      </c>
-      <c r="T81">
-        <v>0</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>0</v>
-      </c>
-      <c r="W81">
-        <v>0</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
-      </c>
-      <c r="Z81">
-        <v>0</v>
-      </c>
-      <c r="AA81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82" s="10">
-        <v>0</v>
-      </c>
-      <c r="S82" s="10">
-        <v>0</v>
-      </c>
-      <c r="T82">
-        <v>0</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>0</v>
-      </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82">
-        <v>0</v>
-      </c>
-      <c r="Y82">
-        <v>0</v>
-      </c>
-      <c r="Z82">
-        <v>0</v>
-      </c>
-      <c r="AA82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="Q83">
-        <v>0</v>
-      </c>
-      <c r="R83" s="10">
-        <v>0</v>
-      </c>
-      <c r="S83" s="10">
-        <v>0</v>
-      </c>
-      <c r="T83">
-        <v>0</v>
-      </c>
-      <c r="U83">
-        <v>0</v>
-      </c>
-      <c r="V83">
-        <v>0</v>
-      </c>
-      <c r="W83">
-        <v>0</v>
-      </c>
-      <c r="X83">
-        <v>0</v>
-      </c>
-      <c r="Y83">
-        <v>0</v>
-      </c>
-      <c r="Z83">
-        <v>0</v>
-      </c>
-      <c r="AA83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84" s="10">
-        <v>0</v>
-      </c>
-      <c r="S84" s="10">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
-      </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84">
-        <v>0</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>0</v>
-      </c>
-      <c r="Z84">
-        <v>0</v>
-      </c>
-      <c r="AA84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85" s="10">
-        <v>0</v>
-      </c>
-      <c r="S85" s="10">
-        <v>0</v>
-      </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>0</v>
-      </c>
-      <c r="V85">
-        <v>0</v>
-      </c>
-      <c r="W85">
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <v>0</v>
-      </c>
-      <c r="Z85">
-        <v>0</v>
-      </c>
-      <c r="AA85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="Q86">
-        <v>0</v>
-      </c>
-      <c r="R86" s="10">
-        <v>0</v>
-      </c>
-      <c r="S86" s="10">
-        <v>0</v>
-      </c>
-      <c r="T86">
-        <v>0</v>
-      </c>
-      <c r="U86">
-        <v>0</v>
-      </c>
-      <c r="V86">
-        <v>0</v>
-      </c>
-      <c r="W86">
-        <v>0</v>
-      </c>
-      <c r="X86">
-        <v>0</v>
-      </c>
-      <c r="Y86">
-        <v>0</v>
-      </c>
-      <c r="Z86">
-        <v>0</v>
-      </c>
-      <c r="AA86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87" s="10">
-        <v>0</v>
-      </c>
-      <c r="S87" s="10">
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <v>0</v>
-      </c>
-      <c r="Y87">
-        <v>0</v>
-      </c>
-      <c r="Z87">
-        <v>0</v>
-      </c>
-      <c r="AA87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88" s="10">
-        <v>0</v>
-      </c>
-      <c r="S88" s="10">
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <v>0</v>
-      </c>
-      <c r="U88">
-        <v>0</v>
-      </c>
-      <c r="V88">
-        <v>0</v>
-      </c>
-      <c r="W88">
-        <v>0</v>
-      </c>
-      <c r="X88">
-        <v>0</v>
-      </c>
-      <c r="Y88">
-        <v>0</v>
-      </c>
-      <c r="Z88">
-        <v>0</v>
-      </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:27" ht="15.75" customHeight="1">

--- a/03.game/FPS_chars.xlsx
+++ b/03.game/FPS_chars.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C7C0B08-5788-4A14-8E3D-000699DD905F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3E0BFD-E05D-4263-AEA3-2F2D62408B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="104">
   <si>
     <t>名前</t>
   </si>
@@ -82,6 +82,9 @@
     <t>影響力</t>
   </si>
   <si>
+    <t>調子の波</t>
+  </si>
+  <si>
     <t>総合能力</t>
   </si>
   <si>
@@ -362,6 +365,9 @@
   </si>
   <si>
     <t>trexx</t>
+  </si>
+  <si>
+    <t>mindfreak</t>
   </si>
 </sst>
 </file>
@@ -645,6 +651,7 @@
     <col min="2" max="6" width="12.5703125" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" customWidth="1"/>
     <col min="9" max="10" width="16.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
     <col min="17" max="17" width="14.85546875" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" customWidth="1"/>
     <col min="21" max="21" width="14.28515625" customWidth="1"/>
@@ -679,13 +686,15 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="1"/>
       <c r="N1" s="2"/>
       <c r="O1" s="1"/>
@@ -715,18 +724,18 @@
         <v>7</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="6">
         <v>0.35</v>
@@ -744,60 +753,63 @@
         <v>135</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="4">
         <v>80</v>
       </c>
       <c r="I2" s="4">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4">
         <f>B2*130+(C2)*170+(D2/2)+(E2-0.2)*130+(F2/2.2)</f>
         <v>273.86363636363637</v>
       </c>
-      <c r="J2" s="10">
+      <c r="K2" s="10">
         <f>B2*130+(C2)*170+(E2-0.2)*130+(F2/2.2)</f>
         <v>221.36363636363637</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>1</v>
       </c>
       <c r="Q2" t="str" cm="1">
-        <f t="array" ref="Q2:AA97">_xlfn._xlws.SORT(A2:K97, {10}, {-1})</f>
-        <v>おもこ</v>
+        <f t="array" ref="Q2:AA97">_xlfn._xlws.SORT(A2:K97, {9}, {-1})</f>
+        <v>Aspas</v>
       </c>
       <c r="R2" s="11">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="S2" s="11">
-        <v>0.67</v>
+        <v>0.24</v>
       </c>
       <c r="T2" s="10">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="U2" s="11">
-        <v>0.67</v>
+        <v>0.87</v>
       </c>
       <c r="V2" s="10">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="W2" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X2">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="Y2" s="10">
-        <v>326.05454545454546</v>
+        <v>10</v>
       </c>
       <c r="Z2" s="10">
-        <v>292.55454545454546</v>
+        <v>279.44545454545454</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>234.44545454545451</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="6">
         <v>0.5</v>
@@ -815,59 +827,62 @@
         <v>145</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4">
         <v>150</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" ref="I3:I66" si="0">B3*130+(C3)*170+(D3/2)+(E3-0.2)*130+(F3/2.2)</f>
+        <v>4</v>
+      </c>
+      <c r="J3" s="4">
+        <f t="shared" ref="J3:J66" si="0">B3*130+(C3)*170+(D3/2)+(E3-0.2)*130+(F3/2.2)</f>
         <v>276.5090909090909</v>
       </c>
-      <c r="J3" s="10">
-        <f t="shared" ref="J3:J66" si="1">B3*130+(C3)*170+(E3-0.2)*130+(F3/2.2)</f>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K66" si="1">B3*130+(C3)*170+(E3-0.2)*130+(F3/2.2)</f>
         <v>237.50909090909087</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1</v>
       </c>
       <c r="Q3" t="str">
-        <v>まーやまくん</v>
+        <v>Tortlilyan</v>
       </c>
       <c r="R3" s="11">
-        <v>0.75</v>
+        <v>0.23</v>
       </c>
       <c r="S3" s="11">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="T3" s="10">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="U3" s="11">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V3" s="10">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="W3" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X3">
         <v>50</v>
       </c>
       <c r="Y3" s="10">
-        <v>319.83636363636361</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="10">
-        <v>274.83636363636361</v>
+        <v>319.60909090909092</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>258.10909090909092</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6">
         <v>0.35</v>
@@ -885,59 +900,62 @@
         <v>165</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="4">
         <v>85</v>
       </c>
       <c r="I4" s="4">
+        <v>7</v>
+      </c>
+      <c r="J4" s="4">
         <f t="shared" si="0"/>
         <v>282.2</v>
       </c>
-      <c r="J4" s="10">
+      <c r="K4" s="10">
         <f t="shared" si="1"/>
         <v>249.7</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>1</v>
       </c>
       <c r="Q4" t="str">
-        <v>Tortlilyan</v>
+        <v>eggsterr</v>
       </c>
       <c r="R4" s="11">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="S4" s="11">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="T4" s="10">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="U4" s="11">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="V4" s="10">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="W4" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X4">
         <v>50</v>
       </c>
       <c r="Y4" s="10">
-        <v>319.60909090909092</v>
+        <v>10</v>
       </c>
       <c r="Z4" s="10">
-        <v>258.10909090909092</v>
+        <v>228.58181818181816</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>184.58181818181816</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="7">
         <v>0.27</v>
@@ -955,59 +973,62 @@
         <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="4">
         <v>65</v>
       </c>
       <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
         <f t="shared" si="0"/>
         <v>290.76363636363635</v>
       </c>
-      <c r="J5" s="10">
+      <c r="K5" s="10">
         <f t="shared" si="1"/>
         <v>215.76363636363635</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
       <c r="Q5" t="str">
-        <v>something</v>
+        <v>Lohen</v>
       </c>
       <c r="R5" s="11">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="S5" s="11">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="T5" s="10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="U5" s="11">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="V5" s="10">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="W5" t="str">
         <v>タイガー</v>
       </c>
       <c r="X5">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Y5" s="10">
-        <v>282.2</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="10">
-        <v>249.7</v>
+        <v>270.29090909090905</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <v>235.29090909090908</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="6">
         <v>0.45</v>
@@ -1025,59 +1046,62 @@
         <v>145</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="4">
         <v>60</v>
       </c>
       <c r="I6" s="4">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4">
         <f t="shared" si="0"/>
         <v>268.80909090909086</v>
       </c>
-      <c r="J6" s="10">
+      <c r="K6" s="10">
         <f t="shared" si="1"/>
         <v>238.80909090909088</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>1</v>
       </c>
       <c r="Q6" t="str">
-        <v>cNed</v>
+        <v>IbarakiNinja</v>
       </c>
       <c r="R6" s="11">
-        <v>0.41</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S6" s="11">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="T6" s="10">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="U6" s="11">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="V6" s="10">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="W6" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X6">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="Y6" s="10">
-        <v>284.15454545454543</v>
+        <v>10</v>
       </c>
       <c r="Z6" s="10">
-        <v>241.65454545454543</v>
+        <v>242.37272727272727</v>
       </c>
       <c r="AA6">
-        <v>1</v>
+        <v>187.37272727272727</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="6">
         <v>0.35</v>
@@ -1095,59 +1119,62 @@
         <v>115</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="4">
         <v>90</v>
       </c>
       <c r="I7" s="4">
+        <v>8</v>
+      </c>
+      <c r="J7" s="4">
         <f t="shared" si="0"/>
         <v>255.07272727272726</v>
       </c>
-      <c r="J7" s="10">
+      <c r="K7" s="10">
         <f t="shared" si="1"/>
         <v>210.07272727272726</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
       <c r="Q7" t="str">
-        <v>Katarina</v>
+        <v>Absol</v>
       </c>
       <c r="R7" s="11">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="S7" s="11">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="T7" s="10">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="U7" s="11">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="V7" s="10">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="W7" t="str">
         <v>タイガー</v>
       </c>
       <c r="X7">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="Y7" s="10">
-        <v>283.47272727272724</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="10">
-        <v>240.47272727272724</v>
+        <v>294.75454545454545</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>229.75454545454545</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="7">
         <v>0.2</v>
@@ -1165,59 +1192,62 @@
         <v>96</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4">
         <v>50</v>
       </c>
       <c r="I8" s="4">
+        <v>5</v>
+      </c>
+      <c r="J8" s="4">
         <f t="shared" si="0"/>
         <v>232.13636363636363</v>
       </c>
-      <c r="J8" s="10">
+      <c r="K8" s="10">
         <f t="shared" si="1"/>
         <v>144.63636363636363</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>1</v>
       </c>
       <c r="Q8" t="str">
-        <v>Alfajer</v>
+        <v>Katarina</v>
       </c>
       <c r="R8" s="11">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="S8" s="11">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="T8" s="10">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="U8" s="11">
-        <v>0.91</v>
+        <v>0.81</v>
       </c>
       <c r="V8" s="10">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="W8" t="str">
         <v>タイガー</v>
       </c>
       <c r="X8">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="Y8" s="10">
-        <v>268.80909090909086</v>
+        <v>10</v>
       </c>
       <c r="Z8" s="10">
-        <v>238.80909090909088</v>
+        <v>283.47272727272724</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>240.47272727272724</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="6">
         <v>0.4</v>
@@ -1235,59 +1265,62 @@
         <v>120</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4">
         <v>130</v>
       </c>
       <c r="I9" s="4">
+        <v>10</v>
+      </c>
+      <c r="J9" s="4">
         <f t="shared" si="0"/>
         <v>279.44545454545454</v>
       </c>
-      <c r="J9" s="10">
+      <c r="K9" s="10">
         <f t="shared" si="1"/>
         <v>234.44545454545451</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>1</v>
       </c>
       <c r="Q9" t="str">
-        <v>Demon1</v>
+        <v>SereNa</v>
       </c>
       <c r="R9" s="11">
-        <v>0.5</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S9" s="11">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="T9" s="10">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="U9" s="11">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="V9" s="10">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="W9" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="Y9" s="10">
-        <v>276.5090909090909</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="10">
-        <v>237.50909090909087</v>
+        <v>283.68181818181819</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>224.18181818181819</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6">
         <v>0.27</v>
@@ -1305,59 +1338,62 @@
         <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4">
         <v>50</v>
       </c>
       <c r="I10" s="4">
+        <v>3</v>
+      </c>
+      <c r="J10" s="4">
         <f t="shared" si="0"/>
         <v>228.28181818181818</v>
       </c>
-      <c r="J10" s="10">
+      <c r="K10" s="10">
         <f t="shared" si="1"/>
         <v>165.78181818181818</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>1</v>
       </c>
       <c r="Q10" t="str">
-        <v>Kachina</v>
+        <v>Wo0t</v>
       </c>
       <c r="R10" s="11">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="S10" s="11">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="T10" s="10">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="U10" s="11">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="V10" s="10">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="W10" t="str">
         <v>タイガー</v>
       </c>
       <c r="X10">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Y10" s="10">
-        <v>270.45454545454544</v>
+        <v>9</v>
       </c>
       <c r="Z10" s="10">
-        <v>235.45454545454544</v>
+        <v>244.24545454545452</v>
       </c>
       <c r="AA10">
-        <v>1</v>
+        <v>205.24545454545452</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6">
         <v>0.3</v>
@@ -1375,59 +1411,62 @@
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="4">
         <v>50</v>
       </c>
       <c r="I11" s="4">
+        <v>4</v>
+      </c>
+      <c r="J11" s="4">
         <f t="shared" si="0"/>
         <v>224.40909090909091</v>
       </c>
-      <c r="J11" s="10">
+      <c r="K11" s="10">
         <f t="shared" si="1"/>
         <v>190.40909090909091</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1</v>
       </c>
       <c r="Q11" t="str">
-        <v>Zest</v>
+        <v>ZMJKK</v>
       </c>
       <c r="R11" s="11">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="S11" s="11">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="T11" s="10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="U11" s="11">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="V11" s="10">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="W11" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Y11" s="10">
-        <v>272.8</v>
+        <v>9</v>
       </c>
       <c r="Z11" s="10">
-        <v>235.3</v>
+        <v>234.88181818181818</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <v>202.38181818181818</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="7">
         <v>0.35</v>
@@ -1445,59 +1484,62 @@
         <v>105</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="4">
         <v>40</v>
       </c>
       <c r="I12" s="4">
+        <v>5</v>
+      </c>
+      <c r="J12" s="4">
         <f t="shared" si="0"/>
         <v>223.42727272727271</v>
       </c>
-      <c r="J12" s="10">
+      <c r="K12" s="10">
         <f t="shared" si="1"/>
         <v>188.42727272727271</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>1</v>
       </c>
       <c r="Q12" t="str">
-        <v>Lohen</v>
+        <v>TenZ</v>
       </c>
       <c r="R12" s="11">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="S12" s="11">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="T12" s="10">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="U12" s="11">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="V12" s="10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W12" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X12">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="Y12" s="10">
-        <v>270.29090909090905</v>
+        <v>9</v>
       </c>
       <c r="Z12" s="10">
-        <v>235.29090909090908</v>
+        <v>268.34545454545457</v>
       </c>
       <c r="AA12">
-        <v>1</v>
+        <v>215.84545454545454</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="6">
         <v>0.4</v>
@@ -1515,59 +1557,62 @@
         <v>105</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" s="4">
         <v>60</v>
       </c>
       <c r="I13" s="4">
+        <v>6</v>
+      </c>
+      <c r="J13" s="4">
         <f t="shared" si="0"/>
         <v>234.42727272727271</v>
       </c>
-      <c r="J13" s="10">
+      <c r="K13" s="10">
         <f t="shared" si="1"/>
         <v>200.92727272727271</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>1</v>
       </c>
       <c r="Q13" t="str">
-        <v>Aspas</v>
+        <v>Rossy</v>
       </c>
       <c r="R13" s="11">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="S13" s="11">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="T13" s="10">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U13" s="11">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="V13" s="10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="W13" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X13">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Y13" s="10">
-        <v>279.44545454545454</v>
+        <v>9</v>
       </c>
       <c r="Z13" s="10">
-        <v>234.44545454545451</v>
+        <v>225.85454545454542</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>181.35454545454542</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="6">
         <v>0.28000000000000003</v>
@@ -1585,59 +1630,62 @@
         <v>135</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="4">
         <v>75</v>
       </c>
       <c r="I14" s="4">
+        <v>8</v>
+      </c>
+      <c r="J14" s="4">
         <f t="shared" si="0"/>
         <v>258.06363636363636</v>
       </c>
-      <c r="J14" s="10">
+      <c r="K14" s="10">
         <f t="shared" si="1"/>
         <v>211.56363636363636</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1</v>
       </c>
       <c r="Q14" t="str">
-        <v>Tartaglia</v>
+        <v>CHICHOO</v>
       </c>
       <c r="R14" s="11">
-        <v>0.55000000000000004</v>
+        <v>0.32</v>
       </c>
       <c r="S14" s="11">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="T14" s="10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" s="11">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="V14" s="10">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="W14" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Y14" s="10">
-        <v>270.28181818181821</v>
+        <v>9</v>
       </c>
       <c r="Z14" s="10">
-        <v>232.78181818181821</v>
+        <v>227.85454545454547</v>
       </c>
       <c r="AA14">
-        <v>1</v>
+        <v>187.85454545454547</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6">
         <v>0.26</v>
@@ -1655,59 +1703,62 @@
         <v>95</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="4">
         <v>40</v>
       </c>
       <c r="I15" s="4">
+        <v>5</v>
+      </c>
+      <c r="J15" s="4">
         <f t="shared" si="0"/>
         <v>226.28181818181821</v>
       </c>
-      <c r="J15" s="10">
+      <c r="K15" s="10">
         <f t="shared" si="1"/>
         <v>156.28181818181818</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>1</v>
       </c>
       <c r="Q15" t="str">
-        <v>Canezerra</v>
+        <v>nAts</v>
       </c>
       <c r="R15" s="11">
-        <v>0.45</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S15" s="11">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T15" s="10">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="U15" s="11">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="V15" s="10">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="W15" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Y15" s="10">
-        <v>274.71818181818185</v>
+        <v>9</v>
       </c>
       <c r="Z15" s="10">
-        <v>232.21818181818185</v>
+        <v>237.10000000000002</v>
       </c>
       <c r="AA15">
-        <v>1</v>
+        <v>174.6</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="7">
         <v>0.3</v>
@@ -1725,59 +1776,62 @@
         <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="4">
         <v>55</v>
       </c>
       <c r="I16" s="4">
+        <v>4</v>
+      </c>
+      <c r="J16" s="4">
         <f t="shared" si="0"/>
         <v>263.5090909090909</v>
       </c>
-      <c r="J16" s="10">
+      <c r="K16" s="10">
         <f t="shared" si="1"/>
         <v>188.50909090909093</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>1</v>
       </c>
       <c r="Q16" t="str">
-        <v>WoohyuN</v>
+        <v>C0M</v>
       </c>
       <c r="R16" s="11">
-        <v>0.46</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S16" s="11">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="T16" s="10">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="U16" s="11">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="V16" s="10">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="W16" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y16" s="10">
-        <v>270.78181818181821</v>
+        <v>9</v>
       </c>
       <c r="Z16" s="10">
-        <v>228.28181818181821</v>
+        <v>230.4818181818182</v>
       </c>
       <c r="AA16">
-        <v>1</v>
+        <v>170.48181818181817</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6">
         <v>0.4</v>
@@ -1795,59 +1849,62 @@
         <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="4">
         <v>75</v>
       </c>
       <c r="I17" s="4">
+        <v>9</v>
+      </c>
+      <c r="J17" s="4">
         <f t="shared" si="0"/>
         <v>244.24545454545452</v>
       </c>
-      <c r="J17" s="10">
+      <c r="K17" s="10">
         <f t="shared" si="1"/>
         <v>205.24545454545452</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1</v>
       </c>
       <c r="Q17" t="str">
-        <v>SereNa</v>
+        <v>WsLeo</v>
       </c>
       <c r="R17" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.36</v>
       </c>
       <c r="S17" s="11">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="T17" s="10">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="U17" s="11">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="V17" s="10">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="W17" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X17">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="Y17" s="10">
-        <v>283.68181818181819</v>
+        <v>9</v>
       </c>
       <c r="Z17" s="10">
-        <v>224.18181818181819</v>
+        <v>259.26363636363635</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>194.26363636363635</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6">
         <v>0.35</v>
@@ -1865,59 +1922,62 @@
         <v>100</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="4">
         <v>70</v>
       </c>
       <c r="I18" s="4">
+        <v>7</v>
+      </c>
+      <c r="J18" s="4">
         <f t="shared" si="0"/>
         <v>255.25454545454545</v>
       </c>
-      <c r="J18" s="10">
+      <c r="K18" s="10">
         <f t="shared" si="1"/>
         <v>197.75454545454545</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>1</v>
       </c>
       <c r="Q18" t="str">
-        <v>soulcas</v>
+        <v>Zest</v>
       </c>
       <c r="R18" s="11">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="S18" s="11">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="T18" s="10">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="U18" s="11">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="V18" s="10">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="W18" t="str">
-        <v>フラッシュ</v>
+        <v>シーカー</v>
       </c>
       <c r="X18">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Y18" s="10">
-        <v>284.15454545454548</v>
+        <v>9</v>
       </c>
       <c r="Z18" s="10">
-        <v>224.15454545454548</v>
+        <v>272.8</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>235.3</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6">
         <v>0.35</v>
@@ -1935,59 +1995,62 @@
         <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="4">
         <v>90</v>
       </c>
       <c r="I19" s="4">
+        <v>7</v>
+      </c>
+      <c r="J19" s="4">
         <f t="shared" si="0"/>
         <v>236.8</v>
       </c>
-      <c r="J19" s="10">
+      <c r="K19" s="10">
         <f t="shared" si="1"/>
         <v>201.8</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>1</v>
       </c>
       <c r="Q19" t="str">
-        <v>Primmie</v>
+        <v>Derke</v>
       </c>
       <c r="R19" s="11">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="S19" s="11">
         <v>0.24</v>
       </c>
       <c r="T19" s="10">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="U19" s="11">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="V19" s="10">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="W19" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X19">
         <v>90</v>
       </c>
       <c r="Y19" s="10">
-        <v>252.64545454545453</v>
+        <v>8</v>
       </c>
       <c r="Z19" s="10">
-        <v>223.14545454545456</v>
+        <v>255.07272727272726</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>210.07272727272726</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="6">
         <v>0.35</v>
@@ -2005,59 +2068,62 @@
         <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" s="4">
         <v>80</v>
       </c>
       <c r="I20" s="4">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4">
         <f t="shared" si="0"/>
         <v>223.88181818181818</v>
       </c>
-      <c r="J20" s="10">
+      <c r="K20" s="10">
         <f t="shared" si="1"/>
         <v>180.88181818181818</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>1</v>
       </c>
       <c r="Q20" t="str">
-        <v>Chronicle</v>
+        <v>jawgemo</v>
       </c>
       <c r="R20" s="11">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S20" s="11">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="T20" s="10">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="U20" s="11">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="V20" s="10">
         <v>135</v>
       </c>
       <c r="W20" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X20">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Y20" s="10">
-        <v>273.86363636363637</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="10">
-        <v>221.36363636363637</v>
+        <v>258.06363636363636</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>211.56363636363636</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="7">
         <v>0.33</v>
@@ -2075,59 +2141,62 @@
         <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21" s="4">
         <v>80</v>
       </c>
       <c r="I21" s="4">
+        <v>5</v>
+      </c>
+      <c r="J21" s="4">
         <f t="shared" si="0"/>
         <v>228.6090909090909</v>
       </c>
-      <c r="J21" s="10">
+      <c r="K21" s="10">
         <f t="shared" si="1"/>
         <v>181.1090909090909</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>1</v>
       </c>
       <c r="Q21" t="str">
-        <v>Flashback</v>
+        <v>Meteor</v>
       </c>
       <c r="R21" s="11">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="S21" s="11">
-        <v>0.22</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="T21" s="10">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="U21" s="11">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="V21" s="10">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="W21" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X21">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y21" s="10">
-        <v>259.4909090909091</v>
+        <v>8</v>
       </c>
       <c r="Z21" s="10">
-        <v>219.9909090909091</v>
+        <v>252.4818181818182</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>215.9818181818182</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="6">
         <v>0.27</v>
@@ -2145,59 +2214,62 @@
         <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22" s="4">
         <v>55</v>
       </c>
       <c r="I22" s="4">
+        <v>3</v>
+      </c>
+      <c r="J22" s="4">
         <f t="shared" si="0"/>
         <v>224.13636363636363</v>
       </c>
-      <c r="J22" s="10">
+      <c r="K22" s="10">
         <f t="shared" si="1"/>
         <v>161.63636363636363</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>1</v>
       </c>
       <c r="Q22" t="str">
-        <v>Meteor</v>
+        <v>keiko</v>
       </c>
       <c r="R22" s="11">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="S22" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.19</v>
       </c>
       <c r="T22" s="10">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="U22" s="11">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V22" s="10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="W22" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X22">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y22" s="10">
-        <v>252.4818181818182</v>
+        <v>8</v>
       </c>
       <c r="Z22" s="10">
-        <v>215.9818181818182</v>
+        <v>225.6090909090909</v>
       </c>
       <c r="AA22">
-        <v>1</v>
+        <v>181.1090909090909</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="7">
         <v>0.28000000000000003</v>
@@ -2215,59 +2287,62 @@
         <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="4">
         <v>70</v>
       </c>
       <c r="I23" s="4">
+        <v>6</v>
+      </c>
+      <c r="J23" s="4">
         <f t="shared" si="0"/>
         <v>226.93636363636364</v>
       </c>
-      <c r="J23" s="10">
+      <c r="K23" s="10">
         <f t="shared" si="1"/>
         <v>162.93636363636364</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>1</v>
       </c>
       <c r="Q23" t="str">
-        <v>TenZ</v>
+        <v>Zekken</v>
       </c>
       <c r="R23" s="11">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="S23" s="11">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="T23" s="10">
+        <v>85</v>
+      </c>
+      <c r="U23" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="V23" s="10">
         <v>105</v>
       </c>
-      <c r="U23" s="11">
-        <v>0.76</v>
-      </c>
-      <c r="V23" s="10">
-        <v>120</v>
-      </c>
       <c r="W23" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X23">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="Y23" s="10">
-        <v>268.34545454545457</v>
+        <v>8</v>
       </c>
       <c r="Z23" s="10">
-        <v>215.84545454545454</v>
+        <v>243.22727272727272</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <v>200.72727272727272</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="6">
         <v>0.47</v>
@@ -2285,59 +2360,62 @@
         <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" s="4">
         <v>90</v>
       </c>
       <c r="I24" s="4">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4">
         <f t="shared" si="0"/>
         <v>252.64545454545453</v>
       </c>
-      <c r="J24" s="10">
+      <c r="K24" s="10">
         <f t="shared" si="1"/>
         <v>223.14545454545456</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>1</v>
       </c>
       <c r="Q24" t="str">
-        <v>Leo</v>
+        <v>Smoggy</v>
       </c>
       <c r="R24" s="11">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="S24" s="11">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="T24" s="10">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="U24" s="11">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="V24" s="10">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="W24" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X24">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Y24" s="10">
-        <v>290.76363636363635</v>
+        <v>8</v>
       </c>
       <c r="Z24" s="10">
-        <v>215.76363636363635</v>
+        <v>242.64545454545453</v>
       </c>
       <c r="AA24">
-        <v>1</v>
+        <v>205.14545454545453</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="8">
         <v>0.23</v>
@@ -2355,59 +2433,62 @@
         <v>156</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="4">
         <v>50</v>
       </c>
       <c r="I25" s="4">
+        <v>10</v>
+      </c>
+      <c r="J25" s="4">
         <f t="shared" si="0"/>
         <v>319.60909090909092</v>
       </c>
-      <c r="J25" s="10">
+      <c r="K25" s="10">
         <f t="shared" si="1"/>
         <v>258.10909090909092</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>0</v>
       </c>
       <c r="Q25" t="str">
-        <v>t3xture</v>
+        <v>Nanasaki</v>
       </c>
       <c r="R25" s="11">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="S25" s="11">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="T25" s="10">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="U25" s="11">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="V25" s="10">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="W25" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X25">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y25" s="10">
-        <v>261.38181818181818</v>
+        <v>8</v>
       </c>
       <c r="Z25" s="10">
-        <v>214.88181818181818</v>
+        <v>253.86363636363637</v>
       </c>
       <c r="AA25">
-        <v>1</v>
+        <v>193.86363636363637</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="8">
         <v>0.75</v>
@@ -2425,59 +2506,62 @@
         <v>140</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="4">
         <v>50</v>
       </c>
       <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
         <f t="shared" si="0"/>
         <v>319.83636363636361</v>
       </c>
-      <c r="J26" s="10">
+      <c r="K26" s="10">
         <f t="shared" si="1"/>
         <v>274.83636363636361</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>0</v>
       </c>
       <c r="Q26" t="str">
-        <v>marteen</v>
+        <v>WoohyuN</v>
       </c>
       <c r="R26" s="11">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="S26" s="11">
         <v>0.2</v>
       </c>
       <c r="T26" s="10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U26" s="11">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="V26" s="10">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="W26" t="str">
         <v>タイガー</v>
       </c>
       <c r="X26">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="Y26" s="10">
-        <v>254.64545454545456</v>
+        <v>8</v>
       </c>
       <c r="Z26" s="10">
-        <v>214.64545454545456</v>
+        <v>270.78181818181821</v>
       </c>
       <c r="AA26">
-        <v>1</v>
+        <v>228.28181818181821</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="8">
         <v>0.67</v>
@@ -2495,59 +2579,62 @@
         <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" s="4">
         <v>67</v>
       </c>
       <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
         <f t="shared" si="0"/>
         <v>326.05454545454546</v>
       </c>
-      <c r="J27" s="10">
+      <c r="K27" s="10">
         <f t="shared" si="1"/>
         <v>292.55454545454546</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>0</v>
       </c>
       <c r="Q27" t="str">
-        <v>Jean</v>
+        <v>mindfreak</v>
       </c>
       <c r="R27" s="11">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="S27" s="11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="T27" s="10">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="U27" s="11">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="V27" s="10">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="W27" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y27" s="10">
-        <v>269.86363636363637</v>
+        <v>8</v>
       </c>
       <c r="Z27" s="10">
-        <v>212.36363636363637</v>
+        <v>270.45454545454544</v>
       </c>
       <c r="AA27">
-        <v>1</v>
+        <v>200.45454545454544</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="8">
         <v>0.37</v>
@@ -2565,59 +2652,62 @@
         <v>95</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H28" s="4">
         <v>75</v>
       </c>
       <c r="I28" s="4">
+        <v>8</v>
+      </c>
+      <c r="J28" s="4">
         <f t="shared" si="0"/>
         <v>252.4818181818182</v>
       </c>
-      <c r="J28" s="10">
+      <c r="K28" s="10">
         <f t="shared" si="1"/>
         <v>215.9818181818182</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>1</v>
       </c>
       <c r="Q28" t="str">
-        <v>trexx</v>
+        <v>something</v>
       </c>
       <c r="R28" s="11">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="S28" s="11">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="T28" s="10">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U28" s="11">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="V28" s="10">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="W28" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X28">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="Y28" s="10">
-        <v>262.36363636363637</v>
+        <v>7</v>
       </c>
       <c r="Z28" s="10">
-        <v>212.36363636363637</v>
+        <v>282.2</v>
       </c>
       <c r="AA28">
-        <v>1</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="8">
         <v>0.4</v>
@@ -2635,59 +2725,62 @@
         <v>86</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="4">
         <v>80</v>
       </c>
       <c r="I29" s="4">
+        <v>6</v>
+      </c>
+      <c r="J29" s="4">
         <f t="shared" si="0"/>
         <v>221.3909090909091</v>
       </c>
-      <c r="J29" s="10">
+      <c r="K29" s="10">
         <f t="shared" si="1"/>
         <v>186.3909090909091</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>1</v>
       </c>
       <c r="Q29" t="str">
-        <v>jawgemo</v>
+        <v>kaajak</v>
       </c>
       <c r="R29" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="S29" s="11">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="T29" s="10">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="U29" s="11">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="V29" s="10">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="W29" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y29" s="10">
-        <v>258.06363636363636</v>
+        <v>7</v>
       </c>
       <c r="Z29" s="10">
-        <v>211.56363636363636</v>
+        <v>255.25454545454545</v>
       </c>
       <c r="AA29">
-        <v>1</v>
+        <v>197.75454545454545</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="8">
         <v>0.3</v>
@@ -2705,59 +2798,62 @@
         <v>150</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" s="4">
         <v>90</v>
       </c>
       <c r="I30" s="4">
+        <v>9</v>
+      </c>
+      <c r="J30" s="4">
         <f t="shared" si="0"/>
         <v>234.88181818181818</v>
       </c>
-      <c r="J30" s="10">
+      <c r="K30" s="10">
         <f t="shared" si="1"/>
         <v>202.38181818181818</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>1</v>
       </c>
       <c r="Q30" t="str">
-        <v>Derke</v>
+        <v>Meiy</v>
       </c>
       <c r="R30" s="11">
         <v>0.35</v>
       </c>
       <c r="S30" s="11">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="T30" s="10">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="U30" s="11">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="V30" s="10">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="W30" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X30">
         <v>90</v>
       </c>
       <c r="Y30" s="10">
-        <v>255.07272727272726</v>
+        <v>7</v>
       </c>
       <c r="Z30" s="10">
-        <v>210.07272727272726</v>
+        <v>236.8</v>
       </c>
       <c r="AA30">
-        <v>1</v>
+        <v>201.8</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B31" s="8">
         <v>0.32</v>
@@ -2775,59 +2871,62 @@
         <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H31" s="4">
         <v>90</v>
       </c>
       <c r="I31" s="4">
+        <v>6</v>
+      </c>
+      <c r="J31" s="4">
         <f t="shared" si="0"/>
         <v>218.98181818181817</v>
       </c>
-      <c r="J31" s="10">
+      <c r="K31" s="10">
         <f t="shared" si="1"/>
         <v>173.98181818181817</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>1</v>
       </c>
       <c r="Q31" t="str">
-        <v>Lisa</v>
+        <v>Verno</v>
       </c>
       <c r="R31" s="11">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S31" s="11">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="T31" s="10">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="U31" s="11">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="V31" s="10">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="W31" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X31">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Y31" s="10">
-        <v>269.7</v>
+        <v>7</v>
       </c>
       <c r="Z31" s="10">
-        <v>209.7</v>
+        <v>223.88181818181818</v>
       </c>
       <c r="AA31">
-        <v>1</v>
+        <v>180.88181818181818</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" s="8">
         <v>0.35</v>
@@ -2845,59 +2944,62 @@
         <v>110</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H32" s="4">
         <v>70</v>
       </c>
       <c r="I32" s="4">
+        <v>5</v>
+      </c>
+      <c r="J32" s="4">
         <f t="shared" si="0"/>
         <v>245.8</v>
       </c>
-      <c r="J32" s="10">
+      <c r="K32" s="10">
         <f t="shared" si="1"/>
         <v>207.8</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>1</v>
       </c>
       <c r="Q32" t="str">
-        <v>vo0kashu</v>
+        <v>t3xture</v>
       </c>
       <c r="R32" s="11">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S32" s="11">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="T32" s="10">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="U32" s="11">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="V32" s="10">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="W32" t="str">
         <v>タイガー</v>
       </c>
       <c r="X32">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Y32" s="10">
-        <v>249.67272727272729</v>
+        <v>7</v>
       </c>
       <c r="Z32" s="10">
-        <v>209.67272727272729</v>
+        <v>261.38181818181818</v>
       </c>
       <c r="AA32">
-        <v>1</v>
+        <v>214.88181818181818</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B33" s="8">
         <v>0.38</v>
@@ -2915,59 +3017,62 @@
         <v>130</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" s="4">
         <v>70</v>
       </c>
       <c r="I33" s="4">
+        <v>5</v>
+      </c>
+      <c r="J33" s="4">
         <f t="shared" si="0"/>
         <v>259.4909090909091</v>
       </c>
-      <c r="J33" s="10">
+      <c r="K33" s="10">
         <f t="shared" si="1"/>
         <v>219.9909090909091</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>1</v>
       </c>
       <c r="Q33" t="str">
-        <v>HYUNMIN</v>
+        <v>tex</v>
       </c>
       <c r="R33" s="11">
         <v>0.35</v>
       </c>
       <c r="S33" s="11">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="T33" s="10">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="U33" s="11">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="V33" s="10">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="W33" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X33">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Y33" s="10">
-        <v>245.8</v>
+        <v>7</v>
       </c>
       <c r="Z33" s="10">
-        <v>207.8</v>
+        <v>233.68181818181819</v>
       </c>
       <c r="AA33">
-        <v>1</v>
+        <v>191.18181818181819</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="15.75" customHeight="1">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" s="9">
         <v>0.28000000000000003</v>
@@ -2985,59 +3090,62 @@
         <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="4">
         <v>50</v>
       </c>
       <c r="I34" s="4">
+        <v>5</v>
+      </c>
+      <c r="J34" s="4">
         <f t="shared" si="0"/>
         <v>227.23636363636362</v>
       </c>
-      <c r="J34" s="10">
+      <c r="K34" s="10">
         <f t="shared" si="1"/>
         <v>167.23636363636362</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>1</v>
       </c>
       <c r="Q34" t="str">
-        <v>Absol</v>
+        <v>Mazino</v>
       </c>
       <c r="R34" s="11">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="S34" s="11">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T34" s="10">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="U34" s="11">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="V34" s="10">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="W34" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X34">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Y34" s="10">
-        <v>259.66363636363639</v>
+        <v>7</v>
       </c>
       <c r="Z34" s="10">
-        <v>207.16363636363639</v>
+        <v>233.82727272727274</v>
       </c>
       <c r="AA34">
-        <v>1</v>
+        <v>183.82727272727274</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="15.75" customHeight="1">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B35">
         <v>0.33</v>
@@ -3055,59 +3163,62 @@
         <v>150</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" s="4">
         <v>75</v>
       </c>
       <c r="I35" s="4">
+        <v>7</v>
+      </c>
+      <c r="J35" s="4">
         <f t="shared" si="0"/>
         <v>261.38181818181818</v>
       </c>
-      <c r="J35" s="10">
+      <c r="K35" s="10">
         <f t="shared" si="1"/>
         <v>214.88181818181818</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>1</v>
       </c>
       <c r="Q35" t="str">
-        <v>Wo0t</v>
+        <v>BABYBAY</v>
       </c>
       <c r="R35" s="11">
         <v>0.4</v>
       </c>
       <c r="S35" s="11">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="T35" s="10">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="U35" s="11">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="V35" s="10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="W35" t="str">
         <v>タイガー</v>
       </c>
       <c r="X35">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="Y35" s="10">
-        <v>244.24545454545452</v>
+        <v>7</v>
       </c>
       <c r="Z35" s="10">
-        <v>205.24545454545452</v>
+        <v>234.35454545454547</v>
       </c>
       <c r="AA35">
-        <v>1</v>
+        <v>191.85454545454547</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" customHeight="1">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B36">
         <v>0.3</v>
@@ -3125,27 +3236,30 @@
         <v>85</v>
       </c>
       <c r="G36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H36" s="4">
         <v>40</v>
       </c>
       <c r="I36" s="4">
+        <v>5</v>
+      </c>
+      <c r="J36" s="4">
         <f t="shared" si="0"/>
         <v>234.5363636363636</v>
       </c>
-      <c r="J36" s="10">
+      <c r="K36" s="10">
         <f t="shared" si="1"/>
         <v>174.5363636363636</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>1</v>
       </c>
       <c r="Q36" t="str">
-        <v>Smoggy</v>
+        <v>Rarga</v>
       </c>
       <c r="R36" s="11">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="S36" s="11">
         <v>0.19</v>
@@ -3154,30 +3268,30 @@
         <v>75</v>
       </c>
       <c r="U36" s="11">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="V36" s="10">
         <v>120</v>
       </c>
       <c r="W36" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X36">
         <v>50</v>
       </c>
       <c r="Y36" s="10">
-        <v>242.64545454545453</v>
+        <v>7</v>
       </c>
       <c r="Z36" s="10">
-        <v>205.14545454545453</v>
+        <v>241.34545454545454</v>
       </c>
       <c r="AA36">
-        <v>1</v>
+        <v>203.84545454545454</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="15.75" customHeight="1">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37">
         <v>0.38</v>
@@ -3195,59 +3309,62 @@
         <v>80</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H37" s="4">
         <v>40</v>
       </c>
       <c r="I37" s="4">
+        <v>5</v>
+      </c>
+      <c r="J37" s="4">
         <f t="shared" si="0"/>
         <v>229.36363636363637</v>
       </c>
-      <c r="J37" s="10">
+      <c r="K37" s="10">
         <f t="shared" si="1"/>
         <v>184.86363636363637</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>1</v>
       </c>
       <c r="Q37" t="str">
-        <v>Loita</v>
+        <v>Lysoar</v>
       </c>
       <c r="R37" s="11">
         <v>0.33</v>
       </c>
       <c r="S37" s="11">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="T37" s="10">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="U37" s="11">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="V37" s="10">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="W37" t="str">
         <v>スモーカー</v>
       </c>
       <c r="X37">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="Y37" s="10">
-        <v>260.35454545454547</v>
+        <v>7</v>
       </c>
       <c r="Z37" s="10">
-        <v>204.85454545454547</v>
+        <v>236.05454545454546</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>183.55454545454546</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="15.75" customHeight="1">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38">
         <v>0.31</v>
@@ -3265,59 +3382,62 @@
         <v>90</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H38" s="4">
         <v>70</v>
       </c>
       <c r="I38" s="4">
+        <v>8</v>
+      </c>
+      <c r="J38" s="4">
         <f t="shared" si="0"/>
         <v>225.6090909090909</v>
       </c>
-      <c r="J38" s="10">
+      <c r="K38" s="10">
         <f t="shared" si="1"/>
         <v>181.1090909090909</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>1</v>
       </c>
       <c r="Q38" t="str">
-        <v>Rarga</v>
+        <v>s0m</v>
       </c>
       <c r="R38" s="11">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="S38" s="11">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="T38" s="10">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="U38" s="11">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="V38" s="10">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="W38" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y38" s="10">
-        <v>241.34545454545454</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="10">
-        <v>203.84545454545454</v>
+        <v>268.32727272727266</v>
       </c>
       <c r="AA38">
-        <v>1</v>
+        <v>195.82727272727269</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="15.75" customHeight="1">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B39">
         <v>0.28999999999999998</v>
@@ -3335,59 +3455,62 @@
         <v>80</v>
       </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="4">
         <v>40</v>
       </c>
       <c r="I39" s="4">
+        <v>4</v>
+      </c>
+      <c r="J39" s="4">
         <f t="shared" si="0"/>
         <v>231.86363636363637</v>
       </c>
-      <c r="J39" s="10">
+      <c r="K39" s="10">
         <f t="shared" si="1"/>
         <v>176.86363636363637</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>1</v>
       </c>
       <c r="Q39" t="str">
-        <v>ZMJKK</v>
+        <v>Canezerra</v>
       </c>
       <c r="R39" s="11">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="S39" s="11">
         <v>0.17</v>
       </c>
       <c r="T39" s="10">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="U39" s="11">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="V39" s="10">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="W39" t="str">
         <v>タイガー</v>
       </c>
       <c r="X39">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y39" s="10">
-        <v>234.88181818181818</v>
+        <v>7</v>
       </c>
       <c r="Z39" s="10">
-        <v>202.38181818181818</v>
+        <v>274.71818181818185</v>
       </c>
       <c r="AA39">
-        <v>1</v>
+        <v>232.21818181818185</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="15.75" customHeight="1">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B40">
         <v>0.28999999999999998</v>
@@ -3405,59 +3528,62 @@
         <v>80</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H40" s="4">
         <v>70</v>
       </c>
       <c r="I40" s="4">
+        <v>4</v>
+      </c>
+      <c r="J40" s="4">
         <f t="shared" si="0"/>
         <v>228.26363636363635</v>
       </c>
-      <c r="J40" s="10">
+      <c r="K40" s="10">
         <f t="shared" si="1"/>
         <v>163.26363636363635</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>1</v>
       </c>
       <c r="Q40" t="str">
-        <v>Arlecchino</v>
+        <v>Tartaglia</v>
       </c>
       <c r="R40" s="11">
-        <v>0.47</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="S40" s="11">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="T40" s="10">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="U40" s="11">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="V40" s="10">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="W40" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X40">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Y40" s="10">
-        <v>269.71818181818179</v>
+        <v>7</v>
       </c>
       <c r="Z40" s="10">
-        <v>202.21818181818179</v>
+        <v>270.28181818181821</v>
       </c>
       <c r="AA40">
-        <v>1</v>
+        <v>232.78181818181821</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="15.75" customHeight="1">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B41">
         <v>0.35</v>
@@ -3475,59 +3601,62 @@
         <v>95</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" s="4">
         <v>60</v>
       </c>
       <c r="I41" s="4">
+        <v>7</v>
+      </c>
+      <c r="J41" s="4">
         <f t="shared" si="0"/>
         <v>233.68181818181819</v>
       </c>
-      <c r="J41" s="10">
+      <c r="K41" s="10">
         <f t="shared" si="1"/>
         <v>191.18181818181819</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>1</v>
       </c>
       <c r="Q41" t="str">
-        <v>Meiy</v>
+        <v>Asuna</v>
       </c>
       <c r="R41" s="11">
-        <v>0.35</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S41" s="11">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="T41" s="10">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="U41" s="11">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="V41" s="10">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="W41" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X41">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Y41" s="10">
-        <v>236.8</v>
+        <v>7</v>
       </c>
       <c r="Z41" s="10">
-        <v>201.8</v>
+        <v>237.41818181818181</v>
       </c>
       <c r="AA41">
-        <v>1</v>
+        <v>194.91818181818181</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="15.75" customHeight="1">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B42">
         <v>0.33</v>
@@ -3545,36 +3674,39 @@
         <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" s="4">
         <v>60</v>
       </c>
       <c r="I42" s="4">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4">
         <f t="shared" si="0"/>
         <v>233.82727272727274</v>
       </c>
-      <c r="J42" s="10">
+      <c r="K42" s="10">
         <f t="shared" si="1"/>
         <v>183.82727272727274</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>1</v>
       </c>
       <c r="Q42" t="str">
-        <v>mada</v>
+        <v>Sato</v>
       </c>
       <c r="R42" s="11">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="S42" s="11">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="T42" s="10">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="U42" s="11">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="V42" s="10">
         <v>105</v>
@@ -3583,21 +3715,21 @@
         <v>フラッシュ</v>
       </c>
       <c r="X42">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y42" s="10">
-        <v>253.72727272727272</v>
+        <v>6</v>
       </c>
       <c r="Z42" s="10">
-        <v>201.22727272727272</v>
+        <v>234.42727272727271</v>
       </c>
       <c r="AA42">
-        <v>1</v>
+        <v>200.92727272727271</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="15.75" customHeight="1">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B43">
         <v>0.35</v>
@@ -3615,59 +3747,62 @@
         <v>105</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" s="4">
         <v>100</v>
       </c>
       <c r="I43" s="4">
+        <v>8</v>
+      </c>
+      <c r="J43" s="4">
         <f t="shared" si="0"/>
         <v>243.22727272727272</v>
       </c>
-      <c r="J43" s="10">
+      <c r="K43" s="10">
         <f t="shared" si="1"/>
         <v>200.72727272727272</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>1</v>
       </c>
       <c r="Q43" t="str">
-        <v>Sato</v>
+        <v>Boostio</v>
       </c>
       <c r="R43" s="11">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S43" s="11">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="T43" s="10">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="U43" s="11">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="V43" s="10">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="W43" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X43">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y43" s="10">
-        <v>234.42727272727271</v>
+        <v>6</v>
       </c>
       <c r="Z43" s="10">
-        <v>200.92727272727271</v>
+        <v>226.93636363636364</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>162.93636363636364</v>
       </c>
     </row>
     <row r="44" spans="1:27" ht="15.75" customHeight="1">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B44">
         <v>0.4</v>
@@ -3685,59 +3820,62 @@
         <v>100</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H44" s="4">
         <v>55</v>
       </c>
       <c r="I44" s="4">
+        <v>7</v>
+      </c>
+      <c r="J44" s="4">
         <f t="shared" si="0"/>
         <v>234.35454545454547</v>
       </c>
-      <c r="J44" s="10">
+      <c r="K44" s="10">
         <f t="shared" si="1"/>
         <v>191.85454545454547</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>1</v>
       </c>
       <c r="Q44" t="str">
-        <v>Zekken</v>
+        <v>Laz</v>
       </c>
       <c r="R44" s="11">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="S44" s="11">
-        <v>0.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="T44" s="10">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="U44" s="11">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="V44" s="10">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="W44" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X44">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Y44" s="10">
-        <v>243.22727272727272</v>
+        <v>6</v>
       </c>
       <c r="Z44" s="10">
-        <v>200.72727272727272</v>
+        <v>221.3909090909091</v>
       </c>
       <c r="AA44">
-        <v>1</v>
+        <v>186.3909090909091</v>
       </c>
     </row>
     <row r="45" spans="1:27" ht="15.75" customHeight="1">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B45">
         <v>0.33</v>
@@ -3755,59 +3893,62 @@
         <v>100</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" s="4">
         <v>50</v>
       </c>
       <c r="I45" s="4">
+        <v>5</v>
+      </c>
+      <c r="J45" s="4">
         <f t="shared" si="0"/>
         <v>232.15454545454543</v>
       </c>
-      <c r="J45" s="10">
+      <c r="K45" s="10">
         <f t="shared" si="1"/>
         <v>194.65454545454543</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>1</v>
       </c>
       <c r="Q45" t="str">
-        <v>Less</v>
+        <v>Brawk</v>
       </c>
       <c r="R45" s="11">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="S45" s="11">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="T45" s="10">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U45" s="11">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="V45" s="10">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="W45" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X45">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Y45" s="10">
-        <v>243.37272727272727</v>
+        <v>6</v>
       </c>
       <c r="Z45" s="10">
-        <v>200.37272727272727</v>
+        <v>218.98181818181817</v>
       </c>
       <c r="AA45">
-        <v>1</v>
+        <v>173.98181818181817</v>
       </c>
     </row>
     <row r="46" spans="1:27" ht="15.75" customHeight="1">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B46">
         <v>0.28999999999999998</v>
@@ -3825,59 +3966,62 @@
         <v>93</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" s="4">
         <v>40</v>
       </c>
       <c r="I46" s="4">
+        <v>5</v>
+      </c>
+      <c r="J46" s="4">
         <f t="shared" si="0"/>
         <v>229.07272727272726</v>
       </c>
-      <c r="J46" s="10">
+      <c r="K46" s="10">
         <f t="shared" si="1"/>
         <v>169.07272727272726</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>1</v>
       </c>
       <c r="Q46" t="str">
-        <v>Lar0k</v>
+        <v>skuba</v>
       </c>
       <c r="R46" s="11">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="S46" s="11">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="T46" s="10">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="U46" s="11">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="V46" s="10">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="W46" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X46">
         <v>50</v>
       </c>
       <c r="Y46" s="10">
-        <v>242.1090909090909</v>
+        <v>6</v>
       </c>
       <c r="Z46" s="10">
-        <v>199.6090909090909</v>
+        <v>233.45454545454544</v>
       </c>
       <c r="AA46">
-        <v>1</v>
+        <v>180.95454545454544</v>
       </c>
     </row>
     <row r="47" spans="1:27" ht="15.75" customHeight="1">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B47">
         <v>0.3</v>
@@ -3895,59 +4039,62 @@
         <v>100</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" s="4">
         <v>60</v>
       </c>
       <c r="I47" s="4">
+        <v>5</v>
+      </c>
+      <c r="J47" s="4">
         <f t="shared" si="0"/>
         <v>231.15454545454543</v>
       </c>
-      <c r="J47" s="10">
+      <c r="K47" s="10">
         <f t="shared" si="1"/>
         <v>191.15454545454543</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>1</v>
       </c>
       <c r="Q47" t="str">
-        <v>Crewn</v>
+        <v>Cryocells</v>
       </c>
       <c r="R47" s="11">
-        <v>0.25</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S47" s="11">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="T47" s="10">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="U47" s="11">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="V47" s="10">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="W47" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X47">
         <v>65</v>
       </c>
       <c r="Y47" s="10">
-        <v>266.27272727272725</v>
+        <v>6</v>
       </c>
       <c r="Z47" s="10">
-        <v>198.77272727272725</v>
+        <v>233.60000000000002</v>
       </c>
       <c r="AA47">
-        <v>1</v>
+        <v>191.10000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:27" ht="15.75" customHeight="1">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B48">
         <v>0.38</v>
@@ -3965,59 +4112,62 @@
         <v>120</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H48" s="4">
         <v>170</v>
       </c>
       <c r="I48" s="4">
+        <v>9</v>
+      </c>
+      <c r="J48" s="4">
         <f t="shared" si="0"/>
         <v>268.34545454545457</v>
       </c>
-      <c r="J48" s="10">
+      <c r="K48" s="10">
         <f t="shared" si="1"/>
         <v>215.84545454545454</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>1</v>
       </c>
       <c r="Q48" t="str">
-        <v>kaajak</v>
+        <v>Loita</v>
       </c>
       <c r="R48" s="11">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S48" s="11">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="T48" s="10">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="U48" s="11">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="V48" s="10">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="W48" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X48">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="Y48" s="10">
-        <v>255.25454545454545</v>
+        <v>6</v>
       </c>
       <c r="Z48" s="10">
-        <v>197.75454545454545</v>
+        <v>260.35454545454547</v>
       </c>
       <c r="AA48">
-        <v>1</v>
+        <v>204.85454545454547</v>
       </c>
     </row>
     <row r="49" spans="1:27" ht="15.75" customHeight="1">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B49">
         <v>0.3</v>
@@ -4035,59 +4185,62 @@
         <v>95</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" s="4">
         <v>50</v>
       </c>
       <c r="I49" s="4">
+        <v>10</v>
+      </c>
+      <c r="J49" s="4">
         <f t="shared" si="0"/>
         <v>228.58181818181816</v>
       </c>
-      <c r="J49" s="10">
+      <c r="K49" s="10">
         <f t="shared" si="1"/>
         <v>184.58181818181816</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>1</v>
       </c>
       <c r="Q49" t="str">
-        <v>s0m</v>
+        <v>Boaster</v>
       </c>
       <c r="R49" s="11">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="S49" s="11">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="T49" s="10">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="U49" s="11">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="V49" s="10">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="W49" t="str">
         <v>スモーカー</v>
       </c>
       <c r="X49">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y49" s="10">
-        <v>268.32727272727266</v>
+        <v>5</v>
       </c>
       <c r="Z49" s="10">
-        <v>195.82727272727269</v>
+        <v>232.13636363636363</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>144.63636363636363</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B50" s="5">
         <v>0.31</v>
@@ -4105,59 +4258,62 @@
         <v>100</v>
       </c>
       <c r="G50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H50" s="4">
         <v>50</v>
       </c>
       <c r="I50" s="4">
+        <v>9</v>
+      </c>
+      <c r="J50" s="4">
         <f t="shared" si="0"/>
         <v>225.85454545454542</v>
       </c>
-      <c r="J50" s="10">
+      <c r="K50" s="10">
         <f t="shared" si="1"/>
         <v>181.35454545454542</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>1</v>
       </c>
       <c r="Q50" t="str">
-        <v>Asuna</v>
+        <v>d4v41</v>
       </c>
       <c r="R50" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="S50" s="11">
         <v>0.17</v>
       </c>
       <c r="T50" s="10">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="U50" s="11">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="V50" s="10">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="W50" t="str">
-        <v>フラッシュ</v>
+        <v>シーカー</v>
       </c>
       <c r="X50">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Y50" s="10">
-        <v>237.41818181818181</v>
+        <v>5</v>
       </c>
       <c r="Z50" s="10">
-        <v>194.91818181818181</v>
+        <v>223.42727272727271</v>
       </c>
       <c r="AA50">
-        <v>1</v>
+        <v>188.42727272727271</v>
       </c>
     </row>
     <row r="51" spans="1:27" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B51" s="5">
         <v>0.35</v>
@@ -4175,59 +4331,62 @@
         <v>120</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H51" s="4">
         <v>50</v>
       </c>
       <c r="I51" s="4">
+        <v>7</v>
+      </c>
+      <c r="J51" s="4">
         <f t="shared" si="0"/>
         <v>241.34545454545454</v>
       </c>
-      <c r="J51" s="10">
+      <c r="K51" s="10">
         <f t="shared" si="1"/>
         <v>203.84545454545454</v>
       </c>
-      <c r="K51">
+      <c r="L51">
         <v>1</v>
       </c>
       <c r="Q51" t="str">
-        <v>Dep</v>
+        <v>valyn</v>
       </c>
       <c r="R51" s="11">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="S51" s="11">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="T51" s="10">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="U51" s="11">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="V51" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="W51" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X51">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y51" s="10">
-        <v>232.15454545454543</v>
+        <v>5</v>
       </c>
       <c r="Z51" s="10">
-        <v>194.65454545454543</v>
+        <v>226.28181818181821</v>
       </c>
       <c r="AA51">
-        <v>1</v>
+        <v>156.28181818181818</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B52" s="5">
         <v>0.33</v>
@@ -4245,59 +4404,62 @@
         <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H52" s="4">
         <v>50</v>
       </c>
       <c r="I52" s="4">
+        <v>7</v>
+      </c>
+      <c r="J52" s="4">
         <f t="shared" si="0"/>
         <v>236.05454545454546</v>
       </c>
-      <c r="J52" s="10">
+      <c r="K52" s="10">
         <f t="shared" si="1"/>
         <v>183.55454545454546</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>1</v>
       </c>
       <c r="Q52" t="str">
-        <v>WsLeo</v>
+        <v>Sayonara</v>
       </c>
       <c r="R52" s="11">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="S52" s="11">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="T52" s="10">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="U52" s="11">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="V52" s="10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="W52" t="str">
         <v>シーカー</v>
       </c>
       <c r="X52">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Y52" s="10">
-        <v>259.26363636363635</v>
+        <v>5</v>
       </c>
       <c r="Z52" s="10">
-        <v>194.26363636363635</v>
+        <v>228.6090909090909</v>
       </c>
       <c r="AA52">
-        <v>1</v>
+        <v>181.1090909090909</v>
       </c>
     </row>
     <row r="53" spans="1:27" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B53" s="5">
         <v>0.38</v>
@@ -4315,59 +4477,62 @@
         <v>120</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H53" s="4">
         <v>50</v>
       </c>
       <c r="I53" s="4">
+        <v>8</v>
+      </c>
+      <c r="J53" s="4">
         <f t="shared" si="0"/>
         <v>242.64545454545453</v>
       </c>
-      <c r="J53" s="10">
+      <c r="K53" s="10">
         <f t="shared" si="1"/>
         <v>205.14545454545453</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>1</v>
       </c>
       <c r="Q53" t="str">
-        <v>Nanasaki</v>
+        <v>Primmie</v>
       </c>
       <c r="R53" s="11">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="S53" s="11">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="T53" s="10">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="U53" s="11">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="V53" s="10">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="W53" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X53">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Y53" s="10">
-        <v>253.86363636363637</v>
+        <v>5</v>
       </c>
       <c r="Z53" s="10">
-        <v>193.86363636363637</v>
+        <v>252.64545454545453</v>
       </c>
       <c r="AA53">
-        <v>1</v>
+        <v>223.14545454545456</v>
       </c>
     </row>
     <row r="54" spans="1:27" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B54" s="5">
         <v>0.32</v>
@@ -4385,59 +4550,62 @@
         <v>100</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" s="4">
         <v>50</v>
       </c>
       <c r="I54" s="4">
+        <v>9</v>
+      </c>
+      <c r="J54" s="4">
         <f t="shared" si="0"/>
         <v>227.85454545454547</v>
       </c>
-      <c r="J54" s="10">
+      <c r="K54" s="10">
         <f t="shared" si="1"/>
         <v>187.85454545454547</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>1</v>
       </c>
       <c r="Q54" t="str">
-        <v>BABYBAY</v>
+        <v>HYUNMIN</v>
       </c>
       <c r="R54" s="11">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="S54" s="11">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="T54" s="10">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="U54" s="11">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="V54" s="10">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="W54" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X54">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Y54" s="10">
-        <v>234.35454545454547</v>
+        <v>5</v>
       </c>
       <c r="Z54" s="10">
-        <v>191.85454545454547</v>
+        <v>245.8</v>
       </c>
       <c r="AA54">
-        <v>1</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="55" spans="1:27" ht="15.75" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B55" s="5">
         <v>0.28000000000000003</v>
@@ -4455,59 +4623,62 @@
         <v>80</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H55" s="4">
         <v>45</v>
       </c>
       <c r="I55" s="4">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4">
         <f t="shared" si="0"/>
         <v>234.06363636363636</v>
       </c>
-      <c r="J55" s="10">
+      <c r="K55" s="10">
         <f t="shared" si="1"/>
         <v>164.06363636363636</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>1</v>
       </c>
       <c r="Q55" t="str">
-        <v>tex</v>
+        <v>Flashback</v>
       </c>
       <c r="R55" s="11">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="S55" s="11">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="T55" s="10">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="U55" s="11">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="V55" s="10">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="W55" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X55">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y55" s="10">
-        <v>233.68181818181819</v>
+        <v>5</v>
       </c>
       <c r="Z55" s="10">
-        <v>191.18181818181819</v>
+        <v>259.4909090909091</v>
       </c>
       <c r="AA55">
-        <v>1</v>
+        <v>219.9909090909091</v>
       </c>
     </row>
     <row r="56" spans="1:27" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B56" s="5">
         <v>0.17</v>
@@ -4525,59 +4696,62 @@
         <v>70</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H56" s="4">
         <v>10</v>
       </c>
       <c r="I56" s="4">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4">
         <f t="shared" si="0"/>
         <v>226.91818181818181</v>
       </c>
-      <c r="J56" s="10">
+      <c r="K56" s="10">
         <f t="shared" si="1"/>
         <v>131.91818181818181</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>1</v>
       </c>
       <c r="Q56" t="str">
-        <v>Buzz</v>
+        <v>Mako</v>
       </c>
       <c r="R56" s="11">
-        <v>0.3</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S56" s="11">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="T56" s="10">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="U56" s="11">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="V56" s="10">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="W56" t="str">
-        <v>タイガー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X56">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y56" s="10">
-        <v>231.15454545454543</v>
+        <v>5</v>
       </c>
       <c r="Z56" s="10">
-        <v>191.15454545454543</v>
+        <v>227.23636363636362</v>
       </c>
       <c r="AA56">
-        <v>1</v>
+        <v>167.23636363636362</v>
       </c>
     </row>
     <row r="57" spans="1:27" ht="15.75" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B57" s="5">
         <v>0.28999999999999998</v>
@@ -4595,59 +4769,62 @@
         <v>88</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="4">
         <v>50</v>
       </c>
       <c r="I57" s="4">
+        <v>9</v>
+      </c>
+      <c r="J57" s="4">
         <f t="shared" si="0"/>
         <v>237.10000000000002</v>
       </c>
-      <c r="J57" s="10">
+      <c r="K57" s="10">
         <f t="shared" si="1"/>
         <v>174.6</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>1</v>
       </c>
       <c r="Q57" t="str">
-        <v>Cryocells</v>
+        <v>trent</v>
       </c>
       <c r="R57" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="S57" s="11">
         <v>0.18</v>
       </c>
       <c r="T57" s="10">
+        <v>120</v>
+      </c>
+      <c r="U57" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="V57" s="10">
         <v>85</v>
       </c>
-      <c r="U57" s="11">
-        <v>0.76</v>
-      </c>
-      <c r="V57" s="10">
-        <v>110</v>
-      </c>
       <c r="W57" t="str">
-        <v>タイガー</v>
+        <v>シーカー</v>
       </c>
       <c r="X57">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Y57" s="10">
-        <v>233.60000000000002</v>
+        <v>5</v>
       </c>
       <c r="Z57" s="10">
-        <v>191.10000000000002</v>
+        <v>234.5363636363636</v>
       </c>
       <c r="AA57">
-        <v>1</v>
+        <v>174.5363636363636</v>
       </c>
     </row>
     <row r="58" spans="1:27" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B58" s="5">
         <v>0.34</v>
@@ -4665,59 +4842,62 @@
         <v>123</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H58" s="4">
         <v>50</v>
       </c>
       <c r="I58" s="4">
+        <v>4</v>
+      </c>
+      <c r="J58" s="4">
         <f t="shared" si="0"/>
         <v>242.1090909090909</v>
       </c>
-      <c r="J58" s="10">
+      <c r="K58" s="10">
         <f t="shared" si="1"/>
         <v>199.6090909090909</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>1</v>
       </c>
       <c r="Q58" t="str">
-        <v>Jinggg</v>
+        <v>leaf</v>
       </c>
       <c r="R58" s="11">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="S58" s="11">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="T58" s="10">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="U58" s="11">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="V58" s="10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="W58" t="str">
-        <v>タイガー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X58">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y58" s="10">
-        <v>224.40909090909091</v>
+        <v>5</v>
       </c>
       <c r="Z58" s="10">
-        <v>190.40909090909091</v>
+        <v>229.36363636363637</v>
       </c>
       <c r="AA58">
-        <v>1</v>
+        <v>184.86363636363637</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B59" s="5">
         <v>0.31</v>
@@ -4735,59 +4915,62 @@
         <v>100</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H59" s="4">
         <v>50</v>
       </c>
       <c r="I59" s="4">
+        <v>6</v>
+      </c>
+      <c r="J59" s="4">
         <f t="shared" si="0"/>
         <v>233.45454545454544</v>
       </c>
-      <c r="J59" s="10">
+      <c r="K59" s="10">
         <f t="shared" si="1"/>
         <v>180.95454545454544</v>
       </c>
-      <c r="K59">
+      <c r="L59">
         <v>1</v>
       </c>
       <c r="Q59" t="str">
-        <v>Ethan</v>
+        <v>Dep</v>
       </c>
       <c r="R59" s="11">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="S59" s="11">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="T59" s="10">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="U59" s="11">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="V59" s="10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="W59" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X59">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y59" s="10">
-        <v>263.5090909090909</v>
+        <v>5</v>
       </c>
       <c r="Z59" s="10">
-        <v>188.50909090909093</v>
+        <v>232.15454545454543</v>
       </c>
       <c r="AA59">
-        <v>1</v>
+        <v>194.65454545454543</v>
       </c>
     </row>
     <row r="60" spans="1:27" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B60" s="5">
         <v>0.28000000000000003</v>
@@ -4805,59 +4988,62 @@
         <v>95</v>
       </c>
       <c r="G60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H60" s="4">
         <v>60</v>
       </c>
       <c r="I60" s="4">
+        <v>9</v>
+      </c>
+      <c r="J60" s="4">
         <f t="shared" si="0"/>
         <v>230.4818181818182</v>
       </c>
-      <c r="J60" s="10">
+      <c r="K60" s="10">
         <f t="shared" si="1"/>
         <v>170.48181818181817</v>
       </c>
-      <c r="K60">
+      <c r="L60">
         <v>1</v>
       </c>
       <c r="Q60" t="str">
-        <v>d4v41</v>
+        <v>SugarZ3ro</v>
       </c>
       <c r="R60" s="11">
-        <v>0.35</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S60" s="11">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T60" s="10">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="U60" s="11">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="V60" s="10">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="W60" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X60">
         <v>40</v>
       </c>
       <c r="Y60" s="10">
-        <v>223.42727272727271</v>
+        <v>5</v>
       </c>
       <c r="Z60" s="10">
-        <v>188.42727272727271</v>
+        <v>229.07272727272726</v>
       </c>
       <c r="AA60">
-        <v>1</v>
+        <v>169.07272727272726</v>
       </c>
     </row>
     <row r="61" spans="1:27" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B61" s="5">
         <v>0.34</v>
@@ -4875,59 +5061,62 @@
         <v>105</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H61" s="4">
         <v>55</v>
       </c>
       <c r="I61" s="4">
+        <v>4</v>
+      </c>
+      <c r="J61" s="4">
         <f t="shared" si="0"/>
         <v>253.72727272727272</v>
       </c>
-      <c r="J61" s="10">
+      <c r="K61" s="10">
         <f t="shared" si="1"/>
         <v>201.22727272727272</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>1</v>
       </c>
       <c r="Q61" t="str">
-        <v>CHICHOO</v>
+        <v>Buzz</v>
       </c>
       <c r="R61" s="11">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="S61" s="11">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="T61" s="10">
         <v>80</v>
       </c>
       <c r="U61" s="11">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="V61" s="10">
         <v>100</v>
       </c>
       <c r="W61" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X61">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Y61" s="10">
-        <v>227.85454545454547</v>
+        <v>5</v>
       </c>
       <c r="Z61" s="10">
-        <v>187.85454545454547</v>
+        <v>231.15454545454543</v>
       </c>
       <c r="AA61">
-        <v>1</v>
+        <v>191.15454545454543</v>
       </c>
     </row>
     <row r="62" spans="1:27" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B62" s="5">
         <v>0.3</v>
@@ -4945,59 +5134,62 @@
         <v>116</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H62" s="4">
         <v>55</v>
       </c>
       <c r="I62" s="4">
+        <v>7</v>
+      </c>
+      <c r="J62" s="4">
         <f t="shared" si="0"/>
         <v>268.32727272727266</v>
       </c>
-      <c r="J62" s="10">
+      <c r="K62" s="10">
         <f t="shared" si="1"/>
         <v>195.82727272727269</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>1</v>
       </c>
       <c r="Q62" t="str">
-        <v>IbarakiNinja</v>
+        <v>Lisa</v>
       </c>
       <c r="R62" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.36</v>
       </c>
       <c r="S62" s="11">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="T62" s="10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="U62" s="11">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V62" s="10">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="W62" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X62">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y62" s="10">
-        <v>242.37272727272727</v>
+        <v>5</v>
       </c>
       <c r="Z62" s="10">
-        <v>187.37272727272727</v>
+        <v>269.7</v>
       </c>
       <c r="AA62">
-        <v>1</v>
+        <v>209.7</v>
       </c>
     </row>
     <row r="63" spans="1:27" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B63" s="5">
         <v>0.4</v>
@@ -5015,59 +5207,62 @@
         <v>130</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H63" s="4">
         <v>100</v>
       </c>
       <c r="I63" s="4">
+        <v>10</v>
+      </c>
+      <c r="J63" s="4">
         <f t="shared" si="0"/>
         <v>270.29090909090905</v>
       </c>
-      <c r="J63" s="10">
+      <c r="K63" s="10">
         <f t="shared" si="1"/>
         <v>235.29090909090908</v>
       </c>
-      <c r="K63">
+      <c r="L63">
         <v>1</v>
       </c>
       <c r="Q63" t="str">
-        <v>Laz</v>
+        <v>Jean</v>
       </c>
       <c r="R63" s="11">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="S63" s="11">
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="T63" s="10">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="U63" s="11">
         <v>0.75</v>
       </c>
       <c r="V63" s="10">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="W63" t="str">
-        <v>フラッシュ</v>
+        <v>シーカー</v>
       </c>
       <c r="X63">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y63" s="10">
-        <v>221.3909090909091</v>
+        <v>5</v>
       </c>
       <c r="Z63" s="10">
-        <v>186.3909090909091</v>
+        <v>269.86363636363637</v>
       </c>
       <c r="AA63">
-        <v>1</v>
+        <v>212.36363636363637</v>
       </c>
     </row>
     <row r="64" spans="1:27" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B64" s="5">
         <v>0.28999999999999998</v>
@@ -5085,59 +5280,62 @@
         <v>129</v>
       </c>
       <c r="G64" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H64" s="4">
         <v>20</v>
       </c>
       <c r="I64" s="4">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4">
         <f t="shared" si="0"/>
         <v>249.83636363636361</v>
       </c>
-      <c r="J64" s="10">
+      <c r="K64" s="10">
         <f t="shared" si="1"/>
         <v>175.33636363636361</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>1</v>
       </c>
       <c r="Q64" t="str">
-        <v>leaf</v>
+        <v>Crewn</v>
       </c>
       <c r="R64" s="11">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="S64" s="11">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="T64" s="10">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="U64" s="11">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="V64" s="10">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="W64" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X64">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Y64" s="10">
-        <v>229.36363636363637</v>
+        <v>5</v>
       </c>
       <c r="Z64" s="10">
-        <v>184.86363636363637</v>
+        <v>266.27272727272725</v>
       </c>
       <c r="AA64">
-        <v>1</v>
+        <v>198.77272727272725</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B65" s="5">
         <v>0.36</v>
@@ -5155,59 +5353,62 @@
         <v>99</v>
       </c>
       <c r="G65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H65" s="4">
         <v>40</v>
       </c>
       <c r="I65" s="4">
+        <v>5</v>
+      </c>
+      <c r="J65" s="4">
         <f t="shared" si="0"/>
         <v>269.7</v>
       </c>
-      <c r="J65" s="10">
+      <c r="K65" s="10">
         <f t="shared" si="1"/>
         <v>209.7</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>1</v>
       </c>
       <c r="Q65" t="str">
-        <v>eggsterr</v>
+        <v>Demon1</v>
       </c>
       <c r="R65" s="11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="S65" s="11">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="T65" s="10">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="U65" s="11">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="V65" s="10">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="W65" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X65">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="Y65" s="10">
-        <v>228.58181818181816</v>
+        <v>4</v>
       </c>
       <c r="Z65" s="10">
-        <v>184.58181818181816</v>
+        <v>276.5090909090909</v>
       </c>
       <c r="AA65">
-        <v>1</v>
+        <v>237.50909090909087</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B66" s="5">
         <v>0.35</v>
@@ -5225,59 +5426,62 @@
         <v>135</v>
       </c>
       <c r="G66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H66" s="4">
         <v>40</v>
       </c>
       <c r="I66" s="4">
+        <v>5</v>
+      </c>
+      <c r="J66" s="4">
         <f t="shared" si="0"/>
         <v>269.86363636363637</v>
       </c>
-      <c r="J66" s="10">
+      <c r="K66" s="10">
         <f t="shared" si="1"/>
         <v>212.36363636363637</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>1</v>
       </c>
       <c r="Q66" t="str">
-        <v>Mazino</v>
+        <v>Alfajer</v>
       </c>
       <c r="R66" s="11">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="S66" s="11">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="T66" s="10">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="U66" s="11">
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
       <c r="V66" s="10">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="W66" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X66">
         <v>60</v>
       </c>
       <c r="Y66" s="10">
-        <v>233.82727272727274</v>
+        <v>4</v>
       </c>
       <c r="Z66" s="10">
-        <v>183.82727272727274</v>
+        <v>268.80909090909086</v>
       </c>
       <c r="AA66">
-        <v>1</v>
+        <v>238.80909090909088</v>
       </c>
     </row>
     <row r="67" spans="1:27" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B67" s="5">
         <v>0.5</v>
@@ -5295,59 +5499,62 @@
         <v>100</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H67" s="4">
         <v>40</v>
       </c>
       <c r="I67" s="4">
-        <f t="shared" ref="I67:I88" si="2">B67*130+(C67)*170+(D67/2)+(E67-0.2)*130+(F67/2.2)</f>
+        <v>3</v>
+      </c>
+      <c r="J67" s="4">
+        <f t="shared" ref="J67:J89" si="2">B67*130+(C67)*170+(D67/2)+(E67-0.2)*130+(F67/2.2)</f>
         <v>270.45454545454544</v>
       </c>
-      <c r="J67" s="10">
-        <f t="shared" ref="J67:J88" si="3">B67*130+(C67)*170+(E67-0.2)*130+(F67/2.2)</f>
+      <c r="K67" s="10">
+        <f t="shared" ref="K67:K89" si="3">B67*130+(C67)*170+(E67-0.2)*130+(F67/2.2)</f>
         <v>235.45454545454544</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>1</v>
       </c>
       <c r="Q67" t="str">
-        <v>Lysoar</v>
+        <v>Jinggg</v>
       </c>
       <c r="R67" s="11">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="S67" s="11">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="T67" s="10">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="U67" s="11">
         <v>0.71</v>
       </c>
       <c r="V67" s="10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W67" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X67">
         <v>50</v>
       </c>
       <c r="Y67" s="10">
-        <v>236.05454545454546</v>
+        <v>4</v>
       </c>
       <c r="Z67" s="10">
-        <v>183.55454545454546</v>
+        <v>224.40909090909091</v>
       </c>
       <c r="AA67">
-        <v>1</v>
+        <v>190.40909090909091</v>
       </c>
     </row>
     <row r="68" spans="1:27" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B68" s="5">
         <v>0.28000000000000003</v>
@@ -5365,59 +5572,62 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H68" s="4">
         <v>50</v>
       </c>
       <c r="I68" s="4">
+        <v>10</v>
+      </c>
+      <c r="J68" s="4">
         <f t="shared" si="2"/>
         <v>242.37272727272727</v>
       </c>
-      <c r="J68" s="10">
+      <c r="K68" s="10">
         <f t="shared" si="3"/>
         <v>187.37272727272727</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>1</v>
       </c>
       <c r="Q68" t="str">
-        <v>Rossy</v>
+        <v>Ethan</v>
       </c>
       <c r="R68" s="11">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="S68" s="11">
         <v>0.18</v>
       </c>
       <c r="T68" s="10">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="U68" s="11">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="V68" s="10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W68" t="str">
         <v>シーカー</v>
       </c>
       <c r="X68">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y68" s="10">
-        <v>225.85454545454542</v>
+        <v>4</v>
       </c>
       <c r="Z68" s="10">
-        <v>181.35454545454542</v>
+        <v>263.5090909090909</v>
       </c>
       <c r="AA68">
-        <v>1</v>
+        <v>188.50909090909093</v>
       </c>
     </row>
     <row r="69" spans="1:27" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B69" s="5">
         <v>0.45</v>
@@ -5435,59 +5645,62 @@
         <v>147</v>
       </c>
       <c r="G69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H69" s="4">
         <v>80</v>
       </c>
       <c r="I69" s="4">
+        <v>7</v>
+      </c>
+      <c r="J69" s="4">
         <f t="shared" si="2"/>
         <v>274.71818181818185</v>
       </c>
-      <c r="J69" s="10">
+      <c r="K69" s="10">
         <f t="shared" si="3"/>
         <v>232.21818181818185</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>1</v>
       </c>
       <c r="Q69" t="str">
-        <v>Sayonara</v>
+        <v>Rb</v>
       </c>
       <c r="R69" s="11">
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S69" s="11">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="T69" s="10">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="U69" s="11">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="V69" s="10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="W69" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X69">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y69" s="10">
-        <v>228.6090909090909</v>
+        <v>4</v>
       </c>
       <c r="Z69" s="10">
-        <v>181.1090909090909</v>
+        <v>231.86363636363637</v>
       </c>
       <c r="AA69">
-        <v>1</v>
+        <v>176.86363636363637</v>
       </c>
     </row>
     <row r="70" spans="1:27" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B70" s="5">
         <v>0.47</v>
@@ -5505,59 +5718,62 @@
         <v>125</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H70" s="4">
         <v>100</v>
       </c>
       <c r="I70" s="4">
+        <v>1</v>
+      </c>
+      <c r="J70" s="4">
         <f t="shared" si="2"/>
         <v>269.71818181818179</v>
       </c>
-      <c r="J70" s="10">
+      <c r="K70" s="10">
         <f t="shared" si="3"/>
         <v>202.21818181818179</v>
       </c>
-      <c r="K70">
+      <c r="L70">
         <v>1</v>
       </c>
       <c r="Q70" t="str">
-        <v>keiko</v>
+        <v>stax</v>
       </c>
       <c r="R70" s="11">
-        <v>0.31</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S70" s="11">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="T70" s="10">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="U70" s="11">
-        <v>0.72</v>
+        <v>0.69</v>
       </c>
       <c r="V70" s="10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="W70" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X70">
         <v>70</v>
       </c>
       <c r="Y70" s="10">
-        <v>225.6090909090909</v>
+        <v>4</v>
       </c>
       <c r="Z70" s="10">
-        <v>181.1090909090909</v>
+        <v>228.26363636363635</v>
       </c>
       <c r="AA70">
-        <v>1</v>
+        <v>163.26363636363635</v>
       </c>
     </row>
     <row r="71" spans="1:27" ht="15.75" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B71" s="5">
         <v>0.36</v>
@@ -5575,59 +5791,62 @@
         <v>80</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H71" s="4">
         <v>50</v>
       </c>
       <c r="I71" s="4">
+        <v>9</v>
+      </c>
+      <c r="J71" s="4">
         <f t="shared" si="2"/>
         <v>259.26363636363635</v>
       </c>
-      <c r="J71" s="10">
+      <c r="K71" s="10">
         <f t="shared" si="3"/>
         <v>194.26363636363635</v>
       </c>
-      <c r="K71">
+      <c r="L71">
         <v>1</v>
       </c>
       <c r="Q71" t="str">
-        <v>skuba</v>
+        <v>Lar0k</v>
       </c>
       <c r="R71" s="11">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="S71" s="11">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T71" s="10">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="U71" s="11">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="V71" s="10">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="W71" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X71">
         <v>50</v>
       </c>
       <c r="Y71" s="10">
-        <v>233.45454545454544</v>
+        <v>4</v>
       </c>
       <c r="Z71" s="10">
-        <v>180.95454545454544</v>
+        <v>242.1090909090909</v>
       </c>
       <c r="AA71">
-        <v>1</v>
+        <v>199.6090909090909</v>
       </c>
     </row>
     <row r="72" spans="1:27" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B72" s="5">
         <v>0.5</v>
@@ -5645,60 +5864,63 @@
         <v>121</v>
       </c>
       <c r="G72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H72">
         <v>100</v>
       </c>
       <c r="I72" s="4">
+        <v>9</v>
+      </c>
+      <c r="J72" s="4">
         <f t="shared" si="2"/>
         <v>272.8</v>
       </c>
-      <c r="J72" s="10">
+      <c r="K72" s="10">
         <f t="shared" si="3"/>
         <v>235.3</v>
       </c>
-      <c r="K72">
+      <c r="L72">
         <v>1</v>
       </c>
       <c r="P72" s="10"/>
       <c r="Q72" s="10" t="str">
-        <v>Verno</v>
+        <v>mada</v>
       </c>
       <c r="R72" s="11">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="S72" s="11">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="T72" s="10">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="U72" s="11">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="V72" s="10">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="W72" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X72">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Y72" s="10">
-        <v>223.88181818181818</v>
+        <v>4</v>
       </c>
       <c r="Z72" s="10">
-        <v>180.88181818181818</v>
+        <v>253.72727272727272</v>
       </c>
       <c r="AA72">
-        <v>1</v>
+        <v>201.22727272727272</v>
       </c>
     </row>
     <row r="73" spans="1:27" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B73" s="5">
         <v>0.55000000000000004</v>
@@ -5716,60 +5938,63 @@
         <v>150</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H73">
         <v>80</v>
       </c>
       <c r="I73" s="4">
+        <v>7</v>
+      </c>
+      <c r="J73" s="4">
         <f t="shared" si="2"/>
         <v>270.28181818181821</v>
       </c>
-      <c r="J73" s="10">
+      <c r="K73" s="10">
         <f t="shared" si="3"/>
         <v>232.78181818181821</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>1</v>
       </c>
       <c r="P73" s="10"/>
       <c r="Q73" s="10" t="str">
-        <v>Rb</v>
+        <v>vo0kashu</v>
       </c>
       <c r="R73" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="S73" s="11">
         <v>0.23</v>
       </c>
       <c r="T73" s="10">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="U73" s="11">
-        <v>0.69</v>
+        <v>0.76</v>
       </c>
       <c r="V73" s="10">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="W73" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X73">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y73" s="10">
-        <v>231.86363636363637</v>
+        <v>4</v>
       </c>
       <c r="Z73" s="10">
-        <v>176.86363636363637</v>
+        <v>249.67272727272729</v>
       </c>
       <c r="AA73">
-        <v>1</v>
+        <v>209.67272727272729</v>
       </c>
     </row>
     <row r="74" spans="1:27" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B74" s="5">
         <v>0.5</v>
@@ -5787,60 +6012,63 @@
         <v>80</v>
       </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H74">
         <v>70</v>
       </c>
       <c r="I74" s="4">
+        <v>8</v>
+      </c>
+      <c r="J74" s="4">
         <f t="shared" si="2"/>
         <v>253.86363636363637</v>
       </c>
-      <c r="J74" s="10">
+      <c r="K74" s="10">
         <f t="shared" si="3"/>
         <v>193.86363636363637</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <v>1</v>
       </c>
       <c r="P74" s="10"/>
       <c r="Q74" s="10" t="str">
-        <v>Furina</v>
+        <v>marteen</v>
       </c>
       <c r="R74" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.39</v>
       </c>
       <c r="S74" s="11">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="T74" s="10">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="U74" s="11">
-        <v>0.69</v>
+        <v>0.78</v>
       </c>
       <c r="V74" s="10">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="W74" t="str">
-        <v>フラッシュ</v>
+        <v>タイガー</v>
       </c>
       <c r="X74">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="Y74" s="10">
-        <v>249.83636363636361</v>
+        <v>4</v>
       </c>
       <c r="Z74" s="10">
-        <v>175.33636363636361</v>
+        <v>254.64545454545456</v>
       </c>
       <c r="AA74">
-        <v>1</v>
+        <v>214.64545454545456</v>
       </c>
     </row>
     <row r="75" spans="1:27" ht="15.75" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B75" s="5">
         <v>0.35</v>
@@ -5858,59 +6086,62 @@
         <v>104</v>
       </c>
       <c r="G75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H75" s="4">
         <v>80</v>
       </c>
       <c r="I75" s="4">
+        <v>3</v>
+      </c>
+      <c r="J75" s="4">
         <f t="shared" si="2"/>
         <v>243.37272727272727</v>
       </c>
-      <c r="J75" s="10">
+      <c r="K75" s="10">
         <f t="shared" si="3"/>
         <v>200.37272727272727</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <v>1</v>
       </c>
       <c r="Q75" t="str">
-        <v>nAts</v>
+        <v>Chronicle</v>
       </c>
       <c r="R75" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="S75" s="11">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="T75" s="10">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="U75" s="11">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="V75" s="10">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="W75" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X75">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Y75" s="10">
-        <v>237.10000000000002</v>
+        <v>3</v>
       </c>
       <c r="Z75" s="10">
-        <v>174.6</v>
+        <v>273.86363636363637</v>
       </c>
       <c r="AA75">
-        <v>1</v>
+        <v>221.36363636363637</v>
       </c>
     </row>
     <row r="76" spans="1:27" ht="15.75" customHeight="1">
       <c r="A76" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B76" s="5">
         <v>0.46</v>
@@ -5928,59 +6159,62 @@
         <v>150</v>
       </c>
       <c r="G76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H76" s="4">
         <v>55</v>
       </c>
       <c r="I76" s="4">
+        <v>8</v>
+      </c>
+      <c r="J76" s="4">
         <f t="shared" si="2"/>
         <v>270.78181818181821</v>
       </c>
-      <c r="J76" s="10">
+      <c r="K76" s="10">
         <f t="shared" si="3"/>
         <v>228.28181818181821</v>
       </c>
-      <c r="K76">
+      <c r="L76">
         <v>1</v>
       </c>
       <c r="Q76" t="str">
-        <v>trent</v>
+        <v>F0rsakeN</v>
       </c>
       <c r="R76" s="11">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="S76" s="11">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="T76" s="10">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="U76" s="11">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="V76" s="10">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="W76" t="str">
-        <v>シーカー</v>
+        <v>スモーカー</v>
       </c>
       <c r="X76">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y76" s="10">
-        <v>234.5363636363636</v>
+        <v>3</v>
       </c>
       <c r="Z76" s="10">
-        <v>174.5363636363636</v>
+        <v>228.28181818181818</v>
       </c>
       <c r="AA76">
-        <v>1</v>
+        <v>165.78181818181818</v>
       </c>
     </row>
     <row r="77" spans="1:27" ht="15.75" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B77" s="5">
         <v>0.28999999999999998</v>
@@ -5998,59 +6232,62 @@
         <v>125</v>
       </c>
       <c r="G77" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H77" s="4">
         <v>65</v>
       </c>
       <c r="I77" s="4">
+        <v>7</v>
+      </c>
+      <c r="J77" s="4">
         <f t="shared" si="2"/>
         <v>237.41818181818181</v>
       </c>
-      <c r="J77" s="10">
+      <c r="K77" s="10">
         <f t="shared" si="3"/>
         <v>194.91818181818181</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>1</v>
       </c>
       <c r="Q77" t="str">
-        <v>Brawk</v>
+        <v>Jamppi</v>
       </c>
       <c r="R77" s="11">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="S77" s="11">
         <v>0.15</v>
       </c>
       <c r="T77" s="10">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="U77" s="11">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="V77" s="10">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="W77" t="str">
-        <v>シーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X77">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="Y77" s="10">
-        <v>218.98181818181817</v>
+        <v>3</v>
       </c>
       <c r="Z77" s="10">
-        <v>173.98181818181817</v>
+        <v>224.13636363636363</v>
       </c>
       <c r="AA77">
-        <v>1</v>
+        <v>161.63636363636363</v>
       </c>
     </row>
     <row r="78" spans="1:27" ht="15.75" customHeight="1">
       <c r="A78" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B78" s="5">
         <v>0.28999999999999998</v>
@@ -6068,59 +6305,62 @@
         <v>110</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H78" s="4">
         <v>65</v>
       </c>
       <c r="I78" s="4">
+        <v>6</v>
+      </c>
+      <c r="J78" s="4">
         <f t="shared" si="2"/>
         <v>233.60000000000002</v>
       </c>
-      <c r="J78" s="10">
+      <c r="K78" s="10">
         <f t="shared" si="3"/>
         <v>191.10000000000002</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>1</v>
       </c>
       <c r="Q78" t="str">
-        <v>C0M</v>
+        <v>Kachina</v>
       </c>
       <c r="R78" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="S78" s="11">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="T78" s="10">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="U78" s="11">
-        <v>0.69</v>
+        <v>0.9</v>
       </c>
       <c r="V78" s="10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="W78" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X78">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Y78" s="10">
-        <v>230.4818181818182</v>
+        <v>3</v>
       </c>
       <c r="Z78" s="10">
-        <v>170.48181818181817</v>
+        <v>270.45454545454544</v>
       </c>
       <c r="AA78">
-        <v>1</v>
+        <v>235.45454545454544</v>
       </c>
     </row>
     <row r="79" spans="1:27" ht="15.75" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B79" s="5">
         <v>0.35</v>
@@ -6138,129 +6378,135 @@
         <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H79" s="4">
         <v>50</v>
       </c>
       <c r="I79" s="4">
+        <v>4</v>
+      </c>
+      <c r="J79" s="4">
         <f t="shared" si="2"/>
         <v>249.67272727272729</v>
       </c>
-      <c r="J79" s="10">
+      <c r="K79" s="10">
         <f t="shared" si="3"/>
         <v>209.67272727272729</v>
       </c>
-      <c r="K79">
+      <c r="L79">
         <v>1</v>
       </c>
       <c r="Q79" t="str">
-        <v>SugarZ3ro</v>
+        <v>Less</v>
       </c>
       <c r="R79" s="11">
-        <v>0.28999999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="S79" s="11">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="T79" s="10">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="U79" s="11">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="V79" s="10">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="W79" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X79">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Y79" s="10">
-        <v>229.07272727272726</v>
+        <v>3</v>
       </c>
       <c r="Z79" s="10">
-        <v>169.07272727272726</v>
+        <v>243.37272727272727</v>
       </c>
       <c r="AA79">
-        <v>1</v>
+        <v>200.37272727272727</v>
       </c>
     </row>
     <row r="80" spans="1:27" ht="15.75" customHeight="1">
       <c r="A80" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B80" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="C80" s="5">
         <v>0.31</v>
       </c>
-      <c r="C80" s="5">
-        <v>0.2</v>
-      </c>
       <c r="D80" s="5">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E80" s="3">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="F80" s="4">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H80" s="4">
         <v>50</v>
       </c>
       <c r="I80" s="4">
+        <v>10</v>
+      </c>
+      <c r="J80" s="4">
         <f t="shared" si="2"/>
-        <v>259.66363636363639</v>
-      </c>
-      <c r="J80" s="10">
+        <v>294.75454545454545</v>
+      </c>
+      <c r="K80" s="10">
         <f t="shared" si="3"/>
-        <v>207.16363636363639</v>
-      </c>
-      <c r="K80">
+        <v>229.75454545454545</v>
+      </c>
+      <c r="L80">
         <v>1</v>
       </c>
       <c r="Q80" t="str">
-        <v>Mako</v>
+        <v>Leo</v>
       </c>
       <c r="R80" s="10">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="S80" s="10">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="T80">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="U80">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="V80">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="W80" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X80">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Y80">
-        <v>227.23636363636362</v>
+        <v>1</v>
       </c>
       <c r="Z80">
-        <v>167.23636363636362</v>
+        <v>290.76363636363635</v>
       </c>
       <c r="AA80">
-        <v>1</v>
+        <v>215.76363636363635</v>
       </c>
     </row>
     <row r="81" spans="1:27" ht="15.75" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B81" s="5">
         <v>0.39</v>
@@ -6278,59 +6524,62 @@
         <v>120</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H81" s="4">
         <v>85</v>
       </c>
       <c r="I81" s="4">
+        <v>4</v>
+      </c>
+      <c r="J81" s="4">
         <f t="shared" si="2"/>
         <v>254.64545454545456</v>
       </c>
-      <c r="J81" s="10">
+      <c r="K81" s="10">
         <f t="shared" si="3"/>
         <v>214.64545454545456</v>
       </c>
-      <c r="K81">
+      <c r="L81">
         <v>1</v>
       </c>
       <c r="Q81" t="str">
-        <v>F0rsakeN</v>
+        <v>まーやまくん</v>
       </c>
       <c r="R81" s="10">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="S81" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="T81">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="U81">
-        <v>0.69</v>
+        <v>0.8</v>
       </c>
       <c r="V81">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="W81" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X81">
         <v>50</v>
       </c>
       <c r="Y81">
-        <v>228.28181818181818</v>
+        <v>1</v>
       </c>
       <c r="Z81">
-        <v>165.78181818181818</v>
+        <v>319.83636363636361</v>
       </c>
       <c r="AA81">
-        <v>1</v>
+        <v>274.83636363636361</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="15.75" customHeight="1">
       <c r="A82" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B82" s="5">
         <v>0.25</v>
@@ -6348,59 +6597,62 @@
         <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H82" s="4">
         <v>65</v>
       </c>
       <c r="I82" s="4">
+        <v>5</v>
+      </c>
+      <c r="J82" s="4">
         <f t="shared" si="2"/>
         <v>266.27272727272725</v>
       </c>
-      <c r="J82" s="10">
+      <c r="K82" s="10">
         <f t="shared" si="3"/>
         <v>198.77272727272725</v>
       </c>
-      <c r="K82">
+      <c r="L82">
         <v>1</v>
       </c>
       <c r="Q82" t="str">
-        <v>crashies</v>
+        <v>Arlecchino</v>
       </c>
       <c r="R82" s="10">
-        <v>0.28000000000000003</v>
+        <v>0.47</v>
       </c>
       <c r="S82" s="10">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="T82">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="U82">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="V82">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="W82" t="str">
-        <v>シーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X82">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="Y82">
-        <v>234.06363636363636</v>
+        <v>1</v>
       </c>
       <c r="Z82">
-        <v>164.06363636363636</v>
+        <v>269.71818181818179</v>
       </c>
       <c r="AA82">
-        <v>1</v>
+        <v>202.21818181818179</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="15.75" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B83" s="5">
         <v>0.33</v>
@@ -6418,59 +6670,62 @@
         <v>111</v>
       </c>
       <c r="G83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H83" s="4">
         <v>77</v>
       </c>
       <c r="I83" s="4">
+        <v>6</v>
+      </c>
+      <c r="J83" s="4">
         <f t="shared" si="2"/>
         <v>260.35454545454547</v>
       </c>
-      <c r="J83" s="10">
+      <c r="K83" s="10">
         <f t="shared" si="3"/>
         <v>204.85454545454547</v>
       </c>
-      <c r="K83">
+      <c r="L83">
         <v>1</v>
       </c>
       <c r="Q83" t="str">
-        <v>stax</v>
+        <v>おもこ</v>
       </c>
       <c r="R83" s="10">
-        <v>0.28999999999999998</v>
+        <v>0.67</v>
       </c>
       <c r="S83" s="10">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
       <c r="T83">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="U83">
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="V83">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="W83" t="str">
         <v>フラッシュ</v>
       </c>
       <c r="X83">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Y83">
-        <v>228.26363636363635</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>163.26363636363635</v>
+        <v>326.05454545454546</v>
       </c>
       <c r="AA83">
-        <v>1</v>
+        <v>292.55454545454546</v>
       </c>
     </row>
     <row r="84" spans="1:27" ht="15.75" customHeight="1">
       <c r="A84" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B84" s="5">
         <v>0.41</v>
@@ -6488,59 +6743,62 @@
         <v>170</v>
       </c>
       <c r="G84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H84" s="4">
         <v>110</v>
       </c>
       <c r="I84" s="4">
+        <v>10</v>
+      </c>
+      <c r="J84" s="4">
         <f t="shared" si="2"/>
         <v>283.47272727272724</v>
       </c>
-      <c r="J84" s="10">
+      <c r="K84" s="10">
         <f t="shared" si="3"/>
         <v>240.47272727272724</v>
       </c>
-      <c r="K84">
+      <c r="L84">
         <v>0</v>
       </c>
       <c r="Q84" t="str">
-        <v>Boostio</v>
+        <v>crashies</v>
       </c>
       <c r="R84" s="10">
         <v>0.28000000000000003</v>
       </c>
       <c r="S84" s="10">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="T84">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="U84">
         <v>0.68</v>
       </c>
       <c r="V84">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="W84" t="str">
-        <v>スモーカー</v>
+        <v>シーカー</v>
       </c>
       <c r="X84">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="Y84">
-        <v>226.93636363636364</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>162.93636363636364</v>
+        <v>234.06363636363636</v>
       </c>
       <c r="AA84">
-        <v>1</v>
+        <v>164.06363636363636</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="15.75" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B85" s="5">
         <v>0.28999999999999998</v>
@@ -6558,59 +6816,62 @@
         <v>139</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H85" s="4">
         <v>120</v>
       </c>
       <c r="I85" s="4">
+        <v>10</v>
+      </c>
+      <c r="J85" s="4">
         <f t="shared" si="2"/>
         <v>283.68181818181819</v>
       </c>
-      <c r="J85" s="10">
+      <c r="K85" s="10">
         <f t="shared" si="3"/>
         <v>224.18181818181819</v>
       </c>
-      <c r="K85">
+      <c r="L85">
         <v>0</v>
       </c>
       <c r="Q85" t="str">
-        <v>Jamppi</v>
+        <v>FNS</v>
       </c>
       <c r="R85" s="10">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="S85" s="10">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="T85">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="U85">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="V85">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="W85" t="str">
-        <v>フラッシュ</v>
+        <v>スモーカー</v>
       </c>
       <c r="X85">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="Y85">
-        <v>224.13636363636363</v>
+        <v>0</v>
       </c>
       <c r="Z85">
-        <v>161.63636363636363</v>
+        <v>226.91818181818181</v>
       </c>
       <c r="AA85">
-        <v>1</v>
+        <v>131.91818181818181</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="15.75" customHeight="1">
       <c r="A86" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B86" s="5">
         <v>0.41</v>
@@ -6628,59 +6889,62 @@
         <v>155</v>
       </c>
       <c r="G86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H86" s="4">
         <v>180</v>
       </c>
       <c r="I86" s="4">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4">
         <f t="shared" si="2"/>
         <v>284.15454545454543</v>
       </c>
-      <c r="J86" s="10">
+      <c r="K86" s="10">
         <f t="shared" si="3"/>
         <v>241.65454545454543</v>
       </c>
-      <c r="K86">
+      <c r="L86">
         <v>1</v>
       </c>
       <c r="Q86" t="str">
-        <v>valyn</v>
+        <v>Furina</v>
       </c>
       <c r="R86" s="10">
-        <v>0.26</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S86" s="10">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="T86">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="U86">
-        <v>0.64</v>
+        <v>0.69</v>
       </c>
       <c r="V86">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="W86" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X86">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Y86">
-        <v>226.28181818181821</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>156.28181818181818</v>
+        <v>249.83636363636361</v>
       </c>
       <c r="AA86">
-        <v>1</v>
+        <v>175.33636363636361</v>
       </c>
     </row>
     <row r="87" spans="1:27" ht="15.75" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B87" s="5">
         <v>0.53</v>
@@ -6698,59 +6962,62 @@
         <v>155</v>
       </c>
       <c r="G87" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H87" s="4">
         <v>90</v>
       </c>
       <c r="I87" s="4">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4">
         <f t="shared" si="2"/>
         <v>284.15454545454548</v>
       </c>
-      <c r="J87" s="10">
+      <c r="K87" s="10">
         <f t="shared" si="3"/>
         <v>224.15454545454548</v>
       </c>
-      <c r="K87">
+      <c r="L87">
         <v>1</v>
       </c>
       <c r="Q87" t="str">
-        <v>Boaster</v>
+        <v>cNed</v>
       </c>
       <c r="R87" s="10">
-        <v>0.2</v>
+        <v>0.41</v>
       </c>
       <c r="S87" s="10">
         <v>0.12</v>
       </c>
       <c r="T87">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="U87">
-        <v>0.62</v>
+        <v>0.95</v>
       </c>
       <c r="V87">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="W87" t="str">
-        <v>スモーカー</v>
+        <v>タイガー</v>
       </c>
       <c r="X87">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="Y87">
-        <v>232.13636363636363</v>
+        <v>0</v>
       </c>
       <c r="Z87">
-        <v>144.63636363636363</v>
+        <v>284.15454545454543</v>
       </c>
       <c r="AA87">
-        <v>1</v>
+        <v>241.65454545454543</v>
       </c>
     </row>
     <row r="88" spans="1:27" ht="15.75" customHeight="1">
       <c r="A88" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B88" s="5">
         <v>0.25</v>
@@ -6768,96 +7035,130 @@
         <v>135</v>
       </c>
       <c r="G88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H88" s="4">
         <v>30</v>
       </c>
       <c r="I88" s="4">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4">
         <f t="shared" si="2"/>
         <v>262.36363636363637</v>
       </c>
-      <c r="J88" s="10">
+      <c r="K88" s="10">
         <f t="shared" si="3"/>
         <v>212.36363636363637</v>
       </c>
-      <c r="K88">
+      <c r="L88">
         <v>1</v>
       </c>
       <c r="Q88" t="str">
-        <v>FNS</v>
+        <v>soulcas</v>
       </c>
       <c r="R88" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="S88" s="10">
         <v>0.17</v>
       </c>
-      <c r="S88" s="10">
-        <v>0.13</v>
-      </c>
       <c r="T88">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="U88">
         <v>0.63</v>
       </c>
       <c r="V88">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="W88" t="str">
-        <v>スモーカー</v>
+        <v>フラッシュ</v>
       </c>
       <c r="X88">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="Y88">
-        <v>226.91818181818181</v>
+        <v>0</v>
       </c>
       <c r="Z88">
-        <v>131.91818181818181</v>
+        <v>284.15454545454548</v>
       </c>
       <c r="AA88">
-        <v>1</v>
+        <v>224.15454545454548</v>
       </c>
     </row>
     <row r="89" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="Q89">
-        <v>0</v>
+      <c r="A89" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="C89" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="D89" s="5">
+        <v>140</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F89" s="4">
+        <v>100</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="4">
+        <v>50</v>
+      </c>
+      <c r="I89" s="4">
+        <v>8</v>
+      </c>
+      <c r="J89" s="4">
+        <f t="shared" si="2"/>
+        <v>270.45454545454544</v>
+      </c>
+      <c r="K89" s="10">
+        <f t="shared" si="3"/>
+        <v>200.45454545454544</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>trexx</v>
       </c>
       <c r="R89" s="10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S89" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="V89">
-        <v>0</v>
-      </c>
-      <c r="W89">
-        <v>0</v>
+        <v>135</v>
+      </c>
+      <c r="W89" t="str">
+        <v>シーカー</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y89">
         <v>0</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>262.36363636363637</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>212.36363636363637</v>
       </c>
     </row>
     <row r="90" spans="1:27" ht="15.75" customHeight="1">
